--- a/research/traditional_assets/database/data/spain/spain_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_oil_gas_integrated.xlsx
@@ -650,10 +650,10 @@
         <v>0.08561747785268063</v>
       </c>
       <c r="X2">
-        <v>0.1527080310154525</v>
+        <v>0.1526791058320918</v>
       </c>
       <c r="Y2">
-        <v>-0.06709055316277183</v>
+        <v>-0.06706162797941119</v>
       </c>
       <c r="Z2">
         <v>1.587857249030445</v>
@@ -662,10 +662,10 @@
         <v>0.0743816042503847</v>
       </c>
       <c r="AB2">
-        <v>0.1028412346924208</v>
+        <v>0.1028269480556555</v>
       </c>
       <c r="AC2">
-        <v>-0.02845963044203606</v>
+        <v>-0.02844534380527075</v>
       </c>
       <c r="AD2">
         <v>14600.7</v>
@@ -787,10 +787,10 @@
         <v>0.08561747785268063</v>
       </c>
       <c r="X3">
-        <v>0.1527080310154525</v>
+        <v>0.1526791058320918</v>
       </c>
       <c r="Y3">
-        <v>-0.06709055316277183</v>
+        <v>-0.06706162797941119</v>
       </c>
       <c r="Z3">
         <v>1.587857249030445</v>
@@ -799,10 +799,10 @@
         <v>0.0743816042503847</v>
       </c>
       <c r="AB3">
-        <v>0.1028412346924208</v>
+        <v>0.1028269480556555</v>
       </c>
       <c r="AC3">
-        <v>-0.02845963044203606</v>
+        <v>-0.02844534380527075</v>
       </c>
       <c r="AD3">
         <v>14600.7</v>
@@ -1139,49 +1139,49 @@
         <v>5.67138542846357</v>
       </c>
       <c r="F2">
-        <v>3.0053940823828</v>
+        <v>3.05034711071156</v>
       </c>
       <c r="G2">
         <v>2.41174430128841</v>
       </c>
       <c r="H2">
-        <v>2.23978989098117</v>
+        <v>2.2874449950446</v>
       </c>
       <c r="I2">
         <v>0.506083104567008</v>
       </c>
       <c r="J2">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="K2">
         <v>14249.7</v>
       </c>
       <c r="L2">
-        <v>14963.912755671</v>
+        <v>15097.1287746136</v>
       </c>
       <c r="M2">
         <v>24475</v>
       </c>
       <c r="N2">
-        <v>24148.200755671</v>
+        <v>24569.9207746136</v>
       </c>
       <c r="O2">
         <v>14600.7</v>
       </c>
       <c r="P2">
-        <v>13559.688</v>
+        <v>13848.192</v>
       </c>
       <c r="Q2">
-        <v>0.102841234692421</v>
+        <v>0.102826948055655</v>
       </c>
       <c r="R2">
-        <v>0.103613177603683</v>
+        <v>0.102606636312164</v>
       </c>
       <c r="S2">
         <v>0.0541732333250682</v>
       </c>
       <c r="T2">
-        <v>0.0552982333250682</v>
+        <v>0.0533482333250682</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.152708031015452</v>
+        <v>0.152679105832092</v>
       </c>
       <c r="X2">
-        <v>0.14645850554887</v>
+        <v>0.148075931377176</v>
       </c>
       <c r="Y2">
         <v>1.65338577559359</v>
       </c>
       <c r="Z2">
-        <v>1.55673376159135</v>
+        <v>1.58217613076096</v>
       </c>
       <c r="AA2">
         <v>14600.7</v>
@@ -1236,7 +1236,7 @@
         <v>14249.7</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1062521336440803</v>
+        <v>0.1062357776319679</v>
       </c>
       <c r="C2">
-        <v>27469.44374900353</v>
+        <v>27469.90806046854</v>
       </c>
       <c r="D2">
-        <v>23094.04374900353</v>
+        <v>23094.50806046854</v>
       </c>
       <c r="E2">
         <v>-14600.7</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1062521336440803</v>
+        <v>0.1062357776319679</v>
       </c>
       <c r="T2">
         <v>0.9349222590860211</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1061494856432208</v>
+        <v>0.1061226705211387</v>
       </c>
       <c r="C3">
-        <v>27220.2202399196</v>
+        <v>27224.70706844507</v>
       </c>
       <c r="D3">
-        <v>23133.3242399196</v>
+        <v>23137.81106844507</v>
       </c>
       <c r="E3">
         <v>-14312.196</v>
@@ -1539,37 +1539,37 @@
         <v>3004.7</v>
       </c>
       <c r="M3">
-        <v>19.48295720962063</v>
+        <v>19.07905160962063</v>
       </c>
       <c r="N3">
-        <v>2985.217042790379</v>
+        <v>2985.620948390379</v>
       </c>
       <c r="O3">
-        <v>746.3042606975948</v>
+        <v>746.4052370975947</v>
       </c>
       <c r="P3">
-        <v>2238.912782092784</v>
+        <v>2239.215711292784</v>
       </c>
       <c r="Q3">
-        <v>5288.212782092784</v>
+        <v>5288.515711292785</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1067101043535051</v>
+        <v>0.1066936244322101</v>
       </c>
       <c r="T3">
         <v>0.9420050034730364</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>154.2219678292106</v>
+        <v>157.4868636806285</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1060468376423612</v>
+        <v>0.1060095634103094</v>
       </c>
       <c r="C4">
-        <v>26971.13058230481</v>
+        <v>26979.66877077926</v>
       </c>
       <c r="D4">
-        <v>23172.73858230481</v>
+        <v>23181.27677077926</v>
       </c>
       <c r="E4">
         <v>-14023.692</v>
@@ -1621,37 +1621,37 @@
         <v>3004.7</v>
       </c>
       <c r="M4">
-        <v>38.96591441924126</v>
+        <v>38.15810321924126</v>
       </c>
       <c r="N4">
-        <v>2965.734085580758</v>
+        <v>2966.541896780759</v>
       </c>
       <c r="O4">
-        <v>741.4335213951896</v>
+        <v>741.6354741951897</v>
       </c>
       <c r="P4">
-        <v>2224.300564185569</v>
+        <v>2224.906422585569</v>
       </c>
       <c r="Q4">
-        <v>5273.600564185569</v>
+        <v>5274.206422585569</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1071774214039387</v>
+        <v>0.1071608150447021</v>
       </c>
       <c r="T4">
         <v>0.9492322936638684</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.1109839146053</v>
+        <v>78.74343184031424</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1059441896415017</v>
+        <v>0.1058964562994802</v>
       </c>
       <c r="C5">
-        <v>26722.17546149152</v>
+        <v>26734.79408608879</v>
       </c>
       <c r="D5">
-        <v>23212.28746149151</v>
+        <v>23224.90608608879</v>
       </c>
       <c r="E5">
         <v>-13735.188</v>
@@ -1703,37 +1703,37 @@
         <v>3004.7</v>
       </c>
       <c r="M5">
-        <v>58.44887162886189</v>
+        <v>57.23715482886189</v>
       </c>
       <c r="N5">
-        <v>2946.251128371138</v>
+        <v>2947.462845171138</v>
       </c>
       <c r="O5">
-        <v>736.5627820927845</v>
+        <v>736.8657112927845</v>
       </c>
       <c r="P5">
-        <v>2209.688346278353</v>
+        <v>2210.597133878353</v>
       </c>
       <c r="Q5">
-        <v>5258.988346278354</v>
+        <v>5259.897133878354</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1076543738574739</v>
+        <v>0.107637638453328</v>
       </c>
       <c r="T5">
         <v>0.9566086001472948</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.40732260973687</v>
+        <v>52.49562122687616</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1058415416406422</v>
+        <v>0.105783349188651</v>
       </c>
       <c r="C6">
-        <v>26473.35556749864</v>
+        <v>26490.08393992007</v>
       </c>
       <c r="D6">
-        <v>23251.97156749864</v>
+        <v>23268.69993992006</v>
       </c>
       <c r="E6">
         <v>-13446.684</v>
@@ -1785,37 +1785,37 @@
         <v>3004.7</v>
       </c>
       <c r="M6">
-        <v>77.93182883848252</v>
+        <v>76.31620643848252</v>
       </c>
       <c r="N6">
-        <v>2926.768171161517</v>
+        <v>2928.383793561517</v>
       </c>
       <c r="O6">
-        <v>731.6920427903793</v>
+        <v>732.0959483903794</v>
       </c>
       <c r="P6">
-        <v>2195.076128371138</v>
+        <v>2196.287845171138</v>
       </c>
       <c r="Q6">
-        <v>5244.376128371138</v>
+        <v>5245.587845171138</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1081412628204578</v>
+        <v>0.1081243956829669</v>
       </c>
       <c r="T6">
         <v>0.9641385796824593</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.55549195730266</v>
+        <v>39.37171592015712</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1057388936397827</v>
+        <v>0.1056702420778217</v>
       </c>
       <c r="C7">
-        <v>26224.67159507189</v>
+        <v>26245.53926481366</v>
       </c>
       <c r="D7">
-        <v>23291.79159507189</v>
+        <v>23312.65926481366</v>
       </c>
       <c r="E7">
         <v>-13158.18</v>
@@ -1867,37 +1867,37 @@
         <v>3004.7</v>
       </c>
       <c r="M7">
-        <v>97.41478604810315</v>
+        <v>95.39525804810316</v>
       </c>
       <c r="N7">
-        <v>2907.285213951897</v>
+        <v>2909.304741951897</v>
       </c>
       <c r="O7">
-        <v>726.8213034879742</v>
+        <v>727.3261854879742</v>
       </c>
       <c r="P7">
-        <v>2180.463910463923</v>
+        <v>2181.978556463922</v>
       </c>
       <c r="Q7">
-        <v>5229.763910463923</v>
+        <v>5231.278556463923</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1086384020773992</v>
+        <v>0.1086214004332298</v>
       </c>
       <c r="T7">
         <v>0.9718270851025745</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.84439356584213</v>
+        <v>31.49737273612569</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1056362456389232</v>
+        <v>0.1055571349669925</v>
       </c>
       <c r="C8">
-        <v>25976.12424372424</v>
+        <v>26001.16100037052</v>
       </c>
       <c r="D8">
-        <v>23331.74824372425</v>
+        <v>23356.78500037053</v>
       </c>
       <c r="E8">
         <v>-12869.676</v>
@@ -1949,37 +1949,37 @@
         <v>3004.7</v>
       </c>
       <c r="M8">
-        <v>116.8977432577238</v>
+        <v>114.4743096577238</v>
       </c>
       <c r="N8">
-        <v>2887.802256742276</v>
+        <v>2890.225690342276</v>
       </c>
       <c r="O8">
-        <v>721.950564185569</v>
+        <v>722.556422585569</v>
       </c>
       <c r="P8">
-        <v>2165.851692556707</v>
+        <v>2167.669267756707</v>
       </c>
       <c r="Q8">
-        <v>5215.151692556707</v>
+        <v>5216.969267756707</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1091461187653394</v>
+        <v>0.1091289797526472</v>
       </c>
       <c r="T8">
         <v>0.9796791757443944</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.70366130486844</v>
+        <v>26.24781061343808</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1055335976380636</v>
+        <v>0.1054440278561632</v>
       </c>
       <c r="C9">
-        <v>25727.71421777697</v>
+        <v>25756.95009331896</v>
       </c>
       <c r="D9">
-        <v>23371.84221777697</v>
+        <v>23401.07809331896</v>
       </c>
       <c r="E9">
         <v>-12581.172</v>
@@ -2031,37 +2031,37 @@
         <v>3004.7</v>
       </c>
       <c r="M9">
-        <v>136.3807004673444</v>
+        <v>133.5533612673444</v>
       </c>
       <c r="N9">
-        <v>2868.319299532655</v>
+        <v>2871.146638732655</v>
       </c>
       <c r="O9">
-        <v>717.0798248831638</v>
+        <v>717.7866596831639</v>
       </c>
       <c r="P9">
-        <v>2151.239474649492</v>
+        <v>2153.359979049492</v>
       </c>
       <c r="Q9">
-        <v>5200.539474649491</v>
+        <v>5202.659979049492</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.10966475409173</v>
+        <v>0.1096474747563532</v>
       </c>
       <c r="T9">
         <v>0.9877001285505546</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.03170968988723</v>
+        <v>22.49812338294693</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1054309496372041</v>
+        <v>0.105330920745334</v>
       </c>
       <c r="C10">
-        <v>25479.44222640091</v>
+        <v>25512.90749758224</v>
       </c>
       <c r="D10">
-        <v>23412.07422640091</v>
+        <v>23445.53949758225</v>
       </c>
       <c r="E10">
         <v>-12292.668</v>
@@ -2113,37 +2113,37 @@
         <v>3004.7</v>
       </c>
       <c r="M10">
-        <v>155.863657676965</v>
+        <v>152.632412876965</v>
       </c>
       <c r="N10">
-        <v>2848.836342323035</v>
+        <v>2852.067587123035</v>
       </c>
       <c r="O10">
-        <v>712.2090855807587</v>
+        <v>713.0168967807587</v>
       </c>
       <c r="P10">
-        <v>2136.627256742276</v>
+        <v>2139.050690342276</v>
       </c>
       <c r="Q10">
-        <v>5185.927256742276</v>
+        <v>5188.350690342277</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.110194664099129</v>
+        <v>0.1101772413905745</v>
       </c>
       <c r="T10">
         <v>0.9958954498959791</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.27774597865133</v>
+        <v>19.68585796007856</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1053283016363446</v>
+        <v>0.1052178136345048</v>
       </c>
       <c r="C11">
-        <v>25231.30898365847</v>
+        <v>25269.03417434725</v>
       </c>
       <c r="D11">
-        <v>23452.44498365847</v>
+        <v>23490.17017434725</v>
       </c>
       <c r="E11">
         <v>-12004.164</v>
@@ -2195,37 +2195,37 @@
         <v>3004.7</v>
       </c>
       <c r="M11">
-        <v>175.3466148865857</v>
+        <v>171.7114644865857</v>
       </c>
       <c r="N11">
-        <v>2829.353385113414</v>
+        <v>2832.988535513414</v>
       </c>
       <c r="O11">
-        <v>707.3383462783536</v>
+        <v>708.2471338783536</v>
       </c>
       <c r="P11">
-        <v>2122.015038835061</v>
+        <v>2124.741401635061</v>
       </c>
       <c r="Q11">
-        <v>5171.31503883506</v>
+        <v>5174.041401635061</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.110736220480317</v>
+        <v>0.110718651247526</v>
       </c>
       <c r="T11">
         <v>1.00427088819405</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.13577420324563</v>
+        <v>17.49854040895872</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1052256536354851</v>
+        <v>0.1051047065236755</v>
       </c>
       <c r="C12">
-        <v>24983.31520854563</v>
+        <v>25025.33109213354</v>
       </c>
       <c r="D12">
-        <v>23492.95520854563</v>
+        <v>23534.97109213355</v>
       </c>
       <c r="E12">
         <v>-11715.66</v>
@@ -2277,37 +2277,37 @@
         <v>3004.7</v>
       </c>
       <c r="M12">
-        <v>194.8295720962063</v>
+        <v>190.7905160962063</v>
       </c>
       <c r="N12">
-        <v>2809.870427903793</v>
+        <v>2813.909483903793</v>
       </c>
       <c r="O12">
-        <v>702.4676069759483</v>
+        <v>703.4773709759484</v>
       </c>
       <c r="P12">
-        <v>2107.402820927845</v>
+        <v>2110.432112927845</v>
       </c>
       <c r="Q12">
-        <v>5156.702820927845</v>
+        <v>5159.732112927845</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1112898114477536</v>
+        <v>0.1112720924346319</v>
       </c>
       <c r="T12">
         <v>1.01283244734319</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.42219678292106</v>
+        <v>15.74868636806285</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1051230056346256</v>
+        <v>0.1049915994128463</v>
       </c>
       <c r="C13">
-        <v>24735.46162503484</v>
+        <v>24781.79922686357</v>
       </c>
       <c r="D13">
-        <v>23533.60562503484</v>
+        <v>23579.94322686357</v>
       </c>
       <c r="E13">
         <v>-11427.156</v>
@@ -2359,37 +2359,37 @@
         <v>3004.7</v>
       </c>
       <c r="M13">
-        <v>214.3125293058269</v>
+        <v>209.8695677058269</v>
       </c>
       <c r="N13">
-        <v>2790.387470694173</v>
+        <v>2794.830432294173</v>
       </c>
       <c r="O13">
-        <v>697.5968676735432</v>
+        <v>698.7076080735433</v>
       </c>
       <c r="P13">
-        <v>2092.79060302063</v>
+        <v>2096.12282422063</v>
       </c>
       <c r="Q13">
-        <v>5142.09060302063</v>
+        <v>5145.42282422063</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1118558426616495</v>
+        <v>0.111837970502347</v>
       </c>
       <c r="T13">
         <v>1.02158640107995</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.0201788935646</v>
+        <v>14.31698760732986</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1050203576337661</v>
+        <v>0.1048784923020171</v>
       </c>
       <c r="C14">
-        <v>24487.74896211803</v>
+        <v>24538.43956193349</v>
       </c>
       <c r="D14">
-        <v>23574.39696211803</v>
+        <v>23625.08756193349</v>
       </c>
       <c r="E14">
         <v>-11138.652</v>
@@ -2441,37 +2441,37 @@
         <v>3004.7</v>
       </c>
       <c r="M14">
-        <v>233.7954865154475</v>
+        <v>228.9486193154476</v>
       </c>
       <c r="N14">
-        <v>2770.904513484552</v>
+        <v>2775.751380684552</v>
       </c>
       <c r="O14">
-        <v>692.7261283711381</v>
+        <v>693.9378451711381</v>
       </c>
       <c r="P14">
-        <v>2078.178385113414</v>
+        <v>2081.813535513414</v>
       </c>
       <c r="Q14">
-        <v>5127.478385113414</v>
+        <v>5131.113535513414</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1124347382213158</v>
+        <v>0.1124167094352374</v>
       </c>
       <c r="T14">
         <v>1.030539308310728</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.85183065243422</v>
+        <v>13.12390530671904</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1049177096329065</v>
+        <v>0.1047653851911878</v>
       </c>
       <c r="C15">
-        <v>24240.17795385024</v>
+        <v>24295.25308828483</v>
       </c>
       <c r="D15">
-        <v>23615.32995385024</v>
+        <v>23670.40508828483</v>
       </c>
       <c r="E15">
         <v>-10850.148</v>
@@ -2523,37 +2523,37 @@
         <v>3004.7</v>
       </c>
       <c r="M15">
-        <v>253.2784437250682</v>
+        <v>248.0276709250682</v>
       </c>
       <c r="N15">
-        <v>2751.421556274932</v>
+        <v>2756.672329074931</v>
       </c>
       <c r="O15">
-        <v>687.855389068733</v>
+        <v>689.1680822687329</v>
       </c>
       <c r="P15">
-        <v>2063.566167206199</v>
+        <v>2067.504246806198</v>
       </c>
       <c r="Q15">
-        <v>5112.866167206199</v>
+        <v>5116.804246806199</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1130269417248824</v>
+        <v>0.1130087527114126</v>
       </c>
       <c r="T15">
         <v>1.039698029500834</v>
       </c>
       <c r="U15">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.86322829455466</v>
+        <v>12.11437412927912</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.104815061632047</v>
+        <v>0.1046522780803586</v>
       </c>
       <c r="C16">
-        <v>23992.74933939358</v>
+        <v>24052.24080447699</v>
       </c>
       <c r="D16">
-        <v>23656.40533939359</v>
+        <v>23715.89680447699</v>
       </c>
       <c r="E16">
         <v>-10561.644</v>
@@ -2605,37 +2605,37 @@
         <v>3004.7</v>
       </c>
       <c r="M16">
-        <v>272.7614009346888</v>
+        <v>267.1067225346889</v>
       </c>
       <c r="N16">
-        <v>2731.938599065311</v>
+        <v>2737.593277465311</v>
       </c>
       <c r="O16">
-        <v>682.9846497663277</v>
+        <v>684.3983193663278</v>
       </c>
       <c r="P16">
-        <v>2048.953949298983</v>
+        <v>2053.194958098983</v>
       </c>
       <c r="Q16">
-        <v>5098.253949298984</v>
+        <v>5102.494958098983</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1136329174029505</v>
+        <v>0.113614564435871</v>
       </c>
       <c r="T16">
         <v>1.049069744206989</v>
       </c>
       <c r="U16">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.01585484494361</v>
+        <v>11.24906169147346</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1047124136311875</v>
+        <v>0.1045391709695293</v>
       </c>
       <c r="C17">
-        <v>23745.46386306183</v>
+        <v>23809.40371676062</v>
       </c>
       <c r="D17">
-        <v>23697.62386306184</v>
+        <v>23761.56371676062</v>
       </c>
       <c r="E17">
         <v>-10273.14</v>
@@ -2687,37 +2687,37 @@
         <v>3004.7</v>
       </c>
       <c r="M17">
-        <v>292.2443581443094</v>
+        <v>286.1857741443094</v>
       </c>
       <c r="N17">
-        <v>2712.45564185569</v>
+        <v>2718.51422585569</v>
       </c>
       <c r="O17">
-        <v>678.1139104639226</v>
+        <v>679.6285564639226</v>
       </c>
       <c r="P17">
-        <v>2034.341731391768</v>
+        <v>2038.885669391768</v>
       </c>
       <c r="Q17">
-        <v>5083.641731391768</v>
+        <v>5088.185669391768</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1142531513322674</v>
+        <v>0.114234630553846</v>
       </c>
       <c r="T17">
         <v>1.058661969847406</v>
       </c>
       <c r="U17">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.28146452194737</v>
+        <v>10.49912424537523</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.104609765630328</v>
+        <v>0.1044260638587001</v>
       </c>
       <c r="C18">
-        <v>23498.32227436535</v>
+        <v>23566.7428391518</v>
       </c>
       <c r="D18">
-        <v>23738.98627436534</v>
+        <v>23807.4068391518</v>
       </c>
       <c r="E18">
         <v>-9984.636000000002</v>
@@ -2769,37 +2769,37 @@
         <v>3004.7</v>
       </c>
       <c r="M18">
-        <v>311.7273153539301</v>
+        <v>305.2648257539301</v>
       </c>
       <c r="N18">
-        <v>2692.97268464607</v>
+        <v>2699.43517424607</v>
       </c>
       <c r="O18">
-        <v>673.2431711615175</v>
+        <v>674.8587935615175</v>
       </c>
       <c r="P18">
-        <v>2019.729513484552</v>
+        <v>2024.576380684553</v>
       </c>
       <c r="Q18">
-        <v>5069.029513484553</v>
+        <v>5073.876380684553</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1148881527360917</v>
+        <v>0.1148694601508205</v>
       </c>
       <c r="T18">
         <v>1.068482581812596</v>
       </c>
       <c r="U18">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.638872989325664</v>
+        <v>9.842928980039281</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1045071176294685</v>
+        <v>0.1043129567478709</v>
       </c>
       <c r="C19">
-        <v>23251.32532805642</v>
+        <v>23324.25919350708</v>
       </c>
       <c r="D19">
-        <v>23780.49332805642</v>
+        <v>23853.42719350708</v>
       </c>
       <c r="E19">
         <v>-9696.132000000001</v>
@@ -2851,37 +2851,37 @@
         <v>3004.7</v>
       </c>
       <c r="M19">
-        <v>331.2102725635507</v>
+        <v>324.3438773635507</v>
       </c>
       <c r="N19">
-        <v>2673.489727436449</v>
+        <v>2680.356122636449</v>
       </c>
       <c r="O19">
-        <v>668.3724318591123</v>
+        <v>670.0890306591123</v>
       </c>
       <c r="P19">
-        <v>2005.117295577337</v>
+        <v>2010.267091977337</v>
       </c>
       <c r="Q19">
-        <v>5054.417295577337</v>
+        <v>5059.567091977337</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1155384553785625</v>
+        <v>0.1155195868465172</v>
       </c>
       <c r="T19">
         <v>1.078539835029958</v>
       </c>
       <c r="U19">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.071880460541802</v>
+        <v>9.263933157684029</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.104552969628609</v>
+        <v>0.1041998496370417</v>
       </c>
       <c r="C20">
-        <v>22944.26255278887</v>
+        <v>23081.95380959944</v>
       </c>
       <c r="D20">
-        <v>23761.93455278887</v>
+        <v>23899.62580959944</v>
       </c>
       <c r="E20">
         <v>-9407.628000000002</v>
@@ -2933,45 +2933,45 @@
         <v>3004.7</v>
       </c>
       <c r="M20">
-        <v>356.4056089731714</v>
+        <v>343.4229289731713</v>
       </c>
       <c r="N20">
-        <v>2648.294391026829</v>
+        <v>2661.277071026829</v>
       </c>
       <c r="O20">
-        <v>662.0735977567072</v>
+        <v>665.3192677567072</v>
       </c>
       <c r="P20">
-        <v>1986.220793270121</v>
+        <v>1995.957803270122</v>
       </c>
       <c r="Q20">
-        <v>5035.520793270121</v>
+        <v>5045.257803270122</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1162046190610935</v>
+        <v>0.1161855702908895</v>
       </c>
       <c r="T20">
         <v>1.088842387106281</v>
       </c>
       <c r="U20">
-        <v>0.06863097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.05147323332506819</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>8.430563168342786</v>
+        <v>8.749270204479362</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1044585716277494</v>
+        <v>0.1043004925262124</v>
       </c>
       <c r="C21">
-        <v>22693.99813237791</v>
+        <v>22752.33344822008</v>
       </c>
       <c r="D21">
-        <v>23800.17413237791</v>
+        <v>23858.50944822008</v>
       </c>
       <c r="E21">
         <v>-9119.124000000003</v>
@@ -3015,37 +3015,37 @@
         <v>3004.7</v>
       </c>
       <c r="M21">
-        <v>376.205920582792</v>
+        <v>370.724344582792</v>
       </c>
       <c r="N21">
-        <v>2628.494079417208</v>
+        <v>2633.975655417208</v>
       </c>
       <c r="O21">
-        <v>657.123519854302</v>
+        <v>658.4939138543019</v>
       </c>
       <c r="P21">
-        <v>1971.370559562906</v>
+        <v>1975.481741562906</v>
       </c>
       <c r="Q21">
-        <v>5020.670559562906</v>
+        <v>5024.781741562906</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1168872312296129</v>
+        <v>0.1168679977709252</v>
       </c>
       <c r="T21">
         <v>1.099399323184488</v>
       </c>
       <c r="U21">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.986849317377377</v>
+        <v>8.104943858978151</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1043641736268899</v>
+        <v>0.1041986354153832</v>
       </c>
       <c r="C22">
-        <v>22443.85698664642</v>
+        <v>22505.44272948604</v>
       </c>
       <c r="D22">
-        <v>23838.53698664643</v>
+        <v>23900.12272948604</v>
       </c>
       <c r="E22">
         <v>-8830.620000000003</v>
@@ -3097,37 +3097,37 @@
         <v>3004.7</v>
       </c>
       <c r="M22">
-        <v>396.0062321924127</v>
+        <v>390.2361521924126</v>
       </c>
       <c r="N22">
-        <v>2608.693767807587</v>
+        <v>2614.463847807587</v>
       </c>
       <c r="O22">
-        <v>652.1734419518968</v>
+        <v>653.6159619518968</v>
       </c>
       <c r="P22">
-        <v>1956.520325855691</v>
+        <v>1960.84788585569</v>
       </c>
       <c r="Q22">
-        <v>5005.82032585569</v>
+        <v>5010.147885855691</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1175869087023453</v>
+        <v>0.1175674859379619</v>
       </c>
       <c r="T22">
         <v>1.11022018266465</v>
       </c>
       <c r="U22">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.587506851508508</v>
+        <v>7.699696666029243</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1042697756260304</v>
+        <v>0.1040967783045539</v>
       </c>
       <c r="C23">
-        <v>22193.83971266618</v>
+        <v>22258.69742560081</v>
       </c>
       <c r="D23">
-        <v>23877.02371266618</v>
+        <v>23941.8814256008</v>
       </c>
       <c r="E23">
         <v>-8542.116000000002</v>
@@ -3179,37 +3179,37 @@
         <v>3004.7</v>
       </c>
       <c r="M23">
-        <v>415.8065438020332</v>
+        <v>409.7479598020332</v>
       </c>
       <c r="N23">
-        <v>2588.893456197967</v>
+        <v>2594.952040197967</v>
       </c>
       <c r="O23">
-        <v>647.2233640494917</v>
+        <v>648.7380100494917</v>
       </c>
       <c r="P23">
-        <v>1941.670092148475</v>
+        <v>1946.214030148475</v>
       </c>
       <c r="Q23">
-        <v>4990.970092148475</v>
+        <v>4995.514030148475</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1183042995288178</v>
+        <v>0.1182846826661894</v>
       </c>
       <c r="T23">
         <v>1.121314987954437</v>
       </c>
       <c r="U23">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.226197001436676</v>
+        <v>7.333044443837375</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1041753776251709</v>
+        <v>0.1039949211937247</v>
       </c>
       <c r="C24">
-        <v>21943.94691137093</v>
+        <v>22012.09830011227</v>
       </c>
       <c r="D24">
-        <v>23915.63491137093</v>
+        <v>23983.78630011227</v>
       </c>
       <c r="E24">
         <v>-8253.612000000001</v>
@@ -3261,37 +3261,37 @@
         <v>3004.7</v>
       </c>
       <c r="M24">
-        <v>435.6068554116539</v>
+        <v>429.2597674116539</v>
       </c>
       <c r="N24">
-        <v>2569.093144588346</v>
+        <v>2575.440232588346</v>
       </c>
       <c r="O24">
-        <v>642.2732861470865</v>
+        <v>643.8600581470864</v>
       </c>
       <c r="P24">
-        <v>1926.81985844126</v>
+        <v>1931.580174441259</v>
       </c>
       <c r="Q24">
-        <v>4976.11985844126</v>
+        <v>4980.880174441259</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1190400849918665</v>
+        <v>0.119020269054115</v>
       </c>
       <c r="T24">
         <v>1.132694275431141</v>
       </c>
       <c r="U24">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.897733501371371</v>
+        <v>6.999724241844765</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1044604796243113</v>
+        <v>0.1038930640828955</v>
       </c>
       <c r="C25">
-        <v>21539.20800556018</v>
+        <v>21765.64612192337</v>
       </c>
       <c r="D25">
-        <v>23799.40000556018</v>
+        <v>24025.83812192337</v>
       </c>
       <c r="E25">
         <v>-7965.108000000002</v>
@@ -3343,45 +3343,45 @@
         <v>3004.7</v>
       </c>
       <c r="M25">
-        <v>470.0054694212745</v>
+        <v>448.7715750212745</v>
       </c>
       <c r="N25">
-        <v>2534.694530578725</v>
+        <v>2555.928424978725</v>
       </c>
       <c r="O25">
-        <v>633.6736326446813</v>
+        <v>638.9821062446813</v>
       </c>
       <c r="P25">
-        <v>1901.020897934044</v>
+        <v>1916.946318734044</v>
       </c>
       <c r="Q25">
-        <v>4950.320897934044</v>
+        <v>4966.246318734044</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1197949817656437</v>
+        <v>0.1197749615819867</v>
       </c>
       <c r="T25">
         <v>1.144369128816331</v>
       </c>
       <c r="U25">
-        <v>0.07083097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.05312323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.392904328751188</v>
+        <v>6.695388405242819</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1043825816234518</v>
+        <v>0.1040972069720662</v>
       </c>
       <c r="C26">
-        <v>21282.35036921833</v>
+        <v>21393.00937759982</v>
       </c>
       <c r="D26">
-        <v>23831.04636921834</v>
+        <v>23941.70537759982</v>
       </c>
       <c r="E26">
         <v>-7676.604000000002</v>
@@ -3425,37 +3425,37 @@
         <v>3004.7</v>
       </c>
       <c r="M26">
-        <v>490.4404898308951</v>
+        <v>480.0543458308951</v>
       </c>
       <c r="N26">
-        <v>2514.259510169105</v>
+        <v>2524.645654169105</v>
       </c>
       <c r="O26">
-        <v>628.5648775422762</v>
+        <v>631.1614135422761</v>
       </c>
       <c r="P26">
-        <v>1885.694632626829</v>
+        <v>1893.484240626829</v>
       </c>
       <c r="Q26">
-        <v>4934.994632626829</v>
+        <v>4942.784240626828</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.120569744243994</v>
+        <v>0.1205495144395393</v>
       </c>
       <c r="T26">
         <v>1.156351215185342</v>
       </c>
       <c r="U26">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.126533315053223</v>
+        <v>6.259083010277426</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1043046836225923</v>
+        <v>0.104008099861237</v>
       </c>
       <c r="C27">
-        <v>21025.57700607688</v>
+        <v>21141.15622515554</v>
       </c>
       <c r="D27">
-        <v>23862.77700607687</v>
+        <v>23978.35622515554</v>
       </c>
       <c r="E27">
         <v>-7388.100000000002</v>
@@ -3507,37 +3507,37 @@
         <v>3004.7</v>
       </c>
       <c r="M27">
-        <v>510.8755102405157</v>
+        <v>500.0566102405157</v>
       </c>
       <c r="N27">
-        <v>2493.824489759484</v>
+        <v>2504.643389759484</v>
       </c>
       <c r="O27">
-        <v>623.456122439871</v>
+        <v>626.1608474398711</v>
       </c>
       <c r="P27">
-        <v>1870.368367319613</v>
+        <v>1878.482542319613</v>
       </c>
       <c r="Q27">
-        <v>4919.668367319613</v>
+        <v>4927.782542319614</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1213651670551004</v>
+        <v>0.1213447220399599</v>
       </c>
       <c r="T27">
         <v>1.168652823857526</v>
       </c>
       <c r="U27">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.881471982451093</v>
+        <v>6.00871968986633</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1042267856217328</v>
+        <v>0.1039189927504077</v>
       </c>
       <c r="C28">
-        <v>20768.88825320966</v>
+        <v>20889.41545769871</v>
       </c>
       <c r="D28">
-        <v>23894.59225320966</v>
+        <v>24015.11945769871</v>
       </c>
       <c r="E28">
         <v>-7099.596000000002</v>
@@ -3589,37 +3589,37 @@
         <v>3004.7</v>
       </c>
       <c r="M28">
-        <v>531.3105306501363</v>
+        <v>520.0588746501363</v>
       </c>
       <c r="N28">
-        <v>2473.389469349863</v>
+        <v>2484.641125349864</v>
       </c>
       <c r="O28">
-        <v>618.3473673374658</v>
+        <v>621.1602813374659</v>
       </c>
       <c r="P28">
-        <v>1855.042102012397</v>
+        <v>1863.480844012398</v>
       </c>
       <c r="Q28">
-        <v>4904.342102012398</v>
+        <v>4912.780844012398</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1221820877800203</v>
+        <v>0.1221614217376892</v>
       </c>
       <c r="T28">
         <v>1.18128690843977</v>
       </c>
       <c r="U28">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.655261521587589</v>
+        <v>5.777615086409933</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1044526376208733</v>
+        <v>0.1038298856395785</v>
       </c>
       <c r="C29">
-        <v>20388.37404449719</v>
+        <v>20637.78759294367</v>
       </c>
       <c r="D29">
-        <v>23802.58204449719</v>
+        <v>24051.99559294367</v>
       </c>
       <c r="E29">
         <v>-6811.092000000001</v>
@@ -3671,45 +3671,45 @@
         <v>3004.7</v>
       </c>
       <c r="M29">
-        <v>563.429963059757</v>
+        <v>540.061139059757</v>
       </c>
       <c r="N29">
-        <v>2441.270036940243</v>
+        <v>2464.638860940243</v>
       </c>
       <c r="O29">
-        <v>610.3175092350607</v>
+        <v>616.1597152350607</v>
       </c>
       <c r="P29">
-        <v>1830.952527705182</v>
+        <v>1848.479145705182</v>
       </c>
       <c r="Q29">
-        <v>4880.252527705183</v>
+        <v>4897.779145705183</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1230213898946642</v>
+        <v>0.1230004967696029</v>
       </c>
       <c r="T29">
         <v>1.194267132325637</v>
       </c>
       <c r="U29">
-        <v>0.07233097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.05424823332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>5.332872223696991</v>
+        <v>5.563629342468824</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1043859896200138</v>
+        <v>0.1039087785287493</v>
       </c>
       <c r="C30">
-        <v>20126.94809709729</v>
+        <v>20316.628777773</v>
       </c>
       <c r="D30">
-        <v>23829.66009709729</v>
+        <v>24019.340777773</v>
       </c>
       <c r="E30">
         <v>-6522.588000000002</v>
@@ -3753,37 +3753,37 @@
         <v>3004.7</v>
       </c>
       <c r="M30">
-        <v>584.2977394693777</v>
+        <v>566.5258930693777</v>
       </c>
       <c r="N30">
-        <v>2420.402260530622</v>
+        <v>2438.174106930622</v>
       </c>
       <c r="O30">
-        <v>605.1005651326556</v>
+        <v>609.5435267326556</v>
       </c>
       <c r="P30">
-        <v>1815.301695397967</v>
+        <v>1828.630580197967</v>
       </c>
       <c r="Q30">
-        <v>4864.601695397967</v>
+        <v>4877.930580197966</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.123884005956937</v>
+        <v>0.1238628794412919</v>
       </c>
       <c r="T30">
         <v>1.207607917986111</v>
       </c>
       <c r="U30">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.142412501422098</v>
+        <v>5.303729338337655</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1043193416191542</v>
+        <v>0.10382567141792</v>
       </c>
       <c r="C31">
-        <v>19865.58382838425</v>
+        <v>20062.52641358841</v>
       </c>
       <c r="D31">
-        <v>23856.79982838425</v>
+        <v>24053.74241358841</v>
       </c>
       <c r="E31">
         <v>-6234.084000000003</v>
@@ -3835,37 +3835,37 @@
         <v>3004.7</v>
       </c>
       <c r="M31">
-        <v>605.1655158789982</v>
+        <v>586.7589606789983</v>
       </c>
       <c r="N31">
-        <v>2399.534484121002</v>
+        <v>2417.941039321001</v>
       </c>
       <c r="O31">
-        <v>599.8836210302504</v>
+        <v>604.4852598302504</v>
       </c>
       <c r="P31">
-        <v>1799.650863090751</v>
+        <v>1813.455779490751</v>
       </c>
       <c r="Q31">
-        <v>4848.950863090751</v>
+        <v>4862.755779490752</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1247709210632175</v>
+        <v>0.124749554582606</v>
       </c>
       <c r="T31">
         <v>1.221324500425753</v>
       </c>
       <c r="U31">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.965087932407544</v>
+        <v>5.120842119774288</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1042526936182947</v>
+        <v>0.1037425643070908</v>
       </c>
       <c r="C32">
-        <v>19604.28144933692</v>
+        <v>19808.52273404418</v>
       </c>
       <c r="D32">
-        <v>23884.00144933692</v>
+        <v>24088.24273404418</v>
       </c>
       <c r="E32">
         <v>-5945.580000000002</v>
@@ -3917,37 +3917,37 @@
         <v>3004.7</v>
       </c>
       <c r="M32">
-        <v>626.0332922886189</v>
+        <v>606.9920282886189</v>
       </c>
       <c r="N32">
-        <v>2378.666707711381</v>
+        <v>2397.707971711381</v>
       </c>
       <c r="O32">
-        <v>594.6666769278452</v>
+        <v>599.4269929278453</v>
       </c>
       <c r="P32">
-        <v>1784.000030783536</v>
+        <v>1798.280978783536</v>
       </c>
       <c r="Q32">
-        <v>4833.300030783535</v>
+        <v>4847.580978783536</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1256831766011061</v>
+        <v>0.1256615632993862</v>
       </c>
       <c r="T32">
         <v>1.235432985220814</v>
       </c>
       <c r="U32">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.799585001327292</v>
+        <v>4.950147382448479</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1041860456174352</v>
+        <v>0.1036594571962615</v>
       </c>
       <c r="C33">
-        <v>19343.04117189753</v>
+        <v>19554.61816438086</v>
       </c>
       <c r="D33">
-        <v>23911.26517189752</v>
+        <v>24122.84216438085</v>
       </c>
       <c r="E33">
         <v>-5657.076000000003</v>
@@ -3999,37 +3999,37 @@
         <v>3004.7</v>
       </c>
       <c r="M33">
-        <v>646.9010686982394</v>
+        <v>627.2250958982395</v>
       </c>
       <c r="N33">
-        <v>2357.798931301761</v>
+        <v>2377.47490410176</v>
       </c>
       <c r="O33">
-        <v>589.4497328254402</v>
+        <v>594.3687260254401</v>
       </c>
       <c r="P33">
-        <v>1768.34919847632</v>
+        <v>1783.10617807632</v>
       </c>
       <c r="Q33">
-        <v>4817.649198476321</v>
+        <v>4832.40617807632</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1266218743284986</v>
+        <v>0.1266000070514354</v>
       </c>
       <c r="T33">
         <v>1.249950411604137</v>
       </c>
       <c r="U33">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.644759678703831</v>
+        <v>4.790465208821109</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1041193976165757</v>
+        <v>0.1035763500854323</v>
       </c>
       <c r="C34">
-        <v>19081.8632089771</v>
+        <v>19300.81313228567</v>
       </c>
       <c r="D34">
-        <v>23938.5912089771</v>
+        <v>24157.54113228567</v>
       </c>
       <c r="E34">
         <v>-5368.572000000002</v>
@@ -4081,37 +4081,37 @@
         <v>3004.7</v>
       </c>
       <c r="M34">
-        <v>667.7688451078601</v>
+        <v>647.4581635078603</v>
       </c>
       <c r="N34">
-        <v>2336.93115489214</v>
+        <v>2357.24183649214</v>
       </c>
       <c r="O34">
-        <v>584.2327887230349</v>
+        <v>589.3104591230349</v>
       </c>
       <c r="P34">
-        <v>1752.698366169105</v>
+        <v>1767.931377369105</v>
       </c>
       <c r="Q34">
-        <v>4801.998366169105</v>
+        <v>4817.231377369105</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1275881808125792</v>
+        <v>0.1275660520903096</v>
       </c>
       <c r="T34">
         <v>1.264894821116382</v>
       </c>
       <c r="U34">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.499610938744336</v>
+        <v>4.640763171045448</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1040527496157161</v>
+        <v>0.1034932429746031</v>
       </c>
       <c r="C35">
-        <v>18820.74777446107</v>
+        <v>19047.10806791017</v>
       </c>
       <c r="D35">
-        <v>23965.97977446107</v>
+        <v>24192.34006791017</v>
       </c>
       <c r="E35">
         <v>-5080.068000000001</v>
@@ -4163,37 +4163,37 @@
         <v>3004.7</v>
       </c>
       <c r="M35">
-        <v>688.6366215174809</v>
+        <v>667.6912311174809</v>
       </c>
       <c r="N35">
-        <v>2316.063378482519</v>
+        <v>2337.008768882519</v>
       </c>
       <c r="O35">
-        <v>579.0158446206298</v>
+        <v>584.2521922206297</v>
       </c>
       <c r="P35">
-        <v>1737.047533861889</v>
+        <v>1752.756576661889</v>
       </c>
       <c r="Q35">
-        <v>4786.34753386189</v>
+        <v>4802.056576661889</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1285833322663338</v>
+        <v>0.1285609342945233</v>
       </c>
       <c r="T35">
         <v>1.280285332405111</v>
       </c>
       <c r="U35">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.363259092115719</v>
+        <v>4.500133984044071</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1043431016148566</v>
+        <v>0.1034101358637738</v>
       </c>
       <c r="C36">
-        <v>18413.38143292246</v>
+        <v>18793.50340388808</v>
       </c>
       <c r="D36">
-        <v>23847.11743292245</v>
+        <v>24227.23940388808</v>
       </c>
       <c r="E36">
         <v>-4791.564000000002</v>
@@ -4245,45 +4245,45 @@
         <v>3004.7</v>
       </c>
       <c r="M36">
-        <v>723.2371883271014</v>
+        <v>687.9242987271015</v>
       </c>
       <c r="N36">
-        <v>2281.462811672898</v>
+        <v>2316.775701272898</v>
       </c>
       <c r="O36">
-        <v>570.3657029182245</v>
+        <v>579.1939253182246</v>
       </c>
       <c r="P36">
-        <v>1711.097108754674</v>
+        <v>1737.581775954674</v>
       </c>
       <c r="Q36">
-        <v>4760.397108754674</v>
+        <v>4786.881775954675</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1296086398247477</v>
+        <v>0.1295859644443192</v>
       </c>
       <c r="T36">
         <v>1.296142222823802</v>
       </c>
       <c r="U36">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.05529823332506818</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.154515349176226</v>
+        <v>4.367777102160423</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1042869536139971</v>
+        <v>0.1035895287529446</v>
       </c>
       <c r="C37">
-        <v>18147.77087987744</v>
+        <v>18429.7921030659</v>
       </c>
       <c r="D37">
-        <v>23870.01087987744</v>
+        <v>24152.0321030659</v>
       </c>
       <c r="E37">
         <v>-4503.060000000001</v>
@@ -4327,37 +4327,37 @@
         <v>3004.7</v>
       </c>
       <c r="M37">
-        <v>744.5088703367221</v>
+        <v>718.2550063367222</v>
       </c>
       <c r="N37">
-        <v>2260.191129663278</v>
+        <v>2286.444993663278</v>
       </c>
       <c r="O37">
-        <v>565.0477824158195</v>
+        <v>571.6112484158194</v>
       </c>
       <c r="P37">
-        <v>1695.143347247458</v>
+        <v>1714.833745247458</v>
       </c>
       <c r="Q37">
-        <v>4744.443347247458</v>
+        <v>4764.133745247458</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1306654953080358</v>
+        <v>0.1306425339833396</v>
       </c>
       <c r="T37">
         <v>1.312487017563068</v>
       </c>
       <c r="U37">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.035814910628334</v>
+        <v>4.183333180404424</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1042308056131376</v>
+        <v>0.1035139216421154</v>
       </c>
       <c r="C38">
-        <v>17882.20432490042</v>
+        <v>18172.92804913109</v>
       </c>
       <c r="D38">
-        <v>23892.94832490042</v>
+        <v>24183.6720491311</v>
       </c>
       <c r="E38">
         <v>-4214.556000000002</v>
@@ -4409,37 +4409,37 @@
         <v>3004.7</v>
       </c>
       <c r="M38">
-        <v>765.7805523463426</v>
+        <v>738.7765779463427</v>
       </c>
       <c r="N38">
-        <v>2238.919447653657</v>
+        <v>2265.923422053657</v>
       </c>
       <c r="O38">
-        <v>559.7298619134143</v>
+        <v>566.4808555134143</v>
       </c>
       <c r="P38">
-        <v>1679.189585740243</v>
+        <v>1699.442566540243</v>
       </c>
       <c r="Q38">
-        <v>4728.489585740243</v>
+        <v>4748.742566540243</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1317553775251767</v>
+        <v>0.1317321213204544</v>
       </c>
       <c r="T38">
         <v>1.329342587137936</v>
       </c>
       <c r="U38">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.923708940888659</v>
+        <v>4.067129480948747</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1041746576122781</v>
+        <v>0.1034383145312861</v>
       </c>
       <c r="C39">
-        <v>17616.68189495079</v>
+        <v>17916.1470026516</v>
       </c>
       <c r="D39">
-        <v>23915.92989495079</v>
+        <v>24215.3950026516</v>
       </c>
       <c r="E39">
         <v>-3926.052000000001</v>
@@ -4491,37 +4491,37 @@
         <v>3004.7</v>
       </c>
       <c r="M39">
-        <v>787.0522343559633</v>
+        <v>759.2981495559634</v>
       </c>
       <c r="N39">
-        <v>2217.647765644037</v>
+        <v>2245.401850444036</v>
       </c>
       <c r="O39">
-        <v>554.4119414110091</v>
+        <v>561.3504626110091</v>
       </c>
       <c r="P39">
-        <v>1663.235824233027</v>
+        <v>1684.051387833027</v>
       </c>
       <c r="Q39">
-        <v>4712.535824233028</v>
+        <v>4733.351387833028</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1328798591777823</v>
+        <v>0.1328562987317633</v>
       </c>
       <c r="T39">
         <v>1.346733254159626</v>
       </c>
       <c r="U39">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.817662753297073</v>
+        <v>3.957207062544726</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1041185096114186</v>
+        <v>0.1033627074204569</v>
       </c>
       <c r="C40">
-        <v>17351.20371747687</v>
+        <v>17659.44929071178</v>
       </c>
       <c r="D40">
-        <v>23938.95571747687</v>
+        <v>24247.20129071179</v>
       </c>
       <c r="E40">
         <v>-3637.548000000003</v>
@@ -4573,37 +4573,37 @@
         <v>3004.7</v>
       </c>
       <c r="M40">
-        <v>808.3239163655838</v>
+        <v>779.8197211655839</v>
       </c>
       <c r="N40">
-        <v>2196.376083634416</v>
+        <v>2224.880278834416</v>
       </c>
       <c r="O40">
-        <v>549.094020908604</v>
+        <v>556.220069708604</v>
       </c>
       <c r="P40">
-        <v>1647.282062725812</v>
+        <v>1668.660209125812</v>
       </c>
       <c r="Q40">
-        <v>4696.582062725813</v>
+        <v>4717.960209125812</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1340406144320849</v>
+        <v>0.1340167399305338</v>
       </c>
       <c r="T40">
         <v>1.364684910440079</v>
       </c>
       <c r="U40">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.717197943999782</v>
+        <v>3.853070034583023</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.104062361610559</v>
+        <v>0.1032871003096276</v>
       </c>
       <c r="C41">
-        <v>17085.76992041826</v>
+        <v>17402.83524211674</v>
       </c>
       <c r="D41">
-        <v>23962.02592041827</v>
+        <v>24279.09124211674</v>
       </c>
       <c r="E41">
         <v>-3349.044000000002</v>
@@ -4655,37 +4655,37 @@
         <v>3004.7</v>
       </c>
       <c r="M41">
-        <v>829.5955983752045</v>
+        <v>800.3412927752047</v>
       </c>
       <c r="N41">
-        <v>2175.104401624795</v>
+        <v>2204.358707224795</v>
       </c>
       <c r="O41">
-        <v>543.7761004061988</v>
+        <v>551.0896768061988</v>
       </c>
       <c r="P41">
-        <v>1631.328301218596</v>
+        <v>1653.269030418596</v>
       </c>
       <c r="Q41">
-        <v>4680.628301218597</v>
+        <v>4702.569030418596</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1352394272357089</v>
+        <v>0.135215228381723</v>
       </c>
       <c r="T41">
         <v>1.383225145614974</v>
       </c>
       <c r="U41">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.621885176204915</v>
+        <v>3.754273367029612</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1040062136096995</v>
+        <v>0.1032114931987984</v>
       </c>
       <c r="C42">
-        <v>16820.38063220827</v>
+        <v>17146.30518740362</v>
       </c>
       <c r="D42">
-        <v>23985.14063220827</v>
+        <v>24311.06518740362</v>
       </c>
       <c r="E42">
         <v>-3060.540000000001</v>
@@ -4737,37 +4737,37 @@
         <v>3004.7</v>
       </c>
       <c r="M42">
-        <v>850.8672803848252</v>
+        <v>820.8628643848253</v>
       </c>
       <c r="N42">
-        <v>2153.832719615174</v>
+        <v>2183.837135615175</v>
       </c>
       <c r="O42">
-        <v>538.4581799037936</v>
+        <v>545.9592839037937</v>
       </c>
       <c r="P42">
-        <v>1615.374539711381</v>
+        <v>1637.877851711381</v>
       </c>
       <c r="Q42">
-        <v>4664.674539711381</v>
+        <v>4687.177851711382</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1364782004661204</v>
+        <v>0.1364536664479519</v>
       </c>
       <c r="T42">
         <v>1.402383388629032</v>
       </c>
       <c r="U42">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.531338046799792</v>
+        <v>3.660416532853871</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.10395006560884</v>
+        <v>0.1031358860879692</v>
       </c>
       <c r="C43">
-        <v>16555.0359817762</v>
+        <v>16889.85945885303</v>
       </c>
       <c r="D43">
-        <v>24008.2999817762</v>
+        <v>24343.12345885303</v>
       </c>
       <c r="E43">
         <v>-2772.036000000002</v>
@@ -4819,37 +4819,37 @@
         <v>3004.7</v>
       </c>
       <c r="M43">
-        <v>872.1389623944458</v>
+        <v>841.3844359944459</v>
       </c>
       <c r="N43">
-        <v>2132.561037605554</v>
+        <v>2163.315564005554</v>
       </c>
       <c r="O43">
-        <v>533.1402594013884</v>
+        <v>540.8288910013885</v>
       </c>
       <c r="P43">
-        <v>1599.420778204165</v>
+        <v>1622.486673004165</v>
       </c>
       <c r="Q43">
-        <v>4648.720778204166</v>
+        <v>4671.786673004166</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1377589660094272</v>
+        <v>0.1377340854655783</v>
       </c>
       <c r="T43">
         <v>1.422191063609668</v>
       </c>
       <c r="U43">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.445207850536383</v>
+        <v>3.571138080833046</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1038939176079805</v>
+        <v>0.1030602789771399</v>
       </c>
       <c r="C44">
-        <v>16289.73609854981</v>
+        <v>16633.49839050061</v>
       </c>
       <c r="D44">
-        <v>24031.50409854981</v>
+        <v>24375.2663905006</v>
       </c>
       <c r="E44">
         <v>-2483.532000000003</v>
@@ -4901,37 +4901,37 @@
         <v>3004.7</v>
       </c>
       <c r="M44">
-        <v>893.4106444040664</v>
+        <v>861.9060076040664</v>
       </c>
       <c r="N44">
-        <v>2111.289355595934</v>
+        <v>2142.793992395933</v>
       </c>
       <c r="O44">
-        <v>527.8223388989834</v>
+        <v>535.6984980989834</v>
       </c>
       <c r="P44">
-        <v>1583.46701669695</v>
+        <v>1607.09549429695</v>
       </c>
       <c r="Q44">
-        <v>4632.76701669695</v>
+        <v>4656.39549429695</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1390838958818135</v>
+        <v>0.1390586568631229</v>
       </c>
       <c r="T44">
         <v>1.442681761865498</v>
       </c>
       <c r="U44">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.363179092190279</v>
+        <v>3.486110983670354</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.103837769607121</v>
+        <v>0.1029846718663107</v>
       </c>
       <c r="C45">
-        <v>16024.48111245773</v>
+        <v>16377.22231814854</v>
       </c>
       <c r="D45">
-        <v>24054.75311245773</v>
+        <v>24407.49431814855</v>
       </c>
       <c r="E45">
         <v>-2195.028000000002</v>
@@ -4983,37 +4983,37 @@
         <v>3004.7</v>
       </c>
       <c r="M45">
-        <v>914.6823264136871</v>
+        <v>882.4275792136872</v>
       </c>
       <c r="N45">
-        <v>2090.017673586313</v>
+        <v>2122.272420786313</v>
       </c>
       <c r="O45">
-        <v>522.5044183965782</v>
+        <v>530.5681051965781</v>
       </c>
       <c r="P45">
-        <v>1567.513255189735</v>
+        <v>1591.704315589735</v>
       </c>
       <c r="Q45">
-        <v>4616.813255189734</v>
+        <v>4641.004315589735</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.140455314521652</v>
+        <v>0.140429704450055</v>
       </c>
       <c r="T45">
         <v>1.463891431989954</v>
       </c>
       <c r="U45">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.284965624930039</v>
+        <v>3.405038635212903</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1037816216062615</v>
+        <v>0.1029090647554815</v>
       </c>
       <c r="C46">
-        <v>15759.27115393187</v>
+        <v>16121.03157937734</v>
       </c>
       <c r="D46">
-        <v>24078.04715393187</v>
+        <v>24439.80757937734</v>
       </c>
       <c r="E46">
         <v>-1906.524000000001</v>
@@ -5065,37 +5065,37 @@
         <v>3004.7</v>
       </c>
       <c r="M46">
-        <v>935.9540084233078</v>
+        <v>902.9491508233078</v>
       </c>
       <c r="N46">
-        <v>2068.745991576692</v>
+        <v>2101.750849176692</v>
       </c>
       <c r="O46">
-        <v>517.186497894173</v>
+        <v>525.437712294173</v>
       </c>
       <c r="P46">
-        <v>1551.559493682519</v>
+        <v>1576.313136882519</v>
       </c>
       <c r="Q46">
-        <v>4600.859493682519</v>
+        <v>4625.613136882519</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1418757123986276</v>
+        <v>0.1418497180222347</v>
       </c>
       <c r="T46">
         <v>1.485858590333141</v>
       </c>
       <c r="U46">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.210307315272539</v>
+        <v>3.327651393503519</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1037254736054019</v>
+        <v>0.1028334576446522</v>
       </c>
       <c r="C47">
-        <v>15494.10635390983</v>
+        <v>15864.92651355756</v>
       </c>
       <c r="D47">
-        <v>24101.38635390983</v>
+        <v>24472.20651355756</v>
       </c>
       <c r="E47">
         <v>-1618.020000000002</v>
@@ -5147,37 +5147,37 @@
         <v>3004.7</v>
       </c>
       <c r="M47">
-        <v>957.2256904329283</v>
+        <v>923.4707224329284</v>
       </c>
       <c r="N47">
-        <v>2047.474309567071</v>
+        <v>2081.229277567071</v>
       </c>
       <c r="O47">
-        <v>511.8685773917679</v>
+        <v>520.3073193917678</v>
       </c>
       <c r="P47">
-        <v>1535.605732175304</v>
+        <v>1560.921958175303</v>
       </c>
       <c r="Q47">
-        <v>4584.905732175304</v>
+        <v>4610.221958175303</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1433477611074932</v>
+        <v>0.1433213684515846</v>
       </c>
       <c r="T47">
         <v>1.508624554434261</v>
       </c>
       <c r="U47">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.138967152710927</v>
+        <v>3.253703584758997</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1036693256045424</v>
+        <v>0.102757850533823</v>
       </c>
       <c r="C48">
-        <v>15228.98684383741</v>
+        <v>15608.90746186171</v>
       </c>
       <c r="D48">
-        <v>24124.77084383741</v>
+        <v>24504.69146186171</v>
       </c>
       <c r="E48">
         <v>-1329.516000000001</v>
@@ -5229,37 +5229,37 @@
         <v>3004.7</v>
       </c>
       <c r="M48">
-        <v>978.497372442549</v>
+        <v>943.9922940425491</v>
       </c>
       <c r="N48">
-        <v>2026.202627557451</v>
+        <v>2060.707705957451</v>
       </c>
       <c r="O48">
-        <v>506.5506568893627</v>
+        <v>515.1769264893627</v>
       </c>
       <c r="P48">
-        <v>1519.651970668088</v>
+        <v>1545.530779468088</v>
       </c>
       <c r="Q48">
-        <v>4568.951970668089</v>
+        <v>4594.830779468088</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1448743301389093</v>
+        <v>0.1448475244523919</v>
       </c>
       <c r="T48">
         <v>1.532233702390979</v>
       </c>
       <c r="U48">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.070728736347645</v>
+        <v>3.182970898133801</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1036131776036829</v>
+        <v>0.1026822434229937</v>
       </c>
       <c r="C49">
-        <v>14963.91275567102</v>
+        <v>15352.97476727623</v>
       </c>
       <c r="D49">
-        <v>24148.20075567102</v>
+        <v>24537.26276727623</v>
       </c>
       <c r="E49">
         <v>-1041.012000000001</v>
@@ -5311,37 +5311,37 @@
         <v>3004.7</v>
       </c>
       <c r="M49">
-        <v>999.7690544521697</v>
+        <v>964.5138656521698</v>
       </c>
       <c r="N49">
-        <v>2004.93094554783</v>
+        <v>2040.18613434783</v>
       </c>
       <c r="O49">
-        <v>501.2327363869575</v>
+        <v>510.0465335869575</v>
       </c>
       <c r="P49">
-        <v>1503.698209160872</v>
+        <v>1530.139600760872</v>
       </c>
       <c r="Q49">
-        <v>4552.998209160873</v>
+        <v>4579.439600760872</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1464585055488695</v>
+        <v>0.1464312712456824</v>
       </c>
       <c r="T49">
         <v>1.556733761591346</v>
       </c>
       <c r="U49">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.005394082382802</v>
+        <v>3.115248113067124</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1044930296028234</v>
+        <v>0.1026066363121645</v>
       </c>
       <c r="C50">
-        <v>14313.40933505327</v>
+        <v>15097.12877461356</v>
       </c>
       <c r="D50">
-        <v>23786.20133505327</v>
+        <v>24569.92077461356</v>
       </c>
       <c r="E50">
         <v>-752.5080000000016</v>
@@ -5393,45 +5393,45 @@
         <v>3004.7</v>
       </c>
       <c r="M50">
-        <v>1057.04603566179</v>
+        <v>985.0354372617903</v>
       </c>
       <c r="N50">
-        <v>1947.65396433821</v>
+        <v>2019.664562738209</v>
       </c>
       <c r="O50">
-        <v>486.9134910845524</v>
+        <v>504.9161406845524</v>
       </c>
       <c r="P50">
-        <v>1460.740473253657</v>
+        <v>1514.748422053657</v>
       </c>
       <c r="Q50">
-        <v>4510.040473253657</v>
+        <v>4564.048422053657</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1481036107822897</v>
+        <v>0.1480759313771765</v>
       </c>
       <c r="T50">
         <v>1.582176130760959</v>
       </c>
       <c r="U50">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.05724823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.842544126395434</v>
+        <v>3.050347110711559</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1044563816019639</v>
+        <v>0.1034497792013352</v>
       </c>
       <c r="C51">
-        <v>14039.76674830728</v>
+        <v>14449.2833465006</v>
       </c>
       <c r="D51">
-        <v>23801.06274830727</v>
+        <v>24210.5793465006</v>
       </c>
       <c r="E51">
         <v>-464.0040000000026</v>
@@ -5475,37 +5475,37 @@
         <v>3004.7</v>
       </c>
       <c r="M51">
-        <v>1079.067828071411</v>
+        <v>1040.898748871411</v>
       </c>
       <c r="N51">
-        <v>1925.632171928589</v>
+        <v>1963.801251128589</v>
       </c>
       <c r="O51">
-        <v>481.4080429821473</v>
+        <v>490.9503127821473</v>
       </c>
       <c r="P51">
-        <v>1444.224128946442</v>
+        <v>1472.850938346442</v>
       </c>
       <c r="Q51">
-        <v>4493.524128946442</v>
+        <v>4522.150938346442</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1498132299464322</v>
+        <v>0.1497850879844154</v>
       </c>
       <c r="T51">
         <v>1.608616239898007</v>
       </c>
       <c r="U51">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.784533021775119</v>
+        <v>2.886640034160701</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1044197336011043</v>
+        <v>0.103392922090506</v>
       </c>
       <c r="C52">
-        <v>13766.14274373668</v>
+        <v>14184.68060976661</v>
       </c>
       <c r="D52">
-        <v>23815.94274373668</v>
+        <v>24234.48060976661</v>
       </c>
       <c r="E52">
         <v>-175.5000000000018</v>
@@ -5557,37 +5557,37 @@
         <v>3004.7</v>
       </c>
       <c r="M52">
-        <v>1101.089620481031</v>
+        <v>1062.141580481031</v>
       </c>
       <c r="N52">
-        <v>1903.610379518969</v>
+        <v>1942.558419518968</v>
       </c>
       <c r="O52">
-        <v>475.9025948797421</v>
+        <v>485.6396048797421</v>
       </c>
       <c r="P52">
-        <v>1427.707784639226</v>
+        <v>1456.918814639226</v>
       </c>
       <c r="Q52">
-        <v>4477.007784639227</v>
+        <v>4506.218814639226</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1515912338771405</v>
+        <v>0.1515626108559439</v>
       </c>
       <c r="T52">
         <v>1.636113953400537</v>
       </c>
       <c r="U52">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.728842361339617</v>
+        <v>2.828907233477486</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1043830856002448</v>
+        <v>0.1033360649796768</v>
       </c>
       <c r="C53">
-        <v>13492.53735621501</v>
+        <v>13920.12511146559</v>
       </c>
       <c r="D53">
-        <v>23830.84135621501</v>
+        <v>24258.42911146559</v>
       </c>
       <c r="E53">
         <v>113.003999999999</v>
@@ -5639,37 +5639,37 @@
         <v>3004.7</v>
       </c>
       <c r="M53">
-        <v>1123.111412890652</v>
+        <v>1083.384412090652</v>
       </c>
       <c r="N53">
-        <v>1881.588587109348</v>
+        <v>1921.315587909348</v>
       </c>
       <c r="O53">
-        <v>470.397146777337</v>
+        <v>480.3288969773369</v>
       </c>
       <c r="P53">
-        <v>1411.191440332011</v>
+        <v>1440.986690932011</v>
       </c>
       <c r="Q53">
-        <v>4460.491440332011</v>
+        <v>4490.286690932011</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1534418093968573</v>
+        <v>0.1534126856814123</v>
       </c>
       <c r="T53">
         <v>1.664734022556232</v>
       </c>
       <c r="U53">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.675335648372173</v>
+        <v>2.773438464193614</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1043464375993853</v>
+        <v>0.1032792078688475</v>
       </c>
       <c r="C54">
-        <v>13218.9506207031</v>
+        <v>13655.61699177906</v>
       </c>
       <c r="D54">
-        <v>23845.7586207031</v>
+        <v>24282.42499177906</v>
       </c>
       <c r="E54">
         <v>401.507999999998</v>
@@ -5721,37 +5721,37 @@
         <v>3004.7</v>
       </c>
       <c r="M54">
-        <v>1145.133205300272</v>
+        <v>1104.627243700273</v>
       </c>
       <c r="N54">
-        <v>1859.566794699727</v>
+        <v>1900.072756299727</v>
       </c>
       <c r="O54">
-        <v>464.8916986749318</v>
+        <v>475.0181890749318</v>
       </c>
       <c r="P54">
-        <v>1394.675096024795</v>
+        <v>1425.054567224795</v>
       </c>
       <c r="Q54">
-        <v>4443.975096024796</v>
+        <v>4474.354567224796</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1553694922298955</v>
+        <v>0.1553398469579419</v>
       </c>
       <c r="T54">
         <v>1.694546594593413</v>
       </c>
       <c r="U54">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.623886885903477</v>
+        <v>2.720103109112968</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1043097895985258</v>
+        <v>0.1032223507580183</v>
       </c>
       <c r="C55">
-        <v>12945.38257224939</v>
+        <v>13391.15639144373</v>
       </c>
       <c r="D55">
-        <v>23860.69457224939</v>
+        <v>24306.46839144374</v>
       </c>
       <c r="E55">
         <v>690.0119999999988</v>
@@ -5803,37 +5803,37 @@
         <v>3004.7</v>
       </c>
       <c r="M55">
-        <v>1167.154997709893</v>
+        <v>1125.870075309893</v>
       </c>
       <c r="N55">
-        <v>1837.545002290107</v>
+        <v>1878.829924690107</v>
       </c>
       <c r="O55">
-        <v>459.3862505725266</v>
+        <v>469.7074811725266</v>
       </c>
       <c r="P55">
-        <v>1378.15875171758</v>
+        <v>1409.12244351758</v>
       </c>
       <c r="Q55">
-        <v>4427.458751717581</v>
+        <v>4458.42244351758</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1573792041196588</v>
+        <v>0.1573490150973025</v>
       </c>
       <c r="T55">
         <v>1.725627786717284</v>
       </c>
       <c r="U55">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.574379586169449</v>
+        <v>2.668780408941025</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1042731415976663</v>
+        <v>0.1031654936471891</v>
       </c>
       <c r="C56">
-        <v>12671.83324599019</v>
+        <v>13126.74345175429</v>
       </c>
       <c r="D56">
-        <v>23875.64924599019</v>
+        <v>24330.5594517543</v>
       </c>
       <c r="E56">
         <v>978.5159999999996</v>
@@ -5885,37 +5885,37 @@
         <v>3004.7</v>
       </c>
       <c r="M56">
-        <v>1189.176790119514</v>
+        <v>1147.112906919514</v>
       </c>
       <c r="N56">
-        <v>1815.523209880486</v>
+        <v>1857.587093080486</v>
       </c>
       <c r="O56">
-        <v>453.8808024701215</v>
+        <v>464.3967732701215</v>
       </c>
       <c r="P56">
-        <v>1361.642407410364</v>
+        <v>1393.190319810364</v>
       </c>
       <c r="Q56">
-        <v>4410.942407410364</v>
+        <v>4442.490319810365</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1594762947872379</v>
+        <v>0.1594455383731571</v>
       </c>
       <c r="T56">
         <v>1.758060335020453</v>
       </c>
       <c r="U56">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.526705890129274</v>
+        <v>2.619358549516191</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1053502435968067</v>
+        <v>0.1031086365363598</v>
       </c>
       <c r="C57">
-        <v>11951.48366517696</v>
+        <v>12862.37831456615</v>
       </c>
       <c r="D57">
-        <v>23443.80366517696</v>
+        <v>24354.69831456615</v>
       </c>
       <c r="E57">
         <v>1267.02</v>
@@ -5967,45 +5967,45 @@
         <v>3004.7</v>
       </c>
       <c r="M57">
-        <v>1254.041426529135</v>
+        <v>1168.355738529135</v>
       </c>
       <c r="N57">
-        <v>1750.658573470865</v>
+        <v>1836.344261470865</v>
       </c>
       <c r="O57">
-        <v>437.6646433677163</v>
+        <v>459.0860653677163</v>
       </c>
       <c r="P57">
-        <v>1312.993930103149</v>
+        <v>1377.258196103149</v>
       </c>
       <c r="Q57">
-        <v>4362.293930103149</v>
+        <v>4426.558196103149</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1616665894844872</v>
+        <v>0.1616352404612719</v>
       </c>
       <c r="T57">
         <v>1.791934329914874</v>
       </c>
       <c r="U57">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.05927323332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.396013350465016</v>
+        <v>2.571733848615897</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1053338455959472</v>
+        <v>0.1030517794255306</v>
       </c>
       <c r="C58">
-        <v>11669.43702583968</v>
+        <v>12598.06112229823</v>
       </c>
       <c r="D58">
-        <v>23450.26102583969</v>
+        <v>24378.88512229823</v>
       </c>
       <c r="E58">
         <v>1555.523999999999</v>
@@ -6049,45 +6049,45 @@
         <v>3004.7</v>
       </c>
       <c r="M58">
-        <v>1276.842179738755</v>
+        <v>1189.598570138755</v>
       </c>
       <c r="N58">
-        <v>1727.857820261245</v>
+        <v>1815.101429861244</v>
       </c>
       <c r="O58">
-        <v>431.9644550653111</v>
+        <v>453.7753574653111</v>
       </c>
       <c r="P58">
-        <v>1295.893365195933</v>
+        <v>1361.326072395933</v>
       </c>
       <c r="Q58">
-        <v>4345.193365195933</v>
+        <v>4410.626072395933</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1639564430316114</v>
+        <v>0.1639244744624828</v>
       </c>
       <c r="T58">
         <v>1.82734805184995</v>
       </c>
       <c r="U58">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.05927323332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.353227397778141</v>
+        <v>2.525810029890613</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1053174475950877</v>
+        <v>0.1044911723147013</v>
       </c>
       <c r="C59">
-        <v>11387.39394471297</v>
+        <v>11711.66833413787</v>
       </c>
       <c r="D59">
-        <v>23456.72194471297</v>
+        <v>23780.99633413788</v>
       </c>
       <c r="E59">
         <v>1844.028</v>
@@ -6131,37 +6131,37 @@
         <v>3004.7</v>
       </c>
       <c r="M59">
-        <v>1299.642932948376</v>
+        <v>1268.397949748376</v>
       </c>
       <c r="N59">
-        <v>1705.057067051624</v>
+        <v>1736.302050251624</v>
       </c>
       <c r="O59">
-        <v>426.2642667629059</v>
+        <v>434.0755125629059</v>
       </c>
       <c r="P59">
-        <v>1278.792800288718</v>
+        <v>1302.226537688718</v>
       </c>
       <c r="Q59">
-        <v>4328.092800288718</v>
+        <v>4351.526537688718</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.166352801394881</v>
+        <v>0.16632018446375</v>
       </c>
       <c r="T59">
         <v>1.864408923642473</v>
       </c>
       <c r="U59">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.05927323332506818</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.31194270658905</v>
+        <v>2.368893769180303</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1053010495942282</v>
+        <v>0.1044605652038721</v>
       </c>
       <c r="C60">
-        <v>11105.35442473869</v>
+        <v>11435.57245853795</v>
       </c>
       <c r="D60">
-        <v>23463.18642473869</v>
+        <v>23793.40445853795</v>
       </c>
       <c r="E60">
         <v>2132.531999999997</v>
@@ -6213,37 +6213,37 @@
         <v>3004.7</v>
       </c>
       <c r="M60">
-        <v>1322.443686157996</v>
+        <v>1290.650545357996</v>
       </c>
       <c r="N60">
-        <v>1682.256313842003</v>
+        <v>1714.049454642003</v>
       </c>
       <c r="O60">
-        <v>420.5640784605009</v>
+        <v>428.5123636605009</v>
       </c>
       <c r="P60">
-        <v>1261.692235381503</v>
+        <v>1285.537090981503</v>
       </c>
       <c r="Q60">
-        <v>4310.992235381503</v>
+        <v>4334.837090981503</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1688632720611634</v>
+        <v>0.168829975893649</v>
       </c>
       <c r="T60">
         <v>1.903234598853686</v>
       </c>
       <c r="U60">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.05927323332506818</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.272081625440963</v>
+        <v>2.328050773159954</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1073644015933687</v>
+        <v>0.1044299580930429</v>
       </c>
       <c r="C61">
-        <v>10030.47369788514</v>
+        <v>11159.48953798187</v>
       </c>
       <c r="D61">
-        <v>22676.80969788514</v>
+        <v>23805.82553798187</v>
       </c>
       <c r="E61">
         <v>2421.035999999998</v>
@@ -6295,45 +6295,45 @@
         <v>3004.7</v>
       </c>
       <c r="M61">
-        <v>1425.246598567617</v>
+        <v>1312.903140967617</v>
       </c>
       <c r="N61">
-        <v>1579.453401432383</v>
+        <v>1691.796859032383</v>
       </c>
       <c r="O61">
-        <v>394.8633503580957</v>
+        <v>422.9492147580956</v>
       </c>
       <c r="P61">
-        <v>1184.590051074287</v>
+        <v>1268.847644274287</v>
       </c>
       <c r="Q61">
-        <v>4233.890051074287</v>
+        <v>4318.147644274287</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1714962047111669</v>
+        <v>0.171462196173787</v>
       </c>
       <c r="T61">
         <v>1.943954209441056</v>
       </c>
       <c r="U61">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.06279823332506819</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.108196576662413</v>
+        <v>2.288592285479276</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1073832535925092</v>
+        <v>0.1043993509822136</v>
       </c>
       <c r="C62">
-        <v>9735.027823723012</v>
+        <v>10883.41959276933</v>
       </c>
       <c r="D62">
-        <v>22669.86782372301</v>
+        <v>23818.25959276934</v>
       </c>
       <c r="E62">
         <v>2709.539999999999</v>
@@ -6377,45 +6377,45 @@
         <v>3004.7</v>
       </c>
       <c r="M62">
-        <v>1449.403320577238</v>
+        <v>1335.155736577238</v>
       </c>
       <c r="N62">
-        <v>1555.296679422762</v>
+        <v>1669.544263422762</v>
       </c>
       <c r="O62">
-        <v>388.8241698556905</v>
+        <v>417.3860658556905</v>
       </c>
       <c r="P62">
-        <v>1166.472509567071</v>
+        <v>1252.158197567072</v>
       </c>
       <c r="Q62">
-        <v>4215.772509567072</v>
+        <v>4301.458197567072</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1742607839936706</v>
+        <v>0.1742260274679318</v>
       </c>
       <c r="T62">
         <v>1.986709800557795</v>
       </c>
       <c r="U62">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.06279823332506819</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.073059967051373</v>
+        <v>2.250449080721289</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1074021055916496</v>
+        <v>0.1056497438713844</v>
       </c>
       <c r="C63">
-        <v>9439.586198383375</v>
+        <v>10097.29972174366</v>
       </c>
       <c r="D63">
-        <v>22662.93019838338</v>
+        <v>23320.64372174366</v>
       </c>
       <c r="E63">
         <v>2998.043999999996</v>
@@ -6459,37 +6459,37 @@
         <v>3004.7</v>
       </c>
       <c r="M63">
-        <v>1473.560042586858</v>
+        <v>1406.684815386858</v>
       </c>
       <c r="N63">
-        <v>1531.139957413141</v>
+        <v>1598.015184613141</v>
       </c>
       <c r="O63">
-        <v>382.7849893532854</v>
+        <v>399.5037961532854</v>
       </c>
       <c r="P63">
-        <v>1148.354968059856</v>
+        <v>1198.511388459856</v>
       </c>
       <c r="Q63">
-        <v>4197.654968059856</v>
+        <v>4247.811388459856</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1771671365727129</v>
+        <v>0.177131593700238</v>
       </c>
       <c r="T63">
         <v>2.031657986090777</v>
       </c>
       <c r="U63">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.06279823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.03907537742758</v>
+        <v>2.136015095303111</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1074209575907901</v>
+        <v>0.1056401367605552</v>
       </c>
       <c r="C64">
-        <v>9144.148817966641</v>
+        <v>9812.539764136818</v>
       </c>
       <c r="D64">
-        <v>22655.99681796664</v>
+        <v>23324.38776413682</v>
       </c>
       <c r="E64">
         <v>3286.547999999997</v>
@@ -6541,37 +6541,37 @@
         <v>3004.7</v>
       </c>
       <c r="M64">
-        <v>1497.716764596479</v>
+        <v>1429.745222196479</v>
       </c>
       <c r="N64">
-        <v>1506.983235403521</v>
+        <v>1574.954777803521</v>
       </c>
       <c r="O64">
-        <v>376.7458088508802</v>
+        <v>393.7386944508802</v>
       </c>
       <c r="P64">
-        <v>1130.23742655264</v>
+        <v>1181.21608335264</v>
       </c>
       <c r="Q64">
-        <v>4179.537426552641</v>
+        <v>4230.516083352641</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.180226455076968</v>
+        <v>0.1801900844710866</v>
       </c>
       <c r="T64">
         <v>2.078971865599179</v>
       </c>
       <c r="U64">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.06279823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.006187064888426</v>
+        <v>2.101563238927254</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1118340595899306</v>
+        <v>0.1056305296497259</v>
       </c>
       <c r="C65">
-        <v>7341.528837959027</v>
+        <v>9527.781008907106</v>
       </c>
       <c r="D65">
-        <v>21141.88083795903</v>
+        <v>23328.13300890711</v>
       </c>
       <c r="E65">
         <v>3575.051999999998</v>
@@ -6623,45 +6623,45 @@
         <v>3004.7</v>
       </c>
       <c r="M65">
-        <v>1690.9079802061</v>
+        <v>1452.8056290061</v>
       </c>
       <c r="N65">
-        <v>1313.7920197939</v>
+        <v>1551.8943709939</v>
       </c>
       <c r="O65">
-        <v>328.448004948475</v>
+        <v>387.973592748475</v>
       </c>
       <c r="P65">
-        <v>985.3440148454251</v>
+        <v>1163.920778245425</v>
       </c>
       <c r="Q65">
-        <v>4034.644014845425</v>
+        <v>4213.220778245425</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1834511421490206</v>
+        <v>0.1834138990673864</v>
       </c>
       <c r="T65">
         <v>2.128843252108035</v>
       </c>
       <c r="U65">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.06977323332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.776974285515978</v>
+        <v>2.068205092277616</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1141786615890711</v>
+        <v>0.1056209225388967</v>
       </c>
       <c r="C66">
-        <v>6328.101376073209</v>
+        <v>9243.023456633819</v>
       </c>
       <c r="D66">
-        <v>20416.95737607321</v>
+        <v>23331.87945663382</v>
       </c>
       <c r="E66">
         <v>3863.555999999999</v>
@@ -6705,45 +6705,45 @@
         <v>3004.7</v>
       </c>
       <c r="M66">
-        <v>1804.52979261572</v>
+        <v>1475.866035815721</v>
       </c>
       <c r="N66">
-        <v>1200.17020738428</v>
+        <v>1528.833964184279</v>
       </c>
       <c r="O66">
-        <v>300.0425518460699</v>
+        <v>382.2084910460698</v>
       </c>
       <c r="P66">
-        <v>900.1276555382096</v>
+        <v>1146.625473138209</v>
       </c>
       <c r="Q66">
-        <v>3949.42765553821</v>
+        <v>4195.92547313821</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.186854978502854</v>
+        <v>0.1868168144745918</v>
       </c>
       <c r="T66">
         <v>2.181485271200716</v>
       </c>
       <c r="U66">
-        <v>0.09773097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.07329823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.665087499411465</v>
+        <v>2.035889387710777</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1143025135882116</v>
+        <v>0.1056113154280675</v>
       </c>
       <c r="C67">
-        <v>6002.683679700051</v>
+        <v>8958.267107896638</v>
       </c>
       <c r="D67">
-        <v>20380.04367970005</v>
+        <v>23335.62710789664</v>
       </c>
       <c r="E67">
         <v>4152.059999999999</v>
@@ -6787,45 +6787,45 @@
         <v>3004.7</v>
       </c>
       <c r="M67">
-        <v>1832.725570625341</v>
+        <v>1498.926442625341</v>
       </c>
       <c r="N67">
-        <v>1171.974429374659</v>
+        <v>1505.773557374659</v>
       </c>
       <c r="O67">
-        <v>292.9936073436647</v>
+        <v>376.4433893436646</v>
       </c>
       <c r="P67">
-        <v>878.9808220309942</v>
+        <v>1129.330168030994</v>
       </c>
       <c r="Q67">
-        <v>3928.280822030994</v>
+        <v>4178.630168030994</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1904533197911921</v>
+        <v>0.1904141821907804</v>
       </c>
       <c r="T67">
         <v>2.237135405670122</v>
       </c>
       <c r="U67">
-        <v>0.09773097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.07329823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.639470768651289</v>
+        <v>2.004568012515227</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.114426365587352</v>
+        <v>0.1094627083172382</v>
       </c>
       <c r="C68">
-        <v>5677.39922177112</v>
+        <v>7258.031331424943</v>
       </c>
       <c r="D68">
-        <v>20343.26322177113</v>
+        <v>21923.89533142494</v>
       </c>
       <c r="E68">
         <v>4440.564</v>
@@ -6869,45 +6869,45 @@
         <v>3004.7</v>
       </c>
       <c r="M68">
-        <v>1860.921348634962</v>
+        <v>1670.508708634962</v>
       </c>
       <c r="N68">
-        <v>1143.778651365038</v>
+        <v>1334.191291365038</v>
       </c>
       <c r="O68">
-        <v>285.9446628412596</v>
+        <v>333.5478228412595</v>
       </c>
       <c r="P68">
-        <v>857.8339885237788</v>
+        <v>1000.643468523778</v>
       </c>
       <c r="Q68">
-        <v>3907.133988523779</v>
+        <v>4049.943468523778</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1942633282141384</v>
+        <v>0.1942231597726271</v>
       </c>
       <c r="T68">
         <v>2.296059077461258</v>
       </c>
       <c r="U68">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.07329823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.614630302459603</v>
+        <v>1.798673652204578</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1145502175864925</v>
+        <v>0.109511601206409</v>
       </c>
       <c r="C69">
-        <v>5352.24728220806</v>
+        <v>6952.70272547668</v>
       </c>
       <c r="D69">
-        <v>20306.61528220806</v>
+        <v>21907.07072547668</v>
       </c>
       <c r="E69">
         <v>4729.068000000001</v>
@@ -6951,45 +6951,45 @@
         <v>3004.7</v>
       </c>
       <c r="M69">
-        <v>1889.117126644582</v>
+        <v>1695.819446644583</v>
       </c>
       <c r="N69">
-        <v>1115.582873355417</v>
+        <v>1308.880553355417</v>
       </c>
       <c r="O69">
-        <v>278.8957183388544</v>
+        <v>327.2201383388543</v>
       </c>
       <c r="P69">
-        <v>836.6871550165631</v>
+        <v>981.6604150165629</v>
       </c>
       <c r="Q69">
-        <v>3885.987155016564</v>
+        <v>4030.960415016563</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1983042462384753</v>
+        <v>0.1982629844806464</v>
       </c>
       <c r="T69">
         <v>2.358553880876099</v>
       </c>
       <c r="U69">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.07329823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.5905313427214</v>
+        <v>1.771827776798539</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.114674069585633</v>
+        <v>0.1115494940955798</v>
       </c>
       <c r="C70">
-        <v>5027.227146112</v>
+        <v>5985.193293296306</v>
       </c>
       <c r="D70">
-        <v>20270.099146112</v>
+        <v>21228.06529329631</v>
       </c>
       <c r="E70">
         <v>5017.571999999998</v>
@@ -7033,37 +7033,37 @@
         <v>3004.7</v>
       </c>
       <c r="M70">
-        <v>1917.312904654203</v>
+        <v>1797.641445454203</v>
       </c>
       <c r="N70">
-        <v>1087.387095345797</v>
+        <v>1207.058554545797</v>
       </c>
       <c r="O70">
-        <v>271.8467738364493</v>
+        <v>301.7646386364493</v>
       </c>
       <c r="P70">
-        <v>815.5403215093479</v>
+        <v>905.2939159093478</v>
       </c>
       <c r="Q70">
-        <v>3864.840321509348</v>
+        <v>3954.593915909348</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2025977216393332</v>
+        <v>0.2025552982329168</v>
       </c>
       <c r="T70">
         <v>2.424954609504367</v>
       </c>
       <c r="U70">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.567141175916674</v>
+        <v>1.671467915694842</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1147979215847735</v>
+        <v>0.1116276369847505</v>
       </c>
       <c r="C71">
-        <v>4702.338103717102</v>
+        <v>5671.489811292911</v>
       </c>
       <c r="D71">
-        <v>20233.71410371711</v>
+        <v>21202.86581129291</v>
       </c>
       <c r="E71">
         <v>5306.075999999999</v>
@@ -7115,37 +7115,37 @@
         <v>3004.7</v>
       </c>
       <c r="M71">
-        <v>1945.508682663823</v>
+        <v>1824.077349063823</v>
       </c>
       <c r="N71">
-        <v>1059.191317336177</v>
+        <v>1180.622650936176</v>
       </c>
       <c r="O71">
-        <v>264.7978293340441</v>
+        <v>295.1556627340441</v>
       </c>
       <c r="P71">
-        <v>794.3934880021325</v>
+        <v>885.4669882021323</v>
       </c>
       <c r="Q71">
-        <v>3843.693488002133</v>
+        <v>3934.766988202132</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2071681954531498</v>
+        <v>0.2071245354530757</v>
       </c>
       <c r="T71">
         <v>2.495639256108654</v>
       </c>
       <c r="U71">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.544428984961359</v>
+        <v>1.647243743003613</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.114921773583914</v>
+        <v>0.1117057798739213</v>
       </c>
       <c r="C72">
-        <v>4377.579450344532</v>
+        <v>5357.846086122157</v>
       </c>
       <c r="D72">
-        <v>20197.45945034453</v>
+        <v>21177.72608612216</v>
       </c>
       <c r="E72">
         <v>5594.58</v>
@@ -7197,37 +7197,37 @@
         <v>3004.7</v>
       </c>
       <c r="M72">
-        <v>1973.704460673444</v>
+        <v>1850.513252673444</v>
       </c>
       <c r="N72">
-        <v>1030.995539326556</v>
+        <v>1154.186747326556</v>
       </c>
       <c r="O72">
-        <v>257.7488848316389</v>
+        <v>288.5466868316389</v>
       </c>
       <c r="P72">
-        <v>773.2466544949168</v>
+        <v>865.6400604949167</v>
       </c>
       <c r="Q72">
-        <v>3822.546654494917</v>
+        <v>3914.940060494917</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2120433675212208</v>
+        <v>0.2119983884879118</v>
       </c>
       <c r="T72">
         <v>2.571036212486558</v>
       </c>
       <c r="U72">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.522365713747625</v>
+        <v>1.623711689532132</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1150456255830545</v>
+        <v>0.111783922763092</v>
       </c>
       <c r="C73">
-        <v>4052.950486356967</v>
+        <v>5044.261905479085</v>
       </c>
       <c r="D73">
-        <v>20161.33448635697</v>
+        <v>21152.64590547909</v>
       </c>
       <c r="E73">
         <v>5883.083999999997</v>
@@ -7279,37 +7279,37 @@
         <v>3004.7</v>
       </c>
       <c r="M73">
-        <v>2001.900238683064</v>
+        <v>1876.949156283064</v>
       </c>
       <c r="N73">
-        <v>1002.799761316935</v>
+        <v>1127.750843716935</v>
       </c>
       <c r="O73">
-        <v>250.6999403292339</v>
+        <v>281.9377109292338</v>
       </c>
       <c r="P73">
-        <v>752.0998209877016</v>
+        <v>845.8131327877015</v>
       </c>
       <c r="Q73">
-        <v>3801.399820987702</v>
+        <v>3895.113132787702</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.217254758352607</v>
+        <v>0.2172083693182539</v>
       </c>
       <c r="T73">
         <v>2.651632958959491</v>
       </c>
       <c r="U73">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.500923943131462</v>
+        <v>1.600842510806328</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1239714775821949</v>
+        <v>0.1118620656522628</v>
       </c>
       <c r="C74">
-        <v>1462.365301551807</v>
+        <v>4730.737058063256</v>
       </c>
       <c r="D74">
-        <v>17859.25330155181</v>
+        <v>21127.62505806325</v>
       </c>
       <c r="E74">
         <v>6171.587999999998</v>
@@ -7361,45 +7361,45 @@
         <v>3004.7</v>
       </c>
       <c r="M74">
-        <v>2368.684311092685</v>
+        <v>1903.385059892685</v>
       </c>
       <c r="N74">
-        <v>636.0156889073146</v>
+        <v>1101.314940107315</v>
       </c>
       <c r="O74">
-        <v>159.0039222268286</v>
+        <v>275.3287350268287</v>
       </c>
       <c r="P74">
-        <v>477.0117666804859</v>
+        <v>825.986205080486</v>
       </c>
       <c r="Q74">
-        <v>3526.311766680486</v>
+        <v>3875.286205080486</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2228383913862351</v>
+        <v>0.2227904916364775</v>
       </c>
       <c r="T74">
         <v>2.737986615894776</v>
       </c>
       <c r="U74">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.08552323332506818</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.268510111680487</v>
+        <v>1.578608587045129</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1242175795813354</v>
+        <v>0.1119402085414336</v>
       </c>
       <c r="C75">
-        <v>1117.81267107719</v>
+        <v>4417.271333572782</v>
       </c>
       <c r="D75">
-        <v>17803.20467107719</v>
+        <v>21102.66333357278</v>
       </c>
       <c r="E75">
         <v>6460.091999999999</v>
@@ -7443,45 +7443,45 @@
         <v>3004.7</v>
       </c>
       <c r="M75">
-        <v>2401.582704302306</v>
+        <v>1929.820963502306</v>
       </c>
       <c r="N75">
-        <v>603.1172956976939</v>
+        <v>1074.879036497694</v>
       </c>
       <c r="O75">
-        <v>150.7793239244235</v>
+        <v>268.7197591244235</v>
       </c>
       <c r="P75">
-        <v>452.3379717732704</v>
+        <v>806.1592773732705</v>
       </c>
       <c r="Q75">
-        <v>3501.637971773271</v>
+        <v>3855.459277373271</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2288356268667986</v>
+        <v>0.2287861044967918</v>
       </c>
       <c r="T75">
         <v>2.830736840010453</v>
       </c>
       <c r="U75">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.08552323332506818</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.251133260835549</v>
+        <v>1.556983811880127</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1441771360281048</v>
+        <v>0.1120183514306043</v>
       </c>
       <c r="C76">
-        <v>-2782.750826815056</v>
+        <v>4103.864522698495</v>
       </c>
       <c r="D76">
-        <v>14191.14517318495</v>
+        <v>21077.7605226985</v>
       </c>
       <c r="E76">
         <v>6748.596</v>
@@ -7525,45 +7525,45 @@
         <v>3004.7</v>
       </c>
       <c r="M76">
-        <v>3132.603076711927</v>
+        <v>1956.256867111927</v>
       </c>
       <c r="N76">
-        <v>-127.903076711927</v>
+        <v>1048.443132888073</v>
       </c>
       <c r="O76">
-        <v>-31.97576917798176</v>
+        <v>262.1107832220183</v>
       </c>
       <c r="P76">
-        <v>-95.92730753394528</v>
+        <v>786.3323496660549</v>
       </c>
       <c r="Q76">
-        <v>2953.372692466055</v>
+        <v>3835.632349666055</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2370504353163624</v>
+        <v>0.235242918346361</v>
       </c>
       <c r="T76">
-        <v>2.957782931035847</v>
+        <v>2.930621696750412</v>
       </c>
       <c r="U76">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V76">
-        <v>0.2397925883378929</v>
+        <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.111545976818717</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.9591703533515717</v>
+        <v>1.535943490097963</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1451864458057723</v>
+        <v>0.1120964943197751</v>
       </c>
       <c r="C77">
-        <v>-3215.37167759355</v>
+        <v>3790.516417118059</v>
       </c>
       <c r="D77">
-        <v>14047.02832240645</v>
+        <v>21052.91641711806</v>
       </c>
       <c r="E77">
         <v>7037.1</v>
@@ -7607,45 +7607,45 @@
         <v>3004.7</v>
       </c>
       <c r="M77">
-        <v>3174.935550721548</v>
+        <v>1982.692770721547</v>
       </c>
       <c r="N77">
-        <v>-170.235550721548</v>
+        <v>1022.007229278453</v>
       </c>
       <c r="O77">
-        <v>-42.55888768038699</v>
+        <v>255.5018073196131</v>
       </c>
       <c r="P77">
-        <v>-127.676663041161</v>
+        <v>766.5054219588394</v>
       </c>
       <c r="Q77">
-        <v>2921.623336958839</v>
+        <v>3815.805421958839</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2447004527290169</v>
+        <v>0.2422162773038957</v>
       </c>
       <c r="T77">
-        <v>3.076094248277281</v>
+        <v>3.038497342029569</v>
       </c>
       <c r="U77">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V77">
-        <v>0.236595353826721</v>
+        <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.1120151101646908</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.9463814153068841</v>
+        <v>1.515464243563323</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1461957555834399</v>
+        <v>0.1202686372089458</v>
       </c>
       <c r="C78">
-        <v>-3645.094825261553</v>
+        <v>1191.678192634765</v>
       </c>
       <c r="D78">
-        <v>13905.80917473845</v>
+        <v>18742.58219263477</v>
       </c>
       <c r="E78">
         <v>7325.603999999998</v>
@@ -7689,45 +7689,45 @@
         <v>3004.7</v>
       </c>
       <c r="M78">
-        <v>3217.268024731168</v>
+        <v>2320.482191131168</v>
       </c>
       <c r="N78">
-        <v>-212.568024731168</v>
+        <v>684.217808868832</v>
       </c>
       <c r="O78">
-        <v>-53.14200618279199</v>
+        <v>171.054452217208</v>
       </c>
       <c r="P78">
-        <v>-159.426018548376</v>
+        <v>513.163356651624</v>
       </c>
       <c r="Q78">
-        <v>2889.873981451624</v>
+        <v>3562.463356651624</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.252987971592726</v>
+        <v>0.2497707495078917</v>
       </c>
       <c r="T78">
-        <v>3.204264841955501</v>
+        <v>3.155362624415321</v>
       </c>
       <c r="U78">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V78">
-        <v>0.2334822570658432</v>
+        <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.112471897896297</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.9339290282633727</v>
+        <v>1.294860185302821</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1472050653611075</v>
+        <v>0.1204532800981166</v>
       </c>
       <c r="C79">
-        <v>-4072.006794493289</v>
+        <v>856.8174281092179</v>
       </c>
       <c r="D79">
-        <v>13767.40120550671</v>
+        <v>18696.22542810922</v>
       </c>
       <c r="E79">
         <v>7614.107999999998</v>
@@ -7771,45 +7771,45 @@
         <v>3004.7</v>
       </c>
       <c r="M79">
-        <v>3259.600498740789</v>
+        <v>2351.014851540789</v>
       </c>
       <c r="N79">
-        <v>-254.9004987407889</v>
+        <v>653.6851484592112</v>
       </c>
       <c r="O79">
-        <v>-63.72512468519722</v>
+        <v>163.4212871148028</v>
       </c>
       <c r="P79">
-        <v>-191.1753740555916</v>
+        <v>490.2638613444084</v>
       </c>
       <c r="Q79">
-        <v>2858.124625944409</v>
+        <v>3539.563861344408</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2619961442706706</v>
+        <v>0.2579821323383222</v>
       </c>
       <c r="T79">
-        <v>3.343580704649219</v>
+        <v>3.282390105269401</v>
       </c>
       <c r="U79">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V79">
-        <v>0.2304500199610919</v>
+        <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.1129168210114978</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.9218000798443677</v>
+        <v>1.278043819259927</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1482143751387751</v>
+        <v>0.1206379229872873</v>
       </c>
       <c r="C80">
-        <v>-4496.190699105911</v>
+        <v>522.1854098286967</v>
       </c>
       <c r="D80">
-        <v>13631.72130089409</v>
+        <v>18650.0974098287</v>
       </c>
       <c r="E80">
         <v>7902.611999999999</v>
@@ -7853,45 +7853,45 @@
         <v>3004.7</v>
       </c>
       <c r="M80">
-        <v>3301.93297275041</v>
+        <v>2381.547511950409</v>
       </c>
       <c r="N80">
-        <v>-297.2329727504098</v>
+        <v>623.1524880495904</v>
       </c>
       <c r="O80">
-        <v>-74.30824318760244</v>
+        <v>155.7881220123976</v>
       </c>
       <c r="P80">
-        <v>-222.9247295628073</v>
+        <v>467.3643660371928</v>
       </c>
       <c r="Q80">
-        <v>2826.375270437193</v>
+        <v>3516.664366037193</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2718232417375192</v>
+        <v>0.2669400045169735</v>
       </c>
       <c r="T80">
-        <v>3.495561645769638</v>
+        <v>3.420965538928395</v>
       </c>
       <c r="U80">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V80">
-        <v>0.2274955325256933</v>
+        <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.1133503358416934</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.9099821301027732</v>
+        <v>1.261658642089928</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1492236849164426</v>
+        <v>0.1385120090705982</v>
       </c>
       <c r="C81">
-        <v>-4917.726408491897</v>
+        <v>-3361.89860086409</v>
       </c>
       <c r="D81">
-        <v>13498.68959150811</v>
+        <v>15054.51739913592</v>
       </c>
       <c r="E81">
         <v>8191.116</v>
@@ -7935,37 +7935,37 @@
         <v>3004.7</v>
       </c>
       <c r="M81">
-        <v>3344.26544676003</v>
+        <v>3063.92610996003</v>
       </c>
       <c r="N81">
-        <v>-339.5654467600302</v>
+        <v>-59.22610996003004</v>
       </c>
       <c r="O81">
-        <v>-84.89136169000756</v>
+        <v>-14.80652749000751</v>
       </c>
       <c r="P81">
-        <v>-254.6740850700227</v>
+        <v>-44.41958247002253</v>
       </c>
       <c r="Q81">
-        <v>2794.625914929978</v>
+        <v>3004.880417529977</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2825862532488297</v>
+        <v>0.2778497016019513</v>
       </c>
       <c r="T81">
-        <v>3.662016962234859</v>
+        <v>3.589735083133555</v>
       </c>
       <c r="U81">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V81">
-        <v>0.2246158422405579</v>
+        <v>0.2451674658726673</v>
       </c>
       <c r="W81">
-        <v>0.1137728756128967</v>
+        <v>0.1014728756128967</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8984633689622318</v>
+        <v>0.9806698634906693</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1502329946941102</v>
+        <v>0.1393983188482658</v>
       </c>
       <c r="C82">
-        <v>-5336.690704400437</v>
+        <v>-3792.958216532268</v>
       </c>
       <c r="D82">
-        <v>13368.22929559957</v>
+        <v>14911.96178346774</v>
       </c>
       <c r="E82">
         <v>8479.620000000001</v>
@@ -8017,37 +8017,37 @@
         <v>3004.7</v>
       </c>
       <c r="M82">
-        <v>3386.597920769651</v>
+        <v>3102.709984769651</v>
       </c>
       <c r="N82">
-        <v>-381.8979207696511</v>
+        <v>-98.00998476965106</v>
       </c>
       <c r="O82">
-        <v>-95.47448019241278</v>
+        <v>-24.50249619241276</v>
       </c>
       <c r="P82">
-        <v>-286.4234405772384</v>
+        <v>-73.50748857723829</v>
       </c>
       <c r="Q82">
-        <v>2762.876559422762</v>
+        <v>2975.792511422762</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2944255659112712</v>
+        <v>0.2894521866820489</v>
       </c>
       <c r="T82">
-        <v>3.845117810346602</v>
+        <v>3.769221837290234</v>
       </c>
       <c r="U82">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V82">
-        <v>0.221808144212551</v>
+        <v>0.2421028725492589</v>
       </c>
       <c r="W82">
-        <v>0.11418485188982</v>
+        <v>0.10188485188982</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8872325768502038</v>
+        <v>0.9684114901970358</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1512423044717778</v>
+        <v>0.1402846286259334</v>
       </c>
       <c r="C83">
-        <v>-5753.157428714403</v>
+        <v>-4221.343356195928</v>
       </c>
       <c r="D83">
-        <v>13240.2665712856</v>
+        <v>14772.08064380408</v>
       </c>
       <c r="E83">
         <v>8768.124000000002</v>
@@ -8099,37 +8099,37 @@
         <v>3004.7</v>
       </c>
       <c r="M83">
-        <v>3428.930394779272</v>
+        <v>3141.493859579271</v>
       </c>
       <c r="N83">
-        <v>-424.230394779272</v>
+        <v>-136.7938595792716</v>
       </c>
       <c r="O83">
-        <v>-106.057598694818</v>
+        <v>-34.1984648948179</v>
       </c>
       <c r="P83">
-        <v>-318.172796084454</v>
+        <v>-102.5953946844537</v>
       </c>
       <c r="Q83">
-        <v>2731.127203915546</v>
+        <v>2946.704605315546</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3075111220118644</v>
+        <v>0.3022759859811042</v>
       </c>
       <c r="T83">
-        <v>4.047492431943792</v>
+        <v>3.96760193398972</v>
       </c>
       <c r="U83">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V83">
-        <v>0.2190697720617787</v>
+        <v>0.239113948196799</v>
       </c>
       <c r="W83">
-        <v>0.1145866559129921</v>
+        <v>0.1022866559129921</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8762790882471148</v>
+        <v>0.9564557927871958</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1522516142494454</v>
+        <v>0.1411709384036009</v>
       </c>
       <c r="C84">
-        <v>-6167.197622820477</v>
+        <v>-4647.128583897495</v>
       </c>
       <c r="D84">
-        <v>13114.73037717953</v>
+        <v>14634.79941610251</v>
       </c>
       <c r="E84">
         <v>9056.627999999999</v>
@@ -8181,37 +8181,37 @@
         <v>3004.7</v>
       </c>
       <c r="M84">
-        <v>3471.262868788892</v>
+        <v>3180.277734388892</v>
       </c>
       <c r="N84">
-        <v>-466.562868788892</v>
+        <v>-175.5777343888922</v>
       </c>
       <c r="O84">
-        <v>-116.640717197223</v>
+        <v>-43.89443359722304</v>
       </c>
       <c r="P84">
-        <v>-349.922151591669</v>
+        <v>-131.6833007916691</v>
       </c>
       <c r="Q84">
-        <v>2699.377848408331</v>
+        <v>2917.616699208331</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3220506287903013</v>
+        <v>0.3165246518689433</v>
       </c>
       <c r="T84">
-        <v>4.272353122607336</v>
+        <v>4.188024263655816</v>
       </c>
       <c r="U84">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V84">
-        <v>0.2163981894756595</v>
+        <v>0.2361979244383014</v>
       </c>
       <c r="W84">
-        <v>0.114978659838038</v>
+        <v>0.102678659838038</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8655927579026379</v>
+        <v>0.9447916977532057</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.153260924027113</v>
+        <v>0.1420572481812685</v>
       </c>
       <c r="C85">
-        <v>-6578.879659125298</v>
+        <v>-5070.385717420162</v>
       </c>
       <c r="D85">
-        <v>12991.5523408747</v>
+        <v>14500.04628257984</v>
       </c>
       <c r="E85">
         <v>9345.132</v>
@@ -8263,37 +8263,37 @@
         <v>3004.7</v>
       </c>
       <c r="M85">
-        <v>3513.595342798513</v>
+        <v>3219.061609198513</v>
       </c>
       <c r="N85">
-        <v>-508.895342798513</v>
+        <v>-214.3616091985127</v>
       </c>
       <c r="O85">
-        <v>-127.2238356996282</v>
+        <v>-53.59040229962818</v>
       </c>
       <c r="P85">
-        <v>-381.6715070988847</v>
+        <v>-160.7712068988845</v>
       </c>
       <c r="Q85">
-        <v>2667.628492901115</v>
+        <v>2888.528793101116</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3383006657779661</v>
+        <v>0.3324496313906458</v>
       </c>
       <c r="T85">
-        <v>4.523668012172473</v>
+        <v>4.434378632106157</v>
       </c>
       <c r="U85">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V85">
-        <v>0.2137909823735431</v>
+        <v>0.2333521663125388</v>
       </c>
       <c r="W85">
-        <v>0.115361217885372</v>
+        <v>0.103061217885372</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8551639294941724</v>
+        <v>0.9334086652501551</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1542702338047805</v>
+        <v>0.1429435579589361</v>
       </c>
       <c r="C86">
-        <v>-6988.269365229</v>
+        <v>-5491.183953568234</v>
       </c>
       <c r="D86">
-        <v>12870.666634771</v>
+        <v>14367.75204643177</v>
       </c>
       <c r="E86">
         <v>9633.635999999997</v>
@@ -8345,37 +8345,37 @@
         <v>3004.7</v>
       </c>
       <c r="M86">
-        <v>3555.927816808133</v>
+        <v>3257.845484008133</v>
       </c>
       <c r="N86">
-        <v>-551.227816808133</v>
+        <v>-253.1454840081328</v>
       </c>
       <c r="O86">
-        <v>-137.8069542020332</v>
+        <v>-63.28637100203321</v>
       </c>
       <c r="P86">
-        <v>-413.4208626060997</v>
+        <v>-189.8591130060996</v>
       </c>
       <c r="Q86">
-        <v>2635.8791373939</v>
+        <v>2859.440886993901</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3565819573890889</v>
+        <v>0.3503652333525611</v>
       </c>
       <c r="T86">
-        <v>4.806397262933251</v>
+        <v>4.711527296612791</v>
       </c>
       <c r="U86">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V86">
-        <v>0.211245851631001</v>
+        <v>0.2305741643326276</v>
       </c>
       <c r="W86">
-        <v>0.1157346674077694</v>
+        <v>0.1034346674077694</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8449834065240038</v>
+        <v>0.9222966573305105</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1552795435824481</v>
+        <v>0.1438298677366037</v>
       </c>
       <c r="C87">
-        <v>-7395.430141230187</v>
+        <v>-5909.589986651368</v>
       </c>
       <c r="D87">
-        <v>12752.00985876981</v>
+        <v>14237.85001334863</v>
       </c>
       <c r="E87">
         <v>9922.139999999998</v>
@@ -8427,37 +8427,37 @@
         <v>3004.7</v>
       </c>
       <c r="M87">
-        <v>3598.260290817754</v>
+        <v>3296.629358817754</v>
       </c>
       <c r="N87">
-        <v>-593.5602908177539</v>
+        <v>-291.9293588177538</v>
       </c>
       <c r="O87">
-        <v>-148.3900727044385</v>
+        <v>-72.98233970443846</v>
       </c>
       <c r="P87">
-        <v>-445.1702181133154</v>
+        <v>-218.9470191133154</v>
       </c>
       <c r="Q87">
-        <v>2604.129781886685</v>
+        <v>2830.352980886685</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3773007545483615</v>
+        <v>0.3706695822427318</v>
       </c>
       <c r="T87">
-        <v>5.126823747128801</v>
+        <v>5.025629116386976</v>
       </c>
       <c r="U87">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V87">
-        <v>0.2087606063176951</v>
+        <v>0.2278615271051849</v>
       </c>
       <c r="W87">
-        <v>0.1160993298825811</v>
+        <v>0.103799329882581</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8350424252707802</v>
+        <v>0.9114461084207397</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1562888533601157</v>
+        <v>0.1447161775142712</v>
       </c>
       <c r="C88">
-        <v>-7800.423070601366</v>
+        <v>-6325.668120599013</v>
       </c>
       <c r="D88">
-        <v>12635.52092939864</v>
+        <v>14110.27587940099</v>
       </c>
       <c r="E88">
         <v>10210.644</v>
@@ -8509,37 +8509,37 @@
         <v>3004.7</v>
       </c>
       <c r="M88">
-        <v>3640.592764827375</v>
+        <v>3335.413233627374</v>
       </c>
       <c r="N88">
-        <v>-635.8927648273748</v>
+        <v>-330.7132336273744</v>
       </c>
       <c r="O88">
-        <v>-158.9731912068437</v>
+        <v>-82.6783084068436</v>
       </c>
       <c r="P88">
-        <v>-476.9195736205311</v>
+        <v>-248.0349252205308</v>
       </c>
       <c r="Q88">
-        <v>2572.380426379469</v>
+        <v>2801.26507477947</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4009793798732444</v>
+        <v>0.3938745524029269</v>
       </c>
       <c r="T88">
-        <v>5.493025443352287</v>
+        <v>5.384602624700332</v>
       </c>
       <c r="U88">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V88">
-        <v>0.2063331574070242</v>
+        <v>0.225211974464427</v>
       </c>
       <c r="W88">
-        <v>0.1164555118347226</v>
+        <v>0.1041555118347226</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8253326296280966</v>
+        <v>0.9008478978577078</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1572981631377833</v>
+        <v>0.1456024872919388</v>
       </c>
       <c r="C89">
-        <v>-8203.307025042468</v>
+        <v>-6739.480375100913</v>
       </c>
       <c r="D89">
-        <v>12521.14097495753</v>
+        <v>13984.96762489909</v>
       </c>
       <c r="E89">
         <v>10499.148</v>
@@ -8591,37 +8591,37 @@
         <v>3004.7</v>
       </c>
       <c r="M89">
-        <v>3682.925238836995</v>
+        <v>3374.197108436995</v>
       </c>
       <c r="N89">
-        <v>-678.2252388369952</v>
+        <v>-369.4971084369949</v>
       </c>
       <c r="O89">
-        <v>-169.5563097092488</v>
+        <v>-92.37427710924874</v>
       </c>
       <c r="P89">
-        <v>-508.6689291277464</v>
+        <v>-277.1228313277462</v>
       </c>
       <c r="Q89">
-        <v>2540.631070872254</v>
+        <v>2772.177168672254</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4283008706327248</v>
+        <v>0.4206495179723828</v>
       </c>
       <c r="T89">
-        <v>5.915565862071694</v>
+        <v>5.798802826600357</v>
       </c>
       <c r="U89">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V89">
-        <v>0.2039615119195871</v>
+        <v>0.2226233310797784</v>
       </c>
       <c r="W89">
-        <v>0.1168035056960104</v>
+        <v>0.1045035056960104</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8158460476783485</v>
+        <v>0.8904933243191135</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1583074729154508</v>
+        <v>0.1464887970696064</v>
       </c>
       <c r="C90">
-        <v>-8604.138763690331</v>
+        <v>-7151.08658614177</v>
       </c>
       <c r="D90">
-        <v>12408.81323630967</v>
+        <v>13861.86541385823</v>
       </c>
       <c r="E90">
         <v>10787.652</v>
@@ -8673,37 +8673,37 @@
         <v>3004.7</v>
       </c>
       <c r="M90">
-        <v>3725.257712846616</v>
+        <v>3412.980983246616</v>
       </c>
       <c r="N90">
-        <v>-720.5577128466161</v>
+        <v>-408.280983246616</v>
       </c>
       <c r="O90">
-        <v>-180.139428211654</v>
+        <v>-102.070245811654</v>
       </c>
       <c r="P90">
-        <v>-540.4182846349621</v>
+        <v>-306.210737434962</v>
       </c>
       <c r="Q90">
-        <v>2508.881715365038</v>
+        <v>2743.089262565038</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4601759431854519</v>
+        <v>0.4518869778034149</v>
       </c>
       <c r="T90">
-        <v>6.408529683911002</v>
+        <v>6.282036395483722</v>
       </c>
       <c r="U90">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V90">
-        <v>0.2016437674659554</v>
+        <v>0.2200935204993263</v>
       </c>
       <c r="W90">
-        <v>0.1171435906059052</v>
+        <v>0.1048435906059052</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8065750698638217</v>
+        <v>0.8803740819973053</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1903747047108632</v>
+        <v>0.147375106847274</v>
       </c>
       <c r="C91">
-        <v>-11644.96580077017</v>
+        <v>-7560.544501272638</v>
       </c>
       <c r="D91">
-        <v>9656.490199229835</v>
+        <v>13740.91149872736</v>
       </c>
       <c r="E91">
         <v>11076.156</v>
@@ -8755,45 +8755,45 @@
         <v>3004.7</v>
       </c>
       <c r="M91">
-        <v>4607.223378056236</v>
+        <v>3451.764858056236</v>
       </c>
       <c r="N91">
-        <v>-1602.523378056237</v>
+        <v>-447.0648580562365</v>
       </c>
       <c r="O91">
-        <v>-400.6308445140592</v>
+        <v>-111.7662145140591</v>
       </c>
       <c r="P91">
-        <v>-1201.892533542177</v>
+        <v>-335.2986435421774</v>
       </c>
       <c r="Q91">
-        <v>1847.407466457823</v>
+        <v>2714.001356457823</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.515618501818173</v>
+        <v>0.4888039757855435</v>
       </c>
       <c r="T91">
-        <v>7.265976378375005</v>
+        <v>6.85313061325497</v>
       </c>
       <c r="U91">
-        <v>0.1794309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V91">
-        <v>0.1630428868671258</v>
+        <v>0.2176205595948395</v>
       </c>
       <c r="W91">
-        <v>0.1501760331582744</v>
+        <v>0.1051760331582744</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.652171547468503</v>
+        <v>0.8704822383793581</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.240667881068277</v>
+        <v>0.1482614166249415</v>
       </c>
       <c r="C92">
-        <v>-14425.69972558442</v>
+        <v>-7967.909869937554</v>
       </c>
       <c r="D92">
-        <v>7164.260274415585</v>
+        <v>13622.05013006245</v>
       </c>
       <c r="E92">
         <v>11364.66</v>
@@ -8837,45 +8837,45 @@
         <v>3004.7</v>
       </c>
       <c r="M92">
-        <v>6014.381724865857</v>
+        <v>3490.548732865857</v>
       </c>
       <c r="N92">
-        <v>-3009.681724865857</v>
+        <v>-485.8487328658571</v>
       </c>
       <c r="O92">
-        <v>-752.4204312164643</v>
+        <v>-121.4621832164643</v>
       </c>
       <c r="P92">
-        <v>-2257.261293649393</v>
+        <v>-364.3865496493928</v>
       </c>
       <c r="Q92">
-        <v>792.0387063506073</v>
+        <v>2684.913450350607</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5823690177974525</v>
+        <v>0.5331043733640978</v>
       </c>
       <c r="T92">
-        <v>8.298306247192079</v>
+        <v>7.538443674580466</v>
       </c>
       <c r="U92">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V92">
-        <v>0.1248964622405562</v>
+        <v>0.2152025533771191</v>
       </c>
       <c r="W92">
-        <v>0.2027010880983686</v>
+        <v>0.1055010880983686</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.4995858489622249</v>
+        <v>0.8608102135084763</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2425261908459446</v>
+        <v>0.1491477264026091</v>
       </c>
       <c r="C93">
-        <v>-14781.87857284523</v>
+        <v>-8373.236529152317</v>
       </c>
       <c r="D93">
-        <v>7096.585427154769</v>
+        <v>13505.22747084769</v>
       </c>
       <c r="E93">
         <v>11653.164</v>
@@ -8919,45 +8919,45 @@
         <v>3004.7</v>
       </c>
       <c r="M93">
-        <v>6081.208188475478</v>
+        <v>3529.332607675477</v>
       </c>
       <c r="N93">
-        <v>-3076.508188475478</v>
+        <v>-524.6326076754776</v>
       </c>
       <c r="O93">
-        <v>-769.1270471188695</v>
+        <v>-131.1581519188694</v>
       </c>
       <c r="P93">
-        <v>-2307.381141356609</v>
+        <v>-393.4744557566082</v>
       </c>
       <c r="Q93">
-        <v>741.9188586433916</v>
+        <v>2655.825544243392</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6419877975527249</v>
+        <v>0.5872493037378865</v>
       </c>
       <c r="T93">
-        <v>9.220340274657865</v>
+        <v>8.376048527311632</v>
       </c>
       <c r="U93">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V93">
-        <v>0.1235239736445062</v>
+        <v>0.2128376901531947</v>
       </c>
       <c r="W93">
-        <v>0.2030189989738454</v>
+        <v>0.1058189989738454</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.4940958945780246</v>
+        <v>0.8513507606127788</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2443845006236122</v>
+        <v>0.1500340361802767</v>
       </c>
       <c r="C94">
-        <v>-15136.7908476397</v>
+        <v>-8776.576484812085</v>
       </c>
       <c r="D94">
-        <v>7030.177152360301</v>
+        <v>13390.39151518792</v>
       </c>
       <c r="E94">
         <v>11941.668</v>
@@ -9001,45 +9001,45 @@
         <v>3004.7</v>
       </c>
       <c r="M94">
-        <v>6148.034652085099</v>
+        <v>3568.116482485098</v>
       </c>
       <c r="N94">
-        <v>-3143.334652085099</v>
+        <v>-563.4164824850982</v>
       </c>
       <c r="O94">
-        <v>-785.8336630212748</v>
+        <v>-140.8541206212745</v>
       </c>
       <c r="P94">
-        <v>-2357.500989063824</v>
+        <v>-422.5623618638236</v>
       </c>
       <c r="Q94">
-        <v>691.7990109361758</v>
+        <v>2626.737638136176</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7165112722468158</v>
+        <v>0.6549304667051224</v>
       </c>
       <c r="T94">
-        <v>10.3728828089901</v>
+        <v>9.423054593225586</v>
       </c>
       <c r="U94">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V94">
-        <v>0.1221813217570659</v>
+        <v>0.2105242369993556</v>
       </c>
       <c r="W94">
-        <v>0.2033299987433336</v>
+        <v>0.1061299987433336</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.4887252870282635</v>
+        <v>0.8420969479974225</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2462428104012797</v>
+        <v>0.1509203459579443</v>
       </c>
       <c r="C95">
-        <v>-15490.4717772328</v>
+        <v>-9177.979988885789</v>
       </c>
       <c r="D95">
-        <v>6965.000222767207</v>
+        <v>13277.49201111421</v>
       </c>
       <c r="E95">
         <v>12230.172</v>
@@ -9083,45 +9083,45 @@
         <v>3004.7</v>
       </c>
       <c r="M95">
-        <v>6214.861115694719</v>
+        <v>3606.900357294719</v>
       </c>
       <c r="N95">
-        <v>-3210.161115694719</v>
+        <v>-602.2003572947192</v>
       </c>
       <c r="O95">
-        <v>-802.5402789236798</v>
+        <v>-150.5500893236798</v>
       </c>
       <c r="P95">
-        <v>-2407.62083677104</v>
+        <v>-451.6502679710394</v>
       </c>
       <c r="Q95">
-        <v>641.6791632289605</v>
+        <v>2597.649732028961</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8123271682820753</v>
+        <v>0.7419491048058543</v>
       </c>
       <c r="T95">
-        <v>11.8547232102744</v>
+        <v>10.76920524940067</v>
       </c>
       <c r="U95">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V95">
-        <v>0.1208675441037641</v>
+        <v>0.2082605355262443</v>
       </c>
       <c r="W95">
-        <v>0.203634310345736</v>
+        <v>0.106434310345736</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.4834701764150564</v>
+        <v>0.8330421421049771</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2481011201789473</v>
+        <v>0.1518066557356119</v>
       </c>
       <c r="C96">
-        <v>-15842.9552945186</v>
+        <v>-9577.495612738014</v>
       </c>
       <c r="D96">
-        <v>6901.020705481406</v>
+        <v>13166.48038726199</v>
       </c>
       <c r="E96">
         <v>12518.676</v>
@@ -9165,45 +9165,45 @@
         <v>3004.7</v>
       </c>
       <c r="M96">
-        <v>6281.68757930434</v>
+        <v>3645.68423210434</v>
       </c>
       <c r="N96">
-        <v>-3276.98757930434</v>
+        <v>-640.9842321043398</v>
       </c>
       <c r="O96">
-        <v>-819.2468948260851</v>
+        <v>-160.2460580260849</v>
       </c>
       <c r="P96">
-        <v>-2457.740684478255</v>
+        <v>-480.7381740782548</v>
       </c>
       <c r="Q96">
-        <v>591.5593155217448</v>
+        <v>2568.561825921745</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.9400816963290882</v>
+        <v>0.8579739556068303</v>
       </c>
       <c r="T96">
-        <v>13.83051041198681</v>
+        <v>12.56407279096745</v>
       </c>
       <c r="U96">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V96">
-        <v>0.11958171916649</v>
+        <v>0.206044997914263</v>
       </c>
       <c r="W96">
-        <v>0.2039321472331937</v>
+        <v>0.1067321472331937</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.47832687666596</v>
+        <v>0.8241799916570518</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2499594299566149</v>
+        <v>0.1526929655132795</v>
       </c>
       <c r="C97">
-        <v>-16194.27409692869</v>
+        <v>-9975.170316803189</v>
       </c>
       <c r="D97">
-        <v>6838.205903071312</v>
+        <v>13057.30968319682</v>
       </c>
       <c r="E97">
         <v>12807.18</v>
@@ -9247,45 +9247,45 @@
         <v>3004.7</v>
       </c>
       <c r="M97">
-        <v>6348.514042913961</v>
+        <v>3684.468106913961</v>
       </c>
       <c r="N97">
-        <v>-3343.814042913961</v>
+        <v>-679.7681069139608</v>
       </c>
       <c r="O97">
-        <v>-835.9535107284903</v>
+        <v>-169.9420267284902</v>
       </c>
       <c r="P97">
-        <v>-2507.860532185471</v>
+        <v>-509.8260801854706</v>
       </c>
       <c r="Q97">
-        <v>541.4394678145291</v>
+        <v>2539.47391981453</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.118938035594906</v>
+        <v>1.020408746728197</v>
       </c>
       <c r="T97">
-        <v>16.59661249438417</v>
+        <v>15.07688734916096</v>
       </c>
       <c r="U97">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V97">
-        <v>0.1183229642278954</v>
+        <v>0.2038761031993759</v>
       </c>
       <c r="W97">
-        <v>0.2042237138703891</v>
+        <v>0.1070237138703891</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.4732918569115815</v>
+        <v>0.8155044127975037</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2518177397342825</v>
+        <v>0.153579275290947</v>
       </c>
       <c r="C98">
-        <v>-16544.45970215245</v>
+        <v>-10371.04951682202</v>
       </c>
       <c r="D98">
-        <v>6776.524297847551</v>
+        <v>12949.93448317798</v>
       </c>
       <c r="E98">
         <v>13095.684</v>
@@ -9329,45 +9329,45 @@
         <v>3004.7</v>
       </c>
       <c r="M98">
-        <v>6415.340506523581</v>
+        <v>3723.251981723581</v>
       </c>
       <c r="N98">
-        <v>-3410.640506523581</v>
+        <v>-718.5519817235809</v>
       </c>
       <c r="O98">
-        <v>-852.6601266308953</v>
+        <v>-179.6379954308952</v>
       </c>
       <c r="P98">
-        <v>-2557.980379892686</v>
+        <v>-538.9139862926856</v>
       </c>
       <c r="Q98">
-        <v>491.3196201073142</v>
+        <v>2510.386013707314</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.38722254449363</v>
+        <v>1.264060933410243</v>
       </c>
       <c r="T98">
-        <v>20.74576561798017</v>
+        <v>18.84610918645114</v>
       </c>
       <c r="U98">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V98">
-        <v>0.1170904333505215</v>
+        <v>0.2017523937910491</v>
       </c>
       <c r="W98">
-        <v>0.2045092062026429</v>
+        <v>0.1073092062026429</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.4683617334020859</v>
+        <v>0.8070095751641966</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2536760495119501</v>
+        <v>0.1838492758499622</v>
       </c>
       <c r="C99">
-        <v>-16893.5425008686</v>
+        <v>-13499.07963263478</v>
       </c>
       <c r="D99">
-        <v>6715.945499131404</v>
+        <v>10110.40836736522</v>
       </c>
       <c r="E99">
         <v>13384.188</v>
@@ -9411,45 +9411,45 @@
         <v>3004.7</v>
       </c>
       <c r="M99">
-        <v>6482.166970133201</v>
+        <v>4551.209698133201</v>
       </c>
       <c r="N99">
-        <v>-3477.466970133201</v>
+        <v>-1546.509698133201</v>
       </c>
       <c r="O99">
-        <v>-869.3667425333003</v>
+        <v>-386.6274245333002</v>
       </c>
       <c r="P99">
-        <v>-2608.100227599901</v>
+        <v>-1159.882273599901</v>
       </c>
       <c r="Q99">
-        <v>441.1997724000994</v>
+        <v>1889.4177264001</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.834363392658173</v>
+        <v>1.737804270591912</v>
       </c>
       <c r="T99">
-        <v>27.66102082397357</v>
+        <v>26.17476794421576</v>
       </c>
       <c r="U99">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.1158833154809285</v>
+        <v>0.1650495252521795</v>
       </c>
       <c r="W99">
-        <v>0.2047888120950565</v>
+        <v>0.1357888120950565</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.4635332619237139</v>
+        <v>0.660198101008718</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2555343592896176</v>
+        <v>0.1850175856276298</v>
       </c>
       <c r="C100">
-        <v>-17241.55180667347</v>
+        <v>-13872.42987457004</v>
       </c>
       <c r="D100">
-        <v>6656.440193326531</v>
+        <v>10025.56212542996</v>
       </c>
       <c r="E100">
         <v>13672.692</v>
@@ -9493,45 +9493,45 @@
         <v>3004.7</v>
       </c>
       <c r="M100">
-        <v>6548.993433742822</v>
+        <v>4598.129385742822</v>
       </c>
       <c r="N100">
-        <v>-3544.293433742822</v>
+        <v>-1593.429385742822</v>
       </c>
       <c r="O100">
-        <v>-886.0733584357056</v>
+        <v>-398.3573464357055</v>
       </c>
       <c r="P100">
-        <v>-2658.220075307117</v>
+        <v>-1195.072039307116</v>
       </c>
       <c r="Q100">
-        <v>391.0799246928837</v>
+        <v>1854.227960692884</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.72864508898726</v>
+        <v>2.583806405887868</v>
       </c>
       <c r="T100">
-        <v>41.49153123596034</v>
+        <v>39.26215191632364</v>
       </c>
       <c r="U100">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1147008326698986</v>
+        <v>0.1633653464230756</v>
       </c>
       <c r="W100">
-        <v>0.2050627117447677</v>
+        <v>0.1360627117447677</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.4588033306795943</v>
+        <v>0.6534613856923024</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2573926690672852</v>
+        <v>0.242057762254414</v>
       </c>
       <c r="C101">
-        <v>-17588.51590337836</v>
+        <v>-17074.75408656251</v>
       </c>
       <c r="D101">
-        <v>6597.980096621644</v>
+        <v>7111.741913437497</v>
       </c>
       <c r="E101">
         <v>13961.196</v>
@@ -9575,37 +9575,37 @@
         <v>3004.7</v>
       </c>
       <c r="M101">
-        <v>6615.819897352442</v>
+        <v>6187.391457352443</v>
       </c>
       <c r="N101">
-        <v>-3611.119897352442</v>
+        <v>-3182.691457352443</v>
       </c>
       <c r="O101">
-        <v>-902.7799743381106</v>
+        <v>-795.6728643381107</v>
       </c>
       <c r="P101">
-        <v>-2708.339923014332</v>
+        <v>-2387.018593014332</v>
       </c>
       <c r="Q101">
-        <v>340.9600769856684</v>
+        <v>662.2814069856681</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.411490177974519</v>
+        <v>5.3629994966874</v>
       </c>
       <c r="T101">
-        <v>82.98306247192069</v>
+        <v>82.25538514167319</v>
       </c>
       <c r="U101">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V101">
-        <v>0.1135422384005057</v>
+        <v>0.1214041499034917</v>
       </c>
       <c r="W101">
-        <v>0.2053310780682222</v>
+        <v>0.1903310780682222</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.4541689536020227</v>
+        <v>0.4856165996139669</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/spain/spain_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_oil_gas_integrated.xlsx
@@ -1175,7 +1175,7 @@
         <v>0.102826948055655</v>
       </c>
       <c r="R2">
-        <v>0.102606636312164</v>
+        <v>0.102606636312165</v>
       </c>
       <c r="S2">
         <v>0.0541732333250682</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1062357776319679</v>
+        <v>0.1061226705211387</v>
       </c>
       <c r="C2">
-        <v>27469.90806046854</v>
+        <v>27224.70706844507</v>
       </c>
       <c r="D2">
-        <v>23094.50806046854</v>
+        <v>23137.81106844507</v>
       </c>
       <c r="E2">
-        <v>-14600.7</v>
+        <v>-14312.196</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>288.504</v>
       </c>
       <c r="G2">
         <v>4375.4</v>
@@ -1457,28 +1457,28 @@
         <v>3004.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>19.07905160962063</v>
       </c>
       <c r="N2">
-        <v>3004.7</v>
+        <v>2985.620948390379</v>
       </c>
       <c r="O2">
-        <v>751.175</v>
+        <v>746.4052370975947</v>
       </c>
       <c r="P2">
-        <v>2253.525</v>
+        <v>2239.215711292784</v>
       </c>
       <c r="Q2">
-        <v>5302.825</v>
+        <v>5288.515711292785</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1062357776319679</v>
+        <v>0.1066936244322101</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9420050034730364</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>157.4868636806285</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1061226705211387</v>
+        <v>0.1060095634103094</v>
       </c>
       <c r="C3">
-        <v>27224.70706844507</v>
+        <v>26979.66877077926</v>
       </c>
       <c r="D3">
-        <v>23137.81106844507</v>
+        <v>23181.27677077926</v>
       </c>
       <c r="E3">
-        <v>-14312.196</v>
+        <v>-14023.692</v>
       </c>
       <c r="F3">
-        <v>288.504</v>
+        <v>577.008</v>
       </c>
       <c r="G3">
         <v>4375.4</v>
@@ -1539,28 +1539,28 @@
         <v>3004.7</v>
       </c>
       <c r="M3">
-        <v>19.07905160962063</v>
+        <v>38.15810321924126</v>
       </c>
       <c r="N3">
-        <v>2985.620948390379</v>
+        <v>2966.541896780759</v>
       </c>
       <c r="O3">
-        <v>746.4052370975947</v>
+        <v>741.6354741951897</v>
       </c>
       <c r="P3">
-        <v>2239.215711292784</v>
+        <v>2224.906422585569</v>
       </c>
       <c r="Q3">
-        <v>5288.515711292785</v>
+        <v>5274.206422585569</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1066936244322101</v>
+        <v>0.1071608150447021</v>
       </c>
       <c r="T3">
-        <v>0.9420050034730364</v>
+        <v>0.9492322936638684</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>157.4868636806285</v>
+        <v>78.74343184031424</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1060095634103094</v>
+        <v>0.1058964562994802</v>
       </c>
       <c r="C4">
-        <v>26979.66877077926</v>
+        <v>26734.79408608879</v>
       </c>
       <c r="D4">
-        <v>23181.27677077926</v>
+        <v>23224.90608608879</v>
       </c>
       <c r="E4">
-        <v>-14023.692</v>
+        <v>-13735.188</v>
       </c>
       <c r="F4">
-        <v>577.008</v>
+        <v>865.5120000000001</v>
       </c>
       <c r="G4">
         <v>4375.4</v>
@@ -1621,28 +1621,28 @@
         <v>3004.7</v>
       </c>
       <c r="M4">
-        <v>38.15810321924126</v>
+        <v>57.23715482886189</v>
       </c>
       <c r="N4">
-        <v>2966.541896780759</v>
+        <v>2947.462845171138</v>
       </c>
       <c r="O4">
-        <v>741.6354741951897</v>
+        <v>736.8657112927845</v>
       </c>
       <c r="P4">
-        <v>2224.906422585569</v>
+        <v>2210.597133878353</v>
       </c>
       <c r="Q4">
-        <v>5274.206422585569</v>
+        <v>5259.897133878354</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1071608150447021</v>
+        <v>0.107637638453328</v>
       </c>
       <c r="T4">
-        <v>0.9492322936638684</v>
+        <v>0.9566086001472948</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>78.74343184031424</v>
+        <v>52.49562122687616</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1058964562994802</v>
+        <v>0.105783349188651</v>
       </c>
       <c r="C5">
-        <v>26734.79408608879</v>
+        <v>26490.08393992007</v>
       </c>
       <c r="D5">
-        <v>23224.90608608879</v>
+        <v>23268.69993992006</v>
       </c>
       <c r="E5">
-        <v>-13735.188</v>
+        <v>-13446.684</v>
       </c>
       <c r="F5">
-        <v>865.5120000000001</v>
+        <v>1154.016</v>
       </c>
       <c r="G5">
         <v>4375.4</v>
@@ -1703,28 +1703,28 @@
         <v>3004.7</v>
       </c>
       <c r="M5">
-        <v>57.23715482886189</v>
+        <v>76.31620643848252</v>
       </c>
       <c r="N5">
-        <v>2947.462845171138</v>
+        <v>2928.383793561517</v>
       </c>
       <c r="O5">
-        <v>736.8657112927845</v>
+        <v>732.0959483903794</v>
       </c>
       <c r="P5">
-        <v>2210.597133878353</v>
+        <v>2196.287845171138</v>
       </c>
       <c r="Q5">
-        <v>5259.897133878354</v>
+        <v>5245.587845171138</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.107637638453328</v>
+        <v>0.1081243956829669</v>
       </c>
       <c r="T5">
-        <v>0.9566086001472948</v>
+        <v>0.9641385796824593</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.49562122687616</v>
+        <v>39.37171592015712</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.105783349188651</v>
+        <v>0.1056702420778217</v>
       </c>
       <c r="C6">
-        <v>26490.08393992007</v>
+        <v>26245.53926481366</v>
       </c>
       <c r="D6">
-        <v>23268.69993992006</v>
+        <v>23312.65926481366</v>
       </c>
       <c r="E6">
-        <v>-13446.684</v>
+        <v>-13158.18</v>
       </c>
       <c r="F6">
-        <v>1154.016</v>
+        <v>1442.52</v>
       </c>
       <c r="G6">
         <v>4375.4</v>
@@ -1785,28 +1785,28 @@
         <v>3004.7</v>
       </c>
       <c r="M6">
-        <v>76.31620643848252</v>
+        <v>95.39525804810316</v>
       </c>
       <c r="N6">
-        <v>2928.383793561517</v>
+        <v>2909.304741951897</v>
       </c>
       <c r="O6">
-        <v>732.0959483903794</v>
+        <v>727.3261854879742</v>
       </c>
       <c r="P6">
-        <v>2196.287845171138</v>
+        <v>2181.978556463922</v>
       </c>
       <c r="Q6">
-        <v>5245.587845171138</v>
+        <v>5231.278556463923</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1081243956829669</v>
+        <v>0.1086214004332298</v>
       </c>
       <c r="T6">
-        <v>0.9641385796824593</v>
+        <v>0.9718270851025745</v>
       </c>
       <c r="U6">
         <v>0.06613097776675758</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.37171592015712</v>
+        <v>31.49737273612569</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1056702420778217</v>
+        <v>0.1055571349669925</v>
       </c>
       <c r="C7">
-        <v>26245.53926481366</v>
+        <v>26001.16100037052</v>
       </c>
       <c r="D7">
-        <v>23312.65926481366</v>
+        <v>23356.78500037052</v>
       </c>
       <c r="E7">
-        <v>-13158.18</v>
+        <v>-12869.676</v>
       </c>
       <c r="F7">
-        <v>1442.52</v>
+        <v>1731.024</v>
       </c>
       <c r="G7">
         <v>4375.4</v>
@@ -1867,28 +1867,28 @@
         <v>3004.7</v>
       </c>
       <c r="M7">
-        <v>95.39525804810316</v>
+        <v>114.4743096577238</v>
       </c>
       <c r="N7">
-        <v>2909.304741951897</v>
+        <v>2890.225690342276</v>
       </c>
       <c r="O7">
-        <v>727.3261854879742</v>
+        <v>722.556422585569</v>
       </c>
       <c r="P7">
-        <v>2181.978556463922</v>
+        <v>2167.669267756707</v>
       </c>
       <c r="Q7">
-        <v>5231.278556463923</v>
+        <v>5216.969267756707</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1086214004332298</v>
+        <v>0.1091289797526472</v>
       </c>
       <c r="T7">
-        <v>0.9718270851025745</v>
+        <v>0.9796791757443944</v>
       </c>
       <c r="U7">
         <v>0.06613097776675758</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.49737273612569</v>
+        <v>26.24781061343808</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1055571349669925</v>
+        <v>0.1054440278561632</v>
       </c>
       <c r="C8">
-        <v>26001.16100037052</v>
+        <v>25756.95009331896</v>
       </c>
       <c r="D8">
-        <v>23356.78500037053</v>
+        <v>23401.07809331896</v>
       </c>
       <c r="E8">
-        <v>-12869.676</v>
+        <v>-12581.172</v>
       </c>
       <c r="F8">
-        <v>1731.024</v>
+        <v>2019.528</v>
       </c>
       <c r="G8">
         <v>4375.4</v>
@@ -1949,28 +1949,28 @@
         <v>3004.7</v>
       </c>
       <c r="M8">
-        <v>114.4743096577238</v>
+        <v>133.5533612673444</v>
       </c>
       <c r="N8">
-        <v>2890.225690342276</v>
+        <v>2871.146638732655</v>
       </c>
       <c r="O8">
-        <v>722.556422585569</v>
+        <v>717.7866596831639</v>
       </c>
       <c r="P8">
-        <v>2167.669267756707</v>
+        <v>2153.359979049492</v>
       </c>
       <c r="Q8">
-        <v>5216.969267756707</v>
+        <v>5202.659979049492</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1091289797526472</v>
+        <v>0.1096474747563532</v>
       </c>
       <c r="T8">
-        <v>0.9796791757443944</v>
+        <v>0.9877001285505546</v>
       </c>
       <c r="U8">
         <v>0.06613097776675758</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.24781061343808</v>
+        <v>22.49812338294693</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1054440278561632</v>
+        <v>0.105330920745334</v>
       </c>
       <c r="C9">
-        <v>25756.95009331896</v>
+        <v>25512.90749758224</v>
       </c>
       <c r="D9">
-        <v>23401.07809331896</v>
+        <v>23445.53949758225</v>
       </c>
       <c r="E9">
-        <v>-12581.172</v>
+        <v>-12292.668</v>
       </c>
       <c r="F9">
-        <v>2019.528</v>
+        <v>2308.032</v>
       </c>
       <c r="G9">
         <v>4375.4</v>
@@ -2031,28 +2031,28 @@
         <v>3004.7</v>
       </c>
       <c r="M9">
-        <v>133.5533612673444</v>
+        <v>152.632412876965</v>
       </c>
       <c r="N9">
-        <v>2871.146638732655</v>
+        <v>2852.067587123035</v>
       </c>
       <c r="O9">
-        <v>717.7866596831639</v>
+        <v>713.0168967807587</v>
       </c>
       <c r="P9">
-        <v>2153.359979049492</v>
+        <v>2139.050690342276</v>
       </c>
       <c r="Q9">
-        <v>5202.659979049492</v>
+        <v>5188.350690342277</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1096474747563532</v>
+        <v>0.1101772413905745</v>
       </c>
       <c r="T9">
-        <v>0.9877001285505546</v>
+        <v>0.9958954498959791</v>
       </c>
       <c r="U9">
         <v>0.06613097776675758</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.49812338294693</v>
+        <v>19.68585796007856</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.105330920745334</v>
+        <v>0.1052178136345048</v>
       </c>
       <c r="C10">
-        <v>25512.90749758224</v>
+        <v>25269.03417434725</v>
       </c>
       <c r="D10">
-        <v>23445.53949758225</v>
+        <v>23490.17017434725</v>
       </c>
       <c r="E10">
-        <v>-12292.668</v>
+        <v>-12004.164</v>
       </c>
       <c r="F10">
-        <v>2308.032</v>
+        <v>2596.536</v>
       </c>
       <c r="G10">
         <v>4375.4</v>
@@ -2113,28 +2113,28 @@
         <v>3004.7</v>
       </c>
       <c r="M10">
-        <v>152.632412876965</v>
+        <v>171.7114644865857</v>
       </c>
       <c r="N10">
-        <v>2852.067587123035</v>
+        <v>2832.988535513414</v>
       </c>
       <c r="O10">
-        <v>713.0168967807587</v>
+        <v>708.2471338783536</v>
       </c>
       <c r="P10">
-        <v>2139.050690342276</v>
+        <v>2124.741401635061</v>
       </c>
       <c r="Q10">
-        <v>5188.350690342277</v>
+        <v>5174.041401635061</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1101772413905745</v>
+        <v>0.110718651247526</v>
       </c>
       <c r="T10">
-        <v>0.9958954498959791</v>
+        <v>1.00427088819405</v>
       </c>
       <c r="U10">
         <v>0.06613097776675758</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.68585796007856</v>
+        <v>17.49854040895872</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1052178136345048</v>
+        <v>0.1051047065236755</v>
       </c>
       <c r="C11">
-        <v>25269.03417434725</v>
+        <v>25025.33109213354</v>
       </c>
       <c r="D11">
-        <v>23490.17017434725</v>
+        <v>23534.97109213355</v>
       </c>
       <c r="E11">
-        <v>-12004.164</v>
+        <v>-11715.66</v>
       </c>
       <c r="F11">
-        <v>2596.536</v>
+        <v>2885.04</v>
       </c>
       <c r="G11">
         <v>4375.4</v>
@@ -2195,28 +2195,28 @@
         <v>3004.7</v>
       </c>
       <c r="M11">
-        <v>171.7114644865857</v>
+        <v>190.7905160962063</v>
       </c>
       <c r="N11">
-        <v>2832.988535513414</v>
+        <v>2813.909483903793</v>
       </c>
       <c r="O11">
-        <v>708.2471338783536</v>
+        <v>703.4773709759484</v>
       </c>
       <c r="P11">
-        <v>2124.741401635061</v>
+        <v>2110.432112927845</v>
       </c>
       <c r="Q11">
-        <v>5174.041401635061</v>
+        <v>5159.732112927845</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.110718651247526</v>
+        <v>0.1112720924346319</v>
       </c>
       <c r="T11">
-        <v>1.00427088819405</v>
+        <v>1.01283244734319</v>
       </c>
       <c r="U11">
         <v>0.06613097776675758</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.49854040895872</v>
+        <v>15.74868636806285</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1051047065236755</v>
+        <v>0.1049915994128463</v>
       </c>
       <c r="C12">
-        <v>25025.33109213354</v>
+        <v>24781.79922686357</v>
       </c>
       <c r="D12">
-        <v>23534.97109213355</v>
+        <v>23579.94322686357</v>
       </c>
       <c r="E12">
-        <v>-11715.66</v>
+        <v>-11427.156</v>
       </c>
       <c r="F12">
-        <v>2885.04</v>
+        <v>3173.544</v>
       </c>
       <c r="G12">
         <v>4375.4</v>
@@ -2277,28 +2277,28 @@
         <v>3004.7</v>
       </c>
       <c r="M12">
-        <v>190.7905160962063</v>
+        <v>209.8695677058269</v>
       </c>
       <c r="N12">
-        <v>2813.909483903793</v>
+        <v>2794.830432294173</v>
       </c>
       <c r="O12">
-        <v>703.4773709759484</v>
+        <v>698.7076080735433</v>
       </c>
       <c r="P12">
-        <v>2110.432112927845</v>
+        <v>2096.12282422063</v>
       </c>
       <c r="Q12">
-        <v>5159.732112927845</v>
+        <v>5145.42282422063</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1112720924346319</v>
+        <v>0.111837970502347</v>
       </c>
       <c r="T12">
-        <v>1.01283244734319</v>
+        <v>1.02158640107995</v>
       </c>
       <c r="U12">
         <v>0.06613097776675758</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.74868636806285</v>
+        <v>14.31698760732986</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1049915994128463</v>
+        <v>0.1048784923020171</v>
       </c>
       <c r="C13">
-        <v>24781.79922686357</v>
+        <v>24538.43956193349</v>
       </c>
       <c r="D13">
-        <v>23579.94322686357</v>
+        <v>23625.08756193349</v>
       </c>
       <c r="E13">
-        <v>-11427.156</v>
+        <v>-11138.652</v>
       </c>
       <c r="F13">
-        <v>3173.544</v>
+        <v>3462.048</v>
       </c>
       <c r="G13">
         <v>4375.4</v>
@@ -2359,28 +2359,28 @@
         <v>3004.7</v>
       </c>
       <c r="M13">
-        <v>209.8695677058269</v>
+        <v>228.9486193154476</v>
       </c>
       <c r="N13">
-        <v>2794.830432294173</v>
+        <v>2775.751380684552</v>
       </c>
       <c r="O13">
-        <v>698.7076080735433</v>
+        <v>693.9378451711381</v>
       </c>
       <c r="P13">
-        <v>2096.12282422063</v>
+        <v>2081.813535513414</v>
       </c>
       <c r="Q13">
-        <v>5145.42282422063</v>
+        <v>5131.113535513414</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.111837970502347</v>
+        <v>0.1124167094352374</v>
       </c>
       <c r="T13">
-        <v>1.02158640107995</v>
+        <v>1.030539308310728</v>
       </c>
       <c r="U13">
         <v>0.06613097776675758</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.31698760732986</v>
+        <v>13.12390530671904</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1048784923020171</v>
+        <v>0.1047653851911878</v>
       </c>
       <c r="C14">
-        <v>24538.43956193349</v>
+        <v>24295.25308828483</v>
       </c>
       <c r="D14">
-        <v>23625.08756193349</v>
+        <v>23670.40508828483</v>
       </c>
       <c r="E14">
-        <v>-11138.652</v>
+        <v>-10850.148</v>
       </c>
       <c r="F14">
-        <v>3462.048</v>
+        <v>3750.552</v>
       </c>
       <c r="G14">
         <v>4375.4</v>
@@ -2441,28 +2441,28 @@
         <v>3004.7</v>
       </c>
       <c r="M14">
-        <v>228.9486193154476</v>
+        <v>248.0276709250682</v>
       </c>
       <c r="N14">
-        <v>2775.751380684552</v>
+        <v>2756.672329074931</v>
       </c>
       <c r="O14">
-        <v>693.9378451711381</v>
+        <v>689.1680822687329</v>
       </c>
       <c r="P14">
-        <v>2081.813535513414</v>
+        <v>2067.504246806198</v>
       </c>
       <c r="Q14">
-        <v>5131.113535513414</v>
+        <v>5116.804246806199</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1124167094352374</v>
+        <v>0.1130087527114126</v>
       </c>
       <c r="T14">
-        <v>1.030539308310728</v>
+        <v>1.039698029500834</v>
       </c>
       <c r="U14">
         <v>0.06613097776675758</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.12390530671904</v>
+        <v>12.11437412927912</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1047653851911878</v>
+        <v>0.1046522780803586</v>
       </c>
       <c r="C15">
-        <v>24295.25308828483</v>
+        <v>24052.24080447699</v>
       </c>
       <c r="D15">
-        <v>23670.40508828483</v>
+        <v>23715.89680447699</v>
       </c>
       <c r="E15">
-        <v>-10850.148</v>
+        <v>-10561.644</v>
       </c>
       <c r="F15">
-        <v>3750.552</v>
+        <v>4039.056</v>
       </c>
       <c r="G15">
         <v>4375.4</v>
@@ -2523,28 +2523,28 @@
         <v>3004.7</v>
       </c>
       <c r="M15">
-        <v>248.0276709250682</v>
+        <v>267.1067225346889</v>
       </c>
       <c r="N15">
-        <v>2756.672329074931</v>
+        <v>2737.593277465311</v>
       </c>
       <c r="O15">
-        <v>689.1680822687329</v>
+        <v>684.3983193663278</v>
       </c>
       <c r="P15">
-        <v>2067.504246806198</v>
+        <v>2053.194958098983</v>
       </c>
       <c r="Q15">
-        <v>5116.804246806199</v>
+        <v>5102.494958098983</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1130087527114126</v>
+        <v>0.113614564435871</v>
       </c>
       <c r="T15">
-        <v>1.039698029500834</v>
+        <v>1.049069744206989</v>
       </c>
       <c r="U15">
         <v>0.06613097776675758</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.11437412927912</v>
+        <v>11.24906169147346</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1046522780803586</v>
+        <v>0.1045391709695293</v>
       </c>
       <c r="C16">
-        <v>24052.24080447699</v>
+        <v>23809.40371676062</v>
       </c>
       <c r="D16">
-        <v>23715.89680447699</v>
+        <v>23761.56371676062</v>
       </c>
       <c r="E16">
-        <v>-10561.644</v>
+        <v>-10273.14</v>
       </c>
       <c r="F16">
-        <v>4039.056</v>
+        <v>4327.560000000001</v>
       </c>
       <c r="G16">
         <v>4375.4</v>
@@ -2605,28 +2605,28 @@
         <v>3004.7</v>
       </c>
       <c r="M16">
-        <v>267.1067225346889</v>
+        <v>286.1857741443095</v>
       </c>
       <c r="N16">
-        <v>2737.593277465311</v>
+        <v>2718.51422585569</v>
       </c>
       <c r="O16">
-        <v>684.3983193663278</v>
+        <v>679.6285564639226</v>
       </c>
       <c r="P16">
-        <v>2053.194958098983</v>
+        <v>2038.885669391768</v>
       </c>
       <c r="Q16">
-        <v>5102.494958098983</v>
+        <v>5088.185669391768</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.113614564435871</v>
+        <v>0.114234630553846</v>
       </c>
       <c r="T16">
-        <v>1.049069744206989</v>
+        <v>1.058661969847406</v>
       </c>
       <c r="U16">
         <v>0.06613097776675758</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.24906169147346</v>
+        <v>10.49912424537523</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1045391709695293</v>
+        <v>0.1044260638587001</v>
       </c>
       <c r="C17">
-        <v>23809.40371676062</v>
+        <v>23566.7428391518</v>
       </c>
       <c r="D17">
-        <v>23761.56371676062</v>
+        <v>23807.4068391518</v>
       </c>
       <c r="E17">
-        <v>-10273.14</v>
+        <v>-9984.636000000002</v>
       </c>
       <c r="F17">
-        <v>4327.56</v>
+        <v>4616.064</v>
       </c>
       <c r="G17">
         <v>4375.4</v>
@@ -2687,28 +2687,28 @@
         <v>3004.7</v>
       </c>
       <c r="M17">
-        <v>286.1857741443094</v>
+        <v>305.2648257539301</v>
       </c>
       <c r="N17">
-        <v>2718.51422585569</v>
+        <v>2699.43517424607</v>
       </c>
       <c r="O17">
-        <v>679.6285564639226</v>
+        <v>674.8587935615175</v>
       </c>
       <c r="P17">
-        <v>2038.885669391768</v>
+        <v>2024.576380684553</v>
       </c>
       <c r="Q17">
-        <v>5088.185669391768</v>
+        <v>5073.876380684553</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.114234630553846</v>
+        <v>0.1148694601508205</v>
       </c>
       <c r="T17">
-        <v>1.058661969847406</v>
+        <v>1.068482581812596</v>
       </c>
       <c r="U17">
         <v>0.06613097776675758</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.49912424537523</v>
+        <v>9.842928980039281</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1044260638587001</v>
+        <v>0.1043129567478709</v>
       </c>
       <c r="C18">
-        <v>23566.7428391518</v>
+        <v>23324.25919350708</v>
       </c>
       <c r="D18">
-        <v>23807.4068391518</v>
+        <v>23853.42719350708</v>
       </c>
       <c r="E18">
-        <v>-9984.636000000002</v>
+        <v>-9696.132000000001</v>
       </c>
       <c r="F18">
-        <v>4616.064</v>
+        <v>4904.568</v>
       </c>
       <c r="G18">
         <v>4375.4</v>
@@ -2769,28 +2769,28 @@
         <v>3004.7</v>
       </c>
       <c r="M18">
-        <v>305.2648257539301</v>
+        <v>324.3438773635507</v>
       </c>
       <c r="N18">
-        <v>2699.43517424607</v>
+        <v>2680.356122636449</v>
       </c>
       <c r="O18">
-        <v>674.8587935615175</v>
+        <v>670.0890306591123</v>
       </c>
       <c r="P18">
-        <v>2024.576380684553</v>
+        <v>2010.267091977337</v>
       </c>
       <c r="Q18">
-        <v>5073.876380684553</v>
+        <v>5059.567091977337</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1148694601508205</v>
+        <v>0.1155195868465172</v>
       </c>
       <c r="T18">
-        <v>1.068482581812596</v>
+        <v>1.078539835029958</v>
       </c>
       <c r="U18">
         <v>0.06613097776675758</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.842928980039281</v>
+        <v>9.263933157684029</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1043129567478709</v>
+        <v>0.1041998496370416</v>
       </c>
       <c r="C19">
-        <v>23324.25919350708</v>
+        <v>23081.95380959944</v>
       </c>
       <c r="D19">
-        <v>23853.42719350708</v>
+        <v>23899.62580959945</v>
       </c>
       <c r="E19">
-        <v>-9696.132000000001</v>
+        <v>-9407.628000000001</v>
       </c>
       <c r="F19">
-        <v>4904.568</v>
+        <v>5193.072000000001</v>
       </c>
       <c r="G19">
         <v>4375.4</v>
@@ -2851,28 +2851,28 @@
         <v>3004.7</v>
       </c>
       <c r="M19">
-        <v>324.3438773635507</v>
+        <v>343.4229289731714</v>
       </c>
       <c r="N19">
-        <v>2680.356122636449</v>
+        <v>2661.277071026828</v>
       </c>
       <c r="O19">
-        <v>670.0890306591123</v>
+        <v>665.3192677567071</v>
       </c>
       <c r="P19">
-        <v>2010.267091977337</v>
+        <v>1995.957803270121</v>
       </c>
       <c r="Q19">
-        <v>5059.567091977337</v>
+        <v>5045.257803270121</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1155195868465172</v>
+        <v>0.1161855702908895</v>
       </c>
       <c r="T19">
-        <v>1.078539835029958</v>
+        <v>1.088842387106281</v>
       </c>
       <c r="U19">
         <v>0.06613097776675758</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.263933157684029</v>
+        <v>8.749270204479359</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1041998496370417</v>
+        <v>0.1043004925262124</v>
       </c>
       <c r="C20">
-        <v>23081.95380959944</v>
+        <v>22752.33344822008</v>
       </c>
       <c r="D20">
-        <v>23899.62580959944</v>
+        <v>23858.50944822008</v>
       </c>
       <c r="E20">
-        <v>-9407.628000000002</v>
+        <v>-9119.124000000003</v>
       </c>
       <c r="F20">
-        <v>5193.072</v>
+        <v>5481.576</v>
       </c>
       <c r="G20">
         <v>4375.4</v>
@@ -2933,45 +2933,45 @@
         <v>3004.7</v>
       </c>
       <c r="M20">
-        <v>343.4229289731713</v>
+        <v>370.724344582792</v>
       </c>
       <c r="N20">
-        <v>2661.277071026829</v>
+        <v>2633.975655417208</v>
       </c>
       <c r="O20">
-        <v>665.3192677567072</v>
+        <v>658.4939138543019</v>
       </c>
       <c r="P20">
-        <v>1995.957803270122</v>
+        <v>1975.481741562906</v>
       </c>
       <c r="Q20">
-        <v>5045.257803270122</v>
+        <v>5024.781741562906</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1161855702908895</v>
+        <v>0.1168679977709252</v>
       </c>
       <c r="T20">
-        <v>1.088842387106281</v>
+        <v>1.099399323184488</v>
       </c>
       <c r="U20">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04959823332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>8.749270204479362</v>
+        <v>8.104943858978151</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1043004925262124</v>
+        <v>0.1041986354153832</v>
       </c>
       <c r="C21">
-        <v>22752.33344822008</v>
+        <v>22505.44272948604</v>
       </c>
       <c r="D21">
-        <v>23858.50944822008</v>
+        <v>23900.12272948604</v>
       </c>
       <c r="E21">
-        <v>-9119.124000000003</v>
+        <v>-8830.620000000003</v>
       </c>
       <c r="F21">
-        <v>5481.576</v>
+        <v>5770.080000000001</v>
       </c>
       <c r="G21">
         <v>4375.4</v>
@@ -3015,28 +3015,28 @@
         <v>3004.7</v>
       </c>
       <c r="M21">
-        <v>370.724344582792</v>
+        <v>390.2361521924126</v>
       </c>
       <c r="N21">
-        <v>2633.975655417208</v>
+        <v>2614.463847807587</v>
       </c>
       <c r="O21">
-        <v>658.4939138543019</v>
+        <v>653.6159619518968</v>
       </c>
       <c r="P21">
-        <v>1975.481741562906</v>
+        <v>1960.84788585569</v>
       </c>
       <c r="Q21">
-        <v>5024.781741562906</v>
+        <v>5010.147885855691</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1168679977709252</v>
+        <v>0.1175674859379619</v>
       </c>
       <c r="T21">
-        <v>1.099399323184488</v>
+        <v>1.11022018266465</v>
       </c>
       <c r="U21">
         <v>0.06763097776675758</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.104943858978151</v>
+        <v>7.699696666029243</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1041986354153832</v>
+        <v>0.1040967783045539</v>
       </c>
       <c r="C22">
-        <v>22505.44272948604</v>
+        <v>22258.6974256008</v>
       </c>
       <c r="D22">
-        <v>23900.12272948604</v>
+        <v>23941.8814256008</v>
       </c>
       <c r="E22">
-        <v>-8830.620000000003</v>
+        <v>-8542.116000000002</v>
       </c>
       <c r="F22">
-        <v>5770.080000000001</v>
+        <v>6058.584000000001</v>
       </c>
       <c r="G22">
         <v>4375.4</v>
@@ -3097,28 +3097,28 @@
         <v>3004.7</v>
       </c>
       <c r="M22">
-        <v>390.2361521924126</v>
+        <v>409.7479598020333</v>
       </c>
       <c r="N22">
-        <v>2614.463847807587</v>
+        <v>2594.952040197967</v>
       </c>
       <c r="O22">
-        <v>653.6159619518968</v>
+        <v>648.7380100494917</v>
       </c>
       <c r="P22">
-        <v>1960.84788585569</v>
+        <v>1946.214030148475</v>
       </c>
       <c r="Q22">
-        <v>5010.147885855691</v>
+        <v>4995.514030148475</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1175674859379619</v>
+        <v>0.1182846826661894</v>
       </c>
       <c r="T22">
-        <v>1.11022018266465</v>
+        <v>1.121314987954437</v>
       </c>
       <c r="U22">
         <v>0.06763097776675758</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.699696666029243</v>
+        <v>7.333044443837374</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1040967783045539</v>
+        <v>0.1039949211937247</v>
       </c>
       <c r="C23">
-        <v>22258.69742560081</v>
+        <v>22012.09830011227</v>
       </c>
       <c r="D23">
-        <v>23941.8814256008</v>
+        <v>23983.78630011227</v>
       </c>
       <c r="E23">
-        <v>-8542.116000000002</v>
+        <v>-8253.612000000001</v>
       </c>
       <c r="F23">
-        <v>6058.584</v>
+        <v>6347.088000000001</v>
       </c>
       <c r="G23">
         <v>4375.4</v>
@@ -3179,28 +3179,28 @@
         <v>3004.7</v>
       </c>
       <c r="M23">
-        <v>409.7479598020332</v>
+        <v>429.2597674116539</v>
       </c>
       <c r="N23">
-        <v>2594.952040197967</v>
+        <v>2575.440232588346</v>
       </c>
       <c r="O23">
-        <v>648.7380100494917</v>
+        <v>643.8600581470864</v>
       </c>
       <c r="P23">
-        <v>1946.214030148475</v>
+        <v>1931.580174441259</v>
       </c>
       <c r="Q23">
-        <v>4995.514030148475</v>
+        <v>4980.880174441259</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1182846826661894</v>
+        <v>0.119020269054115</v>
       </c>
       <c r="T23">
-        <v>1.121314987954437</v>
+        <v>1.132694275431141</v>
       </c>
       <c r="U23">
         <v>0.06763097776675758</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.333044443837375</v>
+        <v>6.999724241844765</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1039949211937247</v>
+        <v>0.1038930640828955</v>
       </c>
       <c r="C24">
-        <v>22012.09830011227</v>
+        <v>21765.64612192337</v>
       </c>
       <c r="D24">
-        <v>23983.78630011227</v>
+        <v>24025.83812192337</v>
       </c>
       <c r="E24">
-        <v>-8253.612000000001</v>
+        <v>-7965.108000000002</v>
       </c>
       <c r="F24">
-        <v>6347.088000000001</v>
+        <v>6635.592000000001</v>
       </c>
       <c r="G24">
         <v>4375.4</v>
@@ -3261,28 +3261,28 @@
         <v>3004.7</v>
       </c>
       <c r="M24">
-        <v>429.2597674116539</v>
+        <v>448.7715750212745</v>
       </c>
       <c r="N24">
-        <v>2575.440232588346</v>
+        <v>2555.928424978725</v>
       </c>
       <c r="O24">
-        <v>643.8600581470864</v>
+        <v>638.9821062446813</v>
       </c>
       <c r="P24">
-        <v>1931.580174441259</v>
+        <v>1916.946318734044</v>
       </c>
       <c r="Q24">
-        <v>4980.880174441259</v>
+        <v>4966.246318734044</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.119020269054115</v>
+        <v>0.1197749615819867</v>
       </c>
       <c r="T24">
-        <v>1.132694275431141</v>
+        <v>1.144369128816331</v>
       </c>
       <c r="U24">
         <v>0.06763097776675758</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.999724241844765</v>
+        <v>6.695388405242819</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1038930640828955</v>
+        <v>0.1040972069720662</v>
       </c>
       <c r="C25">
-        <v>21765.64612192337</v>
+        <v>21393.00937759981</v>
       </c>
       <c r="D25">
-        <v>24025.83812192337</v>
+        <v>23941.70537759981</v>
       </c>
       <c r="E25">
-        <v>-7965.108000000002</v>
+        <v>-7676.604000000002</v>
       </c>
       <c r="F25">
-        <v>6635.592000000001</v>
+        <v>6924.096</v>
       </c>
       <c r="G25">
         <v>4375.4</v>
@@ -3343,45 +3343,45 @@
         <v>3004.7</v>
       </c>
       <c r="M25">
-        <v>448.7715750212745</v>
+        <v>480.0543458308951</v>
       </c>
       <c r="N25">
-        <v>2555.928424978725</v>
+        <v>2524.645654169105</v>
       </c>
       <c r="O25">
-        <v>638.9821062446813</v>
+        <v>631.1614135422761</v>
       </c>
       <c r="P25">
-        <v>1916.946318734044</v>
+        <v>1893.484240626829</v>
       </c>
       <c r="Q25">
-        <v>4966.246318734044</v>
+        <v>4942.784240626828</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1197749615819867</v>
+        <v>0.1205495144395393</v>
       </c>
       <c r="T25">
-        <v>1.144369128816331</v>
+        <v>1.156351215185342</v>
       </c>
       <c r="U25">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.05072323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.695388405242819</v>
+        <v>6.259083010277426</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1040972069720662</v>
+        <v>0.104008099861237</v>
       </c>
       <c r="C26">
-        <v>21393.00937759982</v>
+        <v>21141.15622515554</v>
       </c>
       <c r="D26">
-        <v>23941.70537759982</v>
+        <v>23978.35622515554</v>
       </c>
       <c r="E26">
-        <v>-7676.604000000002</v>
+        <v>-7388.100000000002</v>
       </c>
       <c r="F26">
-        <v>6924.096</v>
+        <v>7212.6</v>
       </c>
       <c r="G26">
         <v>4375.4</v>
@@ -3425,28 +3425,28 @@
         <v>3004.7</v>
       </c>
       <c r="M26">
-        <v>480.0543458308951</v>
+        <v>500.0566102405157</v>
       </c>
       <c r="N26">
-        <v>2524.645654169105</v>
+        <v>2504.643389759484</v>
       </c>
       <c r="O26">
-        <v>631.1614135422761</v>
+        <v>626.1608474398711</v>
       </c>
       <c r="P26">
-        <v>1893.484240626829</v>
+        <v>1878.482542319613</v>
       </c>
       <c r="Q26">
-        <v>4942.784240626828</v>
+        <v>4927.782542319614</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1205495144395393</v>
+        <v>0.1213447220399599</v>
       </c>
       <c r="T26">
-        <v>1.156351215185342</v>
+        <v>1.168652823857526</v>
       </c>
       <c r="U26">
         <v>0.06933097776675758</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.259083010277426</v>
+        <v>6.00871968986633</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.104008099861237</v>
+        <v>0.1039189927504077</v>
       </c>
       <c r="C27">
-        <v>21141.15622515554</v>
+        <v>20889.41545769871</v>
       </c>
       <c r="D27">
-        <v>23978.35622515554</v>
+        <v>24015.11945769871</v>
       </c>
       <c r="E27">
-        <v>-7388.100000000002</v>
+        <v>-7099.596000000002</v>
       </c>
       <c r="F27">
-        <v>7212.6</v>
+        <v>7501.104</v>
       </c>
       <c r="G27">
         <v>4375.4</v>
@@ -3507,28 +3507,28 @@
         <v>3004.7</v>
       </c>
       <c r="M27">
-        <v>500.0566102405157</v>
+        <v>520.0588746501363</v>
       </c>
       <c r="N27">
-        <v>2504.643389759484</v>
+        <v>2484.641125349864</v>
       </c>
       <c r="O27">
-        <v>626.1608474398711</v>
+        <v>621.1602813374659</v>
       </c>
       <c r="P27">
-        <v>1878.482542319613</v>
+        <v>1863.480844012398</v>
       </c>
       <c r="Q27">
-        <v>4927.782542319614</v>
+        <v>4912.780844012398</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1213447220399599</v>
+        <v>0.1221614217376892</v>
       </c>
       <c r="T27">
-        <v>1.168652823857526</v>
+        <v>1.18128690843977</v>
       </c>
       <c r="U27">
         <v>0.06933097776675758</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.00871968986633</v>
+        <v>5.777615086409933</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1039189927504077</v>
+        <v>0.1038298856395785</v>
       </c>
       <c r="C28">
-        <v>20889.41545769871</v>
+        <v>20637.78759294367</v>
       </c>
       <c r="D28">
-        <v>24015.11945769871</v>
+        <v>24051.99559294367</v>
       </c>
       <c r="E28">
-        <v>-7099.596000000002</v>
+        <v>-6811.092000000001</v>
       </c>
       <c r="F28">
-        <v>7501.104</v>
+        <v>7789.608000000001</v>
       </c>
       <c r="G28">
         <v>4375.4</v>
@@ -3589,28 +3589,28 @@
         <v>3004.7</v>
       </c>
       <c r="M28">
-        <v>520.0588746501363</v>
+        <v>540.061139059757</v>
       </c>
       <c r="N28">
-        <v>2484.641125349864</v>
+        <v>2464.638860940243</v>
       </c>
       <c r="O28">
-        <v>621.1602813374659</v>
+        <v>616.1597152350607</v>
       </c>
       <c r="P28">
-        <v>1863.480844012398</v>
+        <v>1848.479145705182</v>
       </c>
       <c r="Q28">
-        <v>4912.780844012398</v>
+        <v>4897.779145705183</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1221614217376892</v>
+        <v>0.1230004967696029</v>
       </c>
       <c r="T28">
-        <v>1.18128690843977</v>
+        <v>1.194267132325637</v>
       </c>
       <c r="U28">
         <v>0.06933097776675758</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.777615086409933</v>
+        <v>5.563629342468824</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1038298856395785</v>
+        <v>0.1039087785287493</v>
       </c>
       <c r="C29">
-        <v>20637.78759294367</v>
+        <v>20316.628777773</v>
       </c>
       <c r="D29">
-        <v>24051.99559294367</v>
+        <v>24019.340777773</v>
       </c>
       <c r="E29">
-        <v>-6811.092000000001</v>
+        <v>-6522.588000000002</v>
       </c>
       <c r="F29">
-        <v>7789.608000000001</v>
+        <v>8078.112000000001</v>
       </c>
       <c r="G29">
         <v>4375.4</v>
@@ -3671,45 +3671,45 @@
         <v>3004.7</v>
       </c>
       <c r="M29">
-        <v>540.061139059757</v>
+        <v>566.5258930693777</v>
       </c>
       <c r="N29">
-        <v>2464.638860940243</v>
+        <v>2438.174106930622</v>
       </c>
       <c r="O29">
-        <v>616.1597152350607</v>
+        <v>609.5435267326556</v>
       </c>
       <c r="P29">
-        <v>1848.479145705182</v>
+        <v>1828.630580197967</v>
       </c>
       <c r="Q29">
-        <v>4897.779145705183</v>
+        <v>4877.930580197966</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1230004967696029</v>
+        <v>0.1238628794412919</v>
       </c>
       <c r="T29">
-        <v>1.194267132325637</v>
+        <v>1.207607917986111</v>
       </c>
       <c r="U29">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.05199823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>5.563629342468824</v>
+        <v>5.303729338337655</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1039087785287493</v>
+        <v>0.10382567141792</v>
       </c>
       <c r="C30">
-        <v>20316.628777773</v>
+        <v>20062.52641358841</v>
       </c>
       <c r="D30">
-        <v>24019.340777773</v>
+        <v>24053.74241358841</v>
       </c>
       <c r="E30">
-        <v>-6522.588000000002</v>
+        <v>-6234.084000000001</v>
       </c>
       <c r="F30">
-        <v>8078.112000000001</v>
+        <v>8366.616000000002</v>
       </c>
       <c r="G30">
         <v>4375.4</v>
@@ -3753,28 +3753,28 @@
         <v>3004.7</v>
       </c>
       <c r="M30">
-        <v>566.5258930693777</v>
+        <v>586.7589606789984</v>
       </c>
       <c r="N30">
-        <v>2438.174106930622</v>
+        <v>2417.941039321001</v>
       </c>
       <c r="O30">
-        <v>609.5435267326556</v>
+        <v>604.4852598302504</v>
       </c>
       <c r="P30">
-        <v>1828.630580197967</v>
+        <v>1813.455779490751</v>
       </c>
       <c r="Q30">
-        <v>4877.930580197966</v>
+        <v>4862.755779490752</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1238628794412919</v>
+        <v>0.124749554582606</v>
       </c>
       <c r="T30">
-        <v>1.207607917986111</v>
+        <v>1.221324500425753</v>
       </c>
       <c r="U30">
         <v>0.07013097776675759</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.303729338337655</v>
+        <v>5.120842119774287</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.10382567141792</v>
+        <v>0.1037425643070908</v>
       </c>
       <c r="C31">
-        <v>20062.52641358841</v>
+        <v>19808.52273404418</v>
       </c>
       <c r="D31">
-        <v>24053.74241358841</v>
+        <v>24088.24273404418</v>
       </c>
       <c r="E31">
-        <v>-6234.084000000003</v>
+        <v>-5945.580000000002</v>
       </c>
       <c r="F31">
-        <v>8366.616</v>
+        <v>8655.120000000001</v>
       </c>
       <c r="G31">
         <v>4375.4</v>
@@ -3835,28 +3835,28 @@
         <v>3004.7</v>
       </c>
       <c r="M31">
-        <v>586.7589606789983</v>
+        <v>606.9920282886189</v>
       </c>
       <c r="N31">
-        <v>2417.941039321001</v>
+        <v>2397.707971711381</v>
       </c>
       <c r="O31">
-        <v>604.4852598302504</v>
+        <v>599.4269929278453</v>
       </c>
       <c r="P31">
-        <v>1813.455779490751</v>
+        <v>1798.280978783536</v>
       </c>
       <c r="Q31">
-        <v>4862.755779490752</v>
+        <v>4847.580978783536</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.124749554582606</v>
+        <v>0.1256615632993862</v>
       </c>
       <c r="T31">
-        <v>1.221324500425753</v>
+        <v>1.235432985220814</v>
       </c>
       <c r="U31">
         <v>0.07013097776675759</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.120842119774288</v>
+        <v>4.950147382448479</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1037425643070908</v>
+        <v>0.1036594571962615</v>
       </c>
       <c r="C32">
-        <v>19808.52273404418</v>
+        <v>19554.61816438086</v>
       </c>
       <c r="D32">
-        <v>24088.24273404418</v>
+        <v>24122.84216438085</v>
       </c>
       <c r="E32">
-        <v>-5945.580000000002</v>
+        <v>-5657.076000000003</v>
       </c>
       <c r="F32">
-        <v>8655.120000000001</v>
+        <v>8943.624</v>
       </c>
       <c r="G32">
         <v>4375.4</v>
@@ -3917,28 +3917,28 @@
         <v>3004.7</v>
       </c>
       <c r="M32">
-        <v>606.9920282886189</v>
+        <v>627.2250958982395</v>
       </c>
       <c r="N32">
-        <v>2397.707971711381</v>
+        <v>2377.47490410176</v>
       </c>
       <c r="O32">
-        <v>599.4269929278453</v>
+        <v>594.3687260254401</v>
       </c>
       <c r="P32">
-        <v>1798.280978783536</v>
+        <v>1783.10617807632</v>
       </c>
       <c r="Q32">
-        <v>4847.580978783536</v>
+        <v>4832.40617807632</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1256615632993862</v>
+        <v>0.1266000070514354</v>
       </c>
       <c r="T32">
-        <v>1.235432985220814</v>
+        <v>1.249950411604137</v>
       </c>
       <c r="U32">
         <v>0.07013097776675759</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.950147382448479</v>
+        <v>4.790465208821109</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1036594571962615</v>
+        <v>0.1035763500854323</v>
       </c>
       <c r="C33">
-        <v>19554.61816438086</v>
+        <v>19300.81313228567</v>
       </c>
       <c r="D33">
-        <v>24122.84216438085</v>
+        <v>24157.54113228567</v>
       </c>
       <c r="E33">
-        <v>-5657.076000000003</v>
+        <v>-5368.572000000002</v>
       </c>
       <c r="F33">
-        <v>8943.624</v>
+        <v>9232.128000000001</v>
       </c>
       <c r="G33">
         <v>4375.4</v>
@@ -3999,28 +3999,28 @@
         <v>3004.7</v>
       </c>
       <c r="M33">
-        <v>627.2250958982395</v>
+        <v>647.4581635078603</v>
       </c>
       <c r="N33">
-        <v>2377.47490410176</v>
+        <v>2357.24183649214</v>
       </c>
       <c r="O33">
-        <v>594.3687260254401</v>
+        <v>589.3104591230349</v>
       </c>
       <c r="P33">
-        <v>1783.10617807632</v>
+        <v>1767.931377369105</v>
       </c>
       <c r="Q33">
-        <v>4832.40617807632</v>
+        <v>4817.231377369105</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1266000070514354</v>
+        <v>0.1275660520903096</v>
       </c>
       <c r="T33">
-        <v>1.249950411604137</v>
+        <v>1.264894821116382</v>
       </c>
       <c r="U33">
         <v>0.07013097776675759</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.790465208821109</v>
+        <v>4.640763171045448</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1035763500854323</v>
+        <v>0.1034932429746031</v>
       </c>
       <c r="C34">
-        <v>19300.81313228567</v>
+        <v>19047.10806791017</v>
       </c>
       <c r="D34">
-        <v>24157.54113228567</v>
+        <v>24192.34006791017</v>
       </c>
       <c r="E34">
-        <v>-5368.572000000002</v>
+        <v>-5080.068000000001</v>
       </c>
       <c r="F34">
-        <v>9232.128000000001</v>
+        <v>9520.632000000001</v>
       </c>
       <c r="G34">
         <v>4375.4</v>
@@ -4081,28 +4081,28 @@
         <v>3004.7</v>
       </c>
       <c r="M34">
-        <v>647.4581635078603</v>
+        <v>667.6912311174809</v>
       </c>
       <c r="N34">
-        <v>2357.24183649214</v>
+        <v>2337.008768882519</v>
       </c>
       <c r="O34">
-        <v>589.3104591230349</v>
+        <v>584.2521922206297</v>
       </c>
       <c r="P34">
-        <v>1767.931377369105</v>
+        <v>1752.756576661889</v>
       </c>
       <c r="Q34">
-        <v>4817.231377369105</v>
+        <v>4802.056576661889</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1275660520903096</v>
+        <v>0.1285609342945233</v>
       </c>
       <c r="T34">
-        <v>1.264894821116382</v>
+        <v>1.280285332405111</v>
       </c>
       <c r="U34">
         <v>0.07013097776675759</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.640763171045448</v>
+        <v>4.500133984044071</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1034932429746031</v>
+        <v>0.1034101358637738</v>
       </c>
       <c r="C35">
-        <v>19047.10806791017</v>
+        <v>18793.50340388808</v>
       </c>
       <c r="D35">
-        <v>24192.34006791017</v>
+        <v>24227.23940388808</v>
       </c>
       <c r="E35">
-        <v>-5080.068000000001</v>
+        <v>-4791.564000000002</v>
       </c>
       <c r="F35">
-        <v>9520.632000000001</v>
+        <v>9809.136</v>
       </c>
       <c r="G35">
         <v>4375.4</v>
@@ -4163,28 +4163,28 @@
         <v>3004.7</v>
       </c>
       <c r="M35">
-        <v>667.6912311174809</v>
+        <v>687.9242987271015</v>
       </c>
       <c r="N35">
-        <v>2337.008768882519</v>
+        <v>2316.775701272898</v>
       </c>
       <c r="O35">
-        <v>584.2521922206297</v>
+        <v>579.1939253182246</v>
       </c>
       <c r="P35">
-        <v>1752.756576661889</v>
+        <v>1737.581775954674</v>
       </c>
       <c r="Q35">
-        <v>4802.056576661889</v>
+        <v>4786.881775954675</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1285609342945233</v>
+        <v>0.1295859644443192</v>
       </c>
       <c r="T35">
-        <v>1.280285332405111</v>
+        <v>1.296142222823802</v>
       </c>
       <c r="U35">
         <v>0.07013097776675759</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.500133984044071</v>
+        <v>4.367777102160423</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1034101358637738</v>
+        <v>0.1035895287529446</v>
       </c>
       <c r="C36">
-        <v>18793.50340388808</v>
+        <v>18429.7921030659</v>
       </c>
       <c r="D36">
-        <v>24227.23940388808</v>
+        <v>24152.0321030659</v>
       </c>
       <c r="E36">
-        <v>-4791.564000000002</v>
+        <v>-4503.060000000001</v>
       </c>
       <c r="F36">
-        <v>9809.136</v>
+        <v>10097.64</v>
       </c>
       <c r="G36">
         <v>4375.4</v>
@@ -4245,45 +4245,45 @@
         <v>3004.7</v>
       </c>
       <c r="M36">
-        <v>687.9242987271015</v>
+        <v>718.2550063367222</v>
       </c>
       <c r="N36">
-        <v>2316.775701272898</v>
+        <v>2286.444993663278</v>
       </c>
       <c r="O36">
-        <v>579.1939253182246</v>
+        <v>571.6112484158194</v>
       </c>
       <c r="P36">
-        <v>1737.581775954674</v>
+        <v>1714.833745247458</v>
       </c>
       <c r="Q36">
-        <v>4786.881775954675</v>
+        <v>4764.133745247458</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1295859644443192</v>
+        <v>0.1306425339833396</v>
       </c>
       <c r="T36">
-        <v>1.296142222823802</v>
+        <v>1.312487017563068</v>
       </c>
       <c r="U36">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.05259823332506819</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.367777102160423</v>
+        <v>4.183333180404424</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1035895287529446</v>
+        <v>0.1035139216421153</v>
       </c>
       <c r="C37">
-        <v>18429.7921030659</v>
+        <v>18172.9280491311</v>
       </c>
       <c r="D37">
-        <v>24152.0321030659</v>
+        <v>24183.6720491311</v>
       </c>
       <c r="E37">
-        <v>-4503.060000000001</v>
+        <v>-4214.556</v>
       </c>
       <c r="F37">
-        <v>10097.64</v>
+        <v>10386.144</v>
       </c>
       <c r="G37">
         <v>4375.4</v>
@@ -4327,28 +4327,28 @@
         <v>3004.7</v>
       </c>
       <c r="M37">
-        <v>718.2550063367222</v>
+        <v>738.7765779463429</v>
       </c>
       <c r="N37">
-        <v>2286.444993663278</v>
+        <v>2265.923422053657</v>
       </c>
       <c r="O37">
-        <v>571.6112484158194</v>
+        <v>566.4808555134142</v>
       </c>
       <c r="P37">
-        <v>1714.833745247458</v>
+        <v>1699.442566540243</v>
       </c>
       <c r="Q37">
-        <v>4764.133745247458</v>
+        <v>4748.742566540242</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1306425339833396</v>
+        <v>0.1317321213204544</v>
       </c>
       <c r="T37">
-        <v>1.312487017563068</v>
+        <v>1.329342587137936</v>
       </c>
       <c r="U37">
         <v>0.07113097776675759</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.183333180404424</v>
+        <v>4.067129480948745</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1035139216421154</v>
+        <v>0.1034383145312861</v>
       </c>
       <c r="C38">
-        <v>18172.92804913109</v>
+        <v>17916.1470026516</v>
       </c>
       <c r="D38">
-        <v>24183.6720491311</v>
+        <v>24215.3950026516</v>
       </c>
       <c r="E38">
-        <v>-4214.556000000002</v>
+        <v>-3926.052000000001</v>
       </c>
       <c r="F38">
-        <v>10386.144</v>
+        <v>10674.648</v>
       </c>
       <c r="G38">
         <v>4375.4</v>
@@ -4409,28 +4409,28 @@
         <v>3004.7</v>
       </c>
       <c r="M38">
-        <v>738.7765779463427</v>
+        <v>759.2981495559634</v>
       </c>
       <c r="N38">
-        <v>2265.923422053657</v>
+        <v>2245.401850444036</v>
       </c>
       <c r="O38">
-        <v>566.4808555134143</v>
+        <v>561.3504626110091</v>
       </c>
       <c r="P38">
-        <v>1699.442566540243</v>
+        <v>1684.051387833027</v>
       </c>
       <c r="Q38">
-        <v>4748.742566540243</v>
+        <v>4733.351387833028</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1317321213204544</v>
+        <v>0.1328562987317633</v>
       </c>
       <c r="T38">
-        <v>1.329342587137936</v>
+        <v>1.346733254159626</v>
       </c>
       <c r="U38">
         <v>0.07113097776675759</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.067129480948747</v>
+        <v>3.957207062544726</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1034383145312861</v>
+        <v>0.1033627074204569</v>
       </c>
       <c r="C39">
-        <v>17916.1470026516</v>
+        <v>17659.44929071178</v>
       </c>
       <c r="D39">
-        <v>24215.3950026516</v>
+        <v>24247.20129071179</v>
       </c>
       <c r="E39">
-        <v>-3926.052000000001</v>
+        <v>-3637.548000000003</v>
       </c>
       <c r="F39">
-        <v>10674.648</v>
+        <v>10963.152</v>
       </c>
       <c r="G39">
         <v>4375.4</v>
@@ -4491,28 +4491,28 @@
         <v>3004.7</v>
       </c>
       <c r="M39">
-        <v>759.2981495559634</v>
+        <v>779.8197211655839</v>
       </c>
       <c r="N39">
-        <v>2245.401850444036</v>
+        <v>2224.880278834416</v>
       </c>
       <c r="O39">
-        <v>561.3504626110091</v>
+        <v>556.220069708604</v>
       </c>
       <c r="P39">
-        <v>1684.051387833027</v>
+        <v>1668.660209125812</v>
       </c>
       <c r="Q39">
-        <v>4733.351387833028</v>
+        <v>4717.960209125812</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1328562987317633</v>
+        <v>0.1340167399305338</v>
       </c>
       <c r="T39">
-        <v>1.346733254159626</v>
+        <v>1.364684910440079</v>
       </c>
       <c r="U39">
         <v>0.07113097776675759</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.957207062544726</v>
+        <v>3.853070034583023</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1033627074204569</v>
+        <v>0.1032871003096276</v>
       </c>
       <c r="C40">
-        <v>17659.44929071178</v>
+        <v>17402.83524211674</v>
       </c>
       <c r="D40">
-        <v>24247.20129071179</v>
+        <v>24279.09124211674</v>
       </c>
       <c r="E40">
-        <v>-3637.548000000003</v>
+        <v>-3349.044000000002</v>
       </c>
       <c r="F40">
-        <v>10963.152</v>
+        <v>11251.656</v>
       </c>
       <c r="G40">
         <v>4375.4</v>
@@ -4573,28 +4573,28 @@
         <v>3004.7</v>
       </c>
       <c r="M40">
-        <v>779.8197211655839</v>
+        <v>800.3412927752047</v>
       </c>
       <c r="N40">
-        <v>2224.880278834416</v>
+        <v>2204.358707224795</v>
       </c>
       <c r="O40">
-        <v>556.220069708604</v>
+        <v>551.0896768061988</v>
       </c>
       <c r="P40">
-        <v>1668.660209125812</v>
+        <v>1653.269030418596</v>
       </c>
       <c r="Q40">
-        <v>4717.960209125812</v>
+        <v>4702.569030418596</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1340167399305338</v>
+        <v>0.135215228381723</v>
       </c>
       <c r="T40">
-        <v>1.364684910440079</v>
+        <v>1.383225145614974</v>
       </c>
       <c r="U40">
         <v>0.07113097776675759</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.853070034583023</v>
+        <v>3.754273367029612</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1032871003096276</v>
+        <v>0.1032114931987984</v>
       </c>
       <c r="C41">
-        <v>17402.83524211674</v>
+        <v>17146.30518740362</v>
       </c>
       <c r="D41">
-        <v>24279.09124211674</v>
+        <v>24311.06518740362</v>
       </c>
       <c r="E41">
-        <v>-3349.044000000002</v>
+        <v>-3060.540000000001</v>
       </c>
       <c r="F41">
-        <v>11251.656</v>
+        <v>11540.16</v>
       </c>
       <c r="G41">
         <v>4375.4</v>
@@ -4655,28 +4655,28 @@
         <v>3004.7</v>
       </c>
       <c r="M41">
-        <v>800.3412927752047</v>
+        <v>820.8628643848253</v>
       </c>
       <c r="N41">
-        <v>2204.358707224795</v>
+        <v>2183.837135615175</v>
       </c>
       <c r="O41">
-        <v>551.0896768061988</v>
+        <v>545.9592839037937</v>
       </c>
       <c r="P41">
-        <v>1653.269030418596</v>
+        <v>1637.877851711381</v>
       </c>
       <c r="Q41">
-        <v>4702.569030418596</v>
+        <v>4687.177851711382</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.135215228381723</v>
+        <v>0.1364536664479519</v>
       </c>
       <c r="T41">
-        <v>1.383225145614974</v>
+        <v>1.402383388629032</v>
       </c>
       <c r="U41">
         <v>0.07113097776675759</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.754273367029612</v>
+        <v>3.660416532853871</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1032114931987984</v>
+        <v>0.1031358860879692</v>
       </c>
       <c r="C42">
-        <v>17146.30518740362</v>
+        <v>16889.85945885303</v>
       </c>
       <c r="D42">
-        <v>24311.06518740362</v>
+        <v>24343.12345885303</v>
       </c>
       <c r="E42">
-        <v>-3060.540000000001</v>
+        <v>-2772.036000000002</v>
       </c>
       <c r="F42">
-        <v>11540.16</v>
+        <v>11828.664</v>
       </c>
       <c r="G42">
         <v>4375.4</v>
@@ -4737,28 +4737,28 @@
         <v>3004.7</v>
       </c>
       <c r="M42">
-        <v>820.8628643848253</v>
+        <v>841.3844359944459</v>
       </c>
       <c r="N42">
-        <v>2183.837135615175</v>
+        <v>2163.315564005554</v>
       </c>
       <c r="O42">
-        <v>545.9592839037937</v>
+        <v>540.8288910013885</v>
       </c>
       <c r="P42">
-        <v>1637.877851711381</v>
+        <v>1622.486673004165</v>
       </c>
       <c r="Q42">
-        <v>4687.177851711382</v>
+        <v>4671.786673004166</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1364536664479519</v>
+        <v>0.1377340854655783</v>
       </c>
       <c r="T42">
-        <v>1.402383388629032</v>
+        <v>1.422191063609668</v>
       </c>
       <c r="U42">
         <v>0.07113097776675759</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.660416532853871</v>
+        <v>3.571138080833046</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1031358860879692</v>
+        <v>0.1030602789771399</v>
       </c>
       <c r="C43">
-        <v>16889.85945885303</v>
+        <v>16633.4983905006</v>
       </c>
       <c r="D43">
-        <v>24343.12345885303</v>
+        <v>24375.2663905006</v>
       </c>
       <c r="E43">
-        <v>-2772.036000000002</v>
+        <v>-2483.532000000001</v>
       </c>
       <c r="F43">
-        <v>11828.664</v>
+        <v>12117.168</v>
       </c>
       <c r="G43">
         <v>4375.4</v>
@@ -4819,28 +4819,28 @@
         <v>3004.7</v>
       </c>
       <c r="M43">
-        <v>841.3844359944459</v>
+        <v>861.9060076040666</v>
       </c>
       <c r="N43">
-        <v>2163.315564005554</v>
+        <v>2142.793992395933</v>
       </c>
       <c r="O43">
-        <v>540.8288910013885</v>
+        <v>535.6984980989832</v>
       </c>
       <c r="P43">
-        <v>1622.486673004165</v>
+        <v>1607.09549429695</v>
       </c>
       <c r="Q43">
-        <v>4671.786673004166</v>
+        <v>4656.39549429695</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1377340854655783</v>
+        <v>0.1390586568631229</v>
       </c>
       <c r="T43">
-        <v>1.422191063609668</v>
+        <v>1.442681761865498</v>
       </c>
       <c r="U43">
         <v>0.07113097776675759</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.571138080833046</v>
+        <v>3.486110983670353</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1030602789771399</v>
+        <v>0.1029846718663107</v>
       </c>
       <c r="C44">
-        <v>16633.49839050061</v>
+        <v>16377.22231814854</v>
       </c>
       <c r="D44">
-        <v>24375.2663905006</v>
+        <v>24407.49431814855</v>
       </c>
       <c r="E44">
-        <v>-2483.532000000003</v>
+        <v>-2195.028000000002</v>
       </c>
       <c r="F44">
-        <v>12117.168</v>
+        <v>12405.672</v>
       </c>
       <c r="G44">
         <v>4375.4</v>
@@ -4901,28 +4901,28 @@
         <v>3004.7</v>
       </c>
       <c r="M44">
-        <v>861.9060076040664</v>
+        <v>882.4275792136872</v>
       </c>
       <c r="N44">
-        <v>2142.793992395933</v>
+        <v>2122.272420786313</v>
       </c>
       <c r="O44">
-        <v>535.6984980989834</v>
+        <v>530.5681051965781</v>
       </c>
       <c r="P44">
-        <v>1607.09549429695</v>
+        <v>1591.704315589735</v>
       </c>
       <c r="Q44">
-        <v>4656.39549429695</v>
+        <v>4641.004315589735</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1390586568631229</v>
+        <v>0.140429704450055</v>
       </c>
       <c r="T44">
-        <v>1.442681761865498</v>
+        <v>1.463891431989954</v>
       </c>
       <c r="U44">
         <v>0.07113097776675759</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.486110983670354</v>
+        <v>3.405038635212903</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1029846718663107</v>
+        <v>0.1029090647554815</v>
       </c>
       <c r="C45">
-        <v>16377.22231814854</v>
+        <v>16121.03157937734</v>
       </c>
       <c r="D45">
-        <v>24407.49431814855</v>
+        <v>24439.80757937734</v>
       </c>
       <c r="E45">
-        <v>-2195.028000000002</v>
+        <v>-1906.524000000001</v>
       </c>
       <c r="F45">
-        <v>12405.672</v>
+        <v>12694.176</v>
       </c>
       <c r="G45">
         <v>4375.4</v>
@@ -4983,28 +4983,28 @@
         <v>3004.7</v>
       </c>
       <c r="M45">
-        <v>882.4275792136872</v>
+        <v>902.9491508233078</v>
       </c>
       <c r="N45">
-        <v>2122.272420786313</v>
+        <v>2101.750849176692</v>
       </c>
       <c r="O45">
-        <v>530.5681051965781</v>
+        <v>525.437712294173</v>
       </c>
       <c r="P45">
-        <v>1591.704315589735</v>
+        <v>1576.313136882519</v>
       </c>
       <c r="Q45">
-        <v>4641.004315589735</v>
+        <v>4625.613136882519</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.140429704450055</v>
+        <v>0.1418497180222347</v>
       </c>
       <c r="T45">
-        <v>1.463891431989954</v>
+        <v>1.485858590333141</v>
       </c>
       <c r="U45">
         <v>0.07113097776675759</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.405038635212903</v>
+        <v>3.327651393503519</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1029090647554815</v>
+        <v>0.1028334576446522</v>
       </c>
       <c r="C46">
-        <v>16121.03157937734</v>
+        <v>15864.92651355756</v>
       </c>
       <c r="D46">
-        <v>24439.80757937734</v>
+        <v>24472.20651355756</v>
       </c>
       <c r="E46">
-        <v>-1906.524000000001</v>
+        <v>-1618.020000000002</v>
       </c>
       <c r="F46">
-        <v>12694.176</v>
+        <v>12982.68</v>
       </c>
       <c r="G46">
         <v>4375.4</v>
@@ -5065,28 +5065,28 @@
         <v>3004.7</v>
       </c>
       <c r="M46">
-        <v>902.9491508233078</v>
+        <v>923.4707224329284</v>
       </c>
       <c r="N46">
-        <v>2101.750849176692</v>
+        <v>2081.229277567071</v>
       </c>
       <c r="O46">
-        <v>525.437712294173</v>
+        <v>520.3073193917678</v>
       </c>
       <c r="P46">
-        <v>1576.313136882519</v>
+        <v>1560.921958175303</v>
       </c>
       <c r="Q46">
-        <v>4625.613136882519</v>
+        <v>4610.221958175303</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1418497180222347</v>
+        <v>0.1433213684515846</v>
       </c>
       <c r="T46">
-        <v>1.485858590333141</v>
+        <v>1.508624554434261</v>
       </c>
       <c r="U46">
         <v>0.07113097776675759</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.327651393503519</v>
+        <v>3.253703584758997</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1028334576446522</v>
+        <v>0.102757850533823</v>
       </c>
       <c r="C47">
-        <v>15864.92651355756</v>
+        <v>15608.90746186171</v>
       </c>
       <c r="D47">
-        <v>24472.20651355756</v>
+        <v>24504.69146186171</v>
       </c>
       <c r="E47">
-        <v>-1618.020000000002</v>
+        <v>-1329.516000000001</v>
       </c>
       <c r="F47">
-        <v>12982.68</v>
+        <v>13271.184</v>
       </c>
       <c r="G47">
         <v>4375.4</v>
@@ -5147,28 +5147,28 @@
         <v>3004.7</v>
       </c>
       <c r="M47">
-        <v>923.4707224329284</v>
+        <v>943.9922940425491</v>
       </c>
       <c r="N47">
-        <v>2081.229277567071</v>
+        <v>2060.707705957451</v>
       </c>
       <c r="O47">
-        <v>520.3073193917678</v>
+        <v>515.1769264893627</v>
       </c>
       <c r="P47">
-        <v>1560.921958175303</v>
+        <v>1545.530779468088</v>
       </c>
       <c r="Q47">
-        <v>4610.221958175303</v>
+        <v>4594.830779468088</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1433213684515846</v>
+        <v>0.1448475244523919</v>
       </c>
       <c r="T47">
-        <v>1.508624554434261</v>
+        <v>1.532233702390979</v>
       </c>
       <c r="U47">
         <v>0.07113097776675759</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.253703584758997</v>
+        <v>3.182970898133801</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.102757850533823</v>
+        <v>0.1026822434229937</v>
       </c>
       <c r="C48">
-        <v>15608.90746186171</v>
+        <v>15352.97476727623</v>
       </c>
       <c r="D48">
-        <v>24504.69146186171</v>
+        <v>24537.26276727623</v>
       </c>
       <c r="E48">
-        <v>-1329.516000000001</v>
+        <v>-1041.012000000001</v>
       </c>
       <c r="F48">
-        <v>13271.184</v>
+        <v>13559.688</v>
       </c>
       <c r="G48">
         <v>4375.4</v>
@@ -5229,28 +5229,28 @@
         <v>3004.7</v>
       </c>
       <c r="M48">
-        <v>943.9922940425491</v>
+        <v>964.5138656521698</v>
       </c>
       <c r="N48">
-        <v>2060.707705957451</v>
+        <v>2040.18613434783</v>
       </c>
       <c r="O48">
-        <v>515.1769264893627</v>
+        <v>510.0465335869575</v>
       </c>
       <c r="P48">
-        <v>1545.530779468088</v>
+        <v>1530.139600760872</v>
       </c>
       <c r="Q48">
-        <v>4594.830779468088</v>
+        <v>4579.439600760872</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1448475244523919</v>
+        <v>0.1464312712456824</v>
       </c>
       <c r="T48">
-        <v>1.532233702390979</v>
+        <v>1.556733761591346</v>
       </c>
       <c r="U48">
         <v>0.07113097776675759</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.182970898133801</v>
+        <v>3.115248113067124</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1026822434229937</v>
+        <v>0.1026066363121645</v>
       </c>
       <c r="C49">
-        <v>15352.97476727623</v>
+        <v>15097.12877461355</v>
       </c>
       <c r="D49">
-        <v>24537.26276727623</v>
+        <v>24569.92077461355</v>
       </c>
       <c r="E49">
-        <v>-1041.012000000001</v>
+        <v>-752.5080000000016</v>
       </c>
       <c r="F49">
-        <v>13559.688</v>
+        <v>13848.192</v>
       </c>
       <c r="G49">
         <v>4375.4</v>
@@ -5311,28 +5311,28 @@
         <v>3004.7</v>
       </c>
       <c r="M49">
-        <v>964.5138656521698</v>
+        <v>985.0354372617903</v>
       </c>
       <c r="N49">
-        <v>2040.18613434783</v>
+        <v>2019.664562738209</v>
       </c>
       <c r="O49">
-        <v>510.0465335869575</v>
+        <v>504.9161406845524</v>
       </c>
       <c r="P49">
-        <v>1530.139600760872</v>
+        <v>1514.748422053657</v>
       </c>
       <c r="Q49">
-        <v>4579.439600760872</v>
+        <v>4564.048422053657</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1464312712456824</v>
+        <v>0.1480759313771765</v>
       </c>
       <c r="T49">
-        <v>1.556733761591346</v>
+        <v>1.582176130760959</v>
       </c>
       <c r="U49">
         <v>0.07113097776675759</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.115248113067124</v>
+        <v>3.050347110711559</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1026066363121645</v>
+        <v>0.1034497792013352</v>
       </c>
       <c r="C50">
-        <v>15097.12877461356</v>
+        <v>14449.2833465006</v>
       </c>
       <c r="D50">
-        <v>24569.92077461356</v>
+        <v>24210.5793465006</v>
       </c>
       <c r="E50">
-        <v>-752.5080000000016</v>
+        <v>-464.0040000000026</v>
       </c>
       <c r="F50">
-        <v>13848.192</v>
+        <v>14136.696</v>
       </c>
       <c r="G50">
         <v>4375.4</v>
@@ -5393,45 +5393,45 @@
         <v>3004.7</v>
       </c>
       <c r="M50">
-        <v>985.0354372617903</v>
+        <v>1040.898748871411</v>
       </c>
       <c r="N50">
-        <v>2019.664562738209</v>
+        <v>1963.801251128589</v>
       </c>
       <c r="O50">
-        <v>504.9161406845524</v>
+        <v>490.9503127821473</v>
       </c>
       <c r="P50">
-        <v>1514.748422053657</v>
+        <v>1472.850938346442</v>
       </c>
       <c r="Q50">
-        <v>4564.048422053657</v>
+        <v>4522.150938346442</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1480759313771765</v>
+        <v>0.1497850879844154</v>
       </c>
       <c r="T50">
-        <v>1.582176130760959</v>
+        <v>1.608616239898007</v>
       </c>
       <c r="U50">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.05334823332506819</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.050347110711559</v>
+        <v>2.886640034160701</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1034497792013352</v>
+        <v>0.103392922090506</v>
       </c>
       <c r="C51">
-        <v>14449.2833465006</v>
+        <v>14184.68060976661</v>
       </c>
       <c r="D51">
-        <v>24210.5793465006</v>
+        <v>24234.48060976661</v>
       </c>
       <c r="E51">
-        <v>-464.0040000000026</v>
+        <v>-175.5000000000018</v>
       </c>
       <c r="F51">
-        <v>14136.696</v>
+        <v>14425.2</v>
       </c>
       <c r="G51">
         <v>4375.4</v>
@@ -5475,28 +5475,28 @@
         <v>3004.7</v>
       </c>
       <c r="M51">
-        <v>1040.898748871411</v>
+        <v>1062.141580481031</v>
       </c>
       <c r="N51">
-        <v>1963.801251128589</v>
+        <v>1942.558419518968</v>
       </c>
       <c r="O51">
-        <v>490.9503127821473</v>
+        <v>485.6396048797421</v>
       </c>
       <c r="P51">
-        <v>1472.850938346442</v>
+        <v>1456.918814639226</v>
       </c>
       <c r="Q51">
-        <v>4522.150938346442</v>
+        <v>4506.218814639226</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1497850879844154</v>
+        <v>0.1515626108559439</v>
       </c>
       <c r="T51">
-        <v>1.608616239898007</v>
+        <v>1.636113953400537</v>
       </c>
       <c r="U51">
         <v>0.07363097776675757</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.886640034160701</v>
+        <v>2.828907233477486</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.103392922090506</v>
+        <v>0.1033360649796768</v>
       </c>
       <c r="C52">
-        <v>14184.68060976661</v>
+        <v>13920.12511146559</v>
       </c>
       <c r="D52">
-        <v>24234.48060976661</v>
+        <v>24258.42911146559</v>
       </c>
       <c r="E52">
-        <v>-175.5000000000018</v>
+        <v>113.003999999999</v>
       </c>
       <c r="F52">
-        <v>14425.2</v>
+        <v>14713.704</v>
       </c>
       <c r="G52">
         <v>4375.4</v>
@@ -5557,28 +5557,28 @@
         <v>3004.7</v>
       </c>
       <c r="M52">
-        <v>1062.141580481031</v>
+        <v>1083.384412090652</v>
       </c>
       <c r="N52">
-        <v>1942.558419518968</v>
+        <v>1921.315587909348</v>
       </c>
       <c r="O52">
-        <v>485.6396048797421</v>
+        <v>480.3288969773369</v>
       </c>
       <c r="P52">
-        <v>1456.918814639226</v>
+        <v>1440.986690932011</v>
       </c>
       <c r="Q52">
-        <v>4506.218814639226</v>
+        <v>4490.286690932011</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1515626108559439</v>
+        <v>0.1534126856814123</v>
       </c>
       <c r="T52">
-        <v>1.636113953400537</v>
+        <v>1.664734022556232</v>
       </c>
       <c r="U52">
         <v>0.07363097776675757</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.828907233477486</v>
+        <v>2.773438464193614</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1033360649796768</v>
+        <v>0.1032792078688475</v>
       </c>
       <c r="C53">
-        <v>13920.12511146559</v>
+        <v>13655.61699177906</v>
       </c>
       <c r="D53">
-        <v>24258.42911146559</v>
+        <v>24282.42499177906</v>
       </c>
       <c r="E53">
-        <v>113.003999999999</v>
+        <v>401.507999999998</v>
       </c>
       <c r="F53">
-        <v>14713.704</v>
+        <v>15002.208</v>
       </c>
       <c r="G53">
         <v>4375.4</v>
@@ -5639,28 +5639,28 @@
         <v>3004.7</v>
       </c>
       <c r="M53">
-        <v>1083.384412090652</v>
+        <v>1104.627243700273</v>
       </c>
       <c r="N53">
-        <v>1921.315587909348</v>
+        <v>1900.072756299727</v>
       </c>
       <c r="O53">
-        <v>480.3288969773369</v>
+        <v>475.0181890749318</v>
       </c>
       <c r="P53">
-        <v>1440.986690932011</v>
+        <v>1425.054567224795</v>
       </c>
       <c r="Q53">
-        <v>4490.286690932011</v>
+        <v>4474.354567224796</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1534126856814123</v>
+        <v>0.1553398469579419</v>
       </c>
       <c r="T53">
-        <v>1.664734022556232</v>
+        <v>1.694546594593413</v>
       </c>
       <c r="U53">
         <v>0.07363097776675757</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.773438464193614</v>
+        <v>2.720103109112968</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1032792078688475</v>
+        <v>0.1032223507580183</v>
       </c>
       <c r="C54">
-        <v>13655.61699177906</v>
+        <v>13391.15639144373</v>
       </c>
       <c r="D54">
-        <v>24282.42499177906</v>
+        <v>24306.46839144374</v>
       </c>
       <c r="E54">
-        <v>401.507999999998</v>
+        <v>690.0119999999988</v>
       </c>
       <c r="F54">
-        <v>15002.208</v>
+        <v>15290.712</v>
       </c>
       <c r="G54">
         <v>4375.4</v>
@@ -5721,28 +5721,28 @@
         <v>3004.7</v>
       </c>
       <c r="M54">
-        <v>1104.627243700273</v>
+        <v>1125.870075309893</v>
       </c>
       <c r="N54">
-        <v>1900.072756299727</v>
+        <v>1878.829924690107</v>
       </c>
       <c r="O54">
-        <v>475.0181890749318</v>
+        <v>469.7074811725266</v>
       </c>
       <c r="P54">
-        <v>1425.054567224795</v>
+        <v>1409.12244351758</v>
       </c>
       <c r="Q54">
-        <v>4474.354567224796</v>
+        <v>4458.42244351758</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1553398469579419</v>
+        <v>0.1573490150973025</v>
       </c>
       <c r="T54">
-        <v>1.694546594593413</v>
+        <v>1.725627786717284</v>
       </c>
       <c r="U54">
         <v>0.07363097776675757</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.720103109112968</v>
+        <v>2.668780408941025</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1032223507580183</v>
+        <v>0.1031654936471891</v>
       </c>
       <c r="C55">
-        <v>13391.15639144373</v>
+        <v>13126.74345175429</v>
       </c>
       <c r="D55">
-        <v>24306.46839144374</v>
+        <v>24330.5594517543</v>
       </c>
       <c r="E55">
-        <v>690.0119999999988</v>
+        <v>978.5159999999996</v>
       </c>
       <c r="F55">
-        <v>15290.712</v>
+        <v>15579.216</v>
       </c>
       <c r="G55">
         <v>4375.4</v>
@@ -5803,28 +5803,28 @@
         <v>3004.7</v>
       </c>
       <c r="M55">
-        <v>1125.870075309893</v>
+        <v>1147.112906919514</v>
       </c>
       <c r="N55">
-        <v>1878.829924690107</v>
+        <v>1857.587093080486</v>
       </c>
       <c r="O55">
-        <v>469.7074811725266</v>
+        <v>464.3967732701215</v>
       </c>
       <c r="P55">
-        <v>1409.12244351758</v>
+        <v>1393.190319810364</v>
       </c>
       <c r="Q55">
-        <v>4458.42244351758</v>
+        <v>4442.490319810365</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1573490150973025</v>
+        <v>0.1594455383731571</v>
       </c>
       <c r="T55">
-        <v>1.725627786717284</v>
+        <v>1.758060335020453</v>
       </c>
       <c r="U55">
         <v>0.07363097776675757</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.668780408941025</v>
+        <v>2.619358549516191</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1031654936471891</v>
+        <v>0.1031086365363598</v>
       </c>
       <c r="C56">
-        <v>13126.74345175429</v>
+        <v>12862.37831456615</v>
       </c>
       <c r="D56">
-        <v>24330.5594517543</v>
+        <v>24354.69831456615</v>
       </c>
       <c r="E56">
-        <v>978.5159999999996</v>
+        <v>1267.02</v>
       </c>
       <c r="F56">
-        <v>15579.216</v>
+        <v>15867.72</v>
       </c>
       <c r="G56">
         <v>4375.4</v>
@@ -5885,28 +5885,28 @@
         <v>3004.7</v>
       </c>
       <c r="M56">
-        <v>1147.112906919514</v>
+        <v>1168.355738529135</v>
       </c>
       <c r="N56">
-        <v>1857.587093080486</v>
+        <v>1836.344261470865</v>
       </c>
       <c r="O56">
-        <v>464.3967732701215</v>
+        <v>459.0860653677163</v>
       </c>
       <c r="P56">
-        <v>1393.190319810364</v>
+        <v>1377.258196103149</v>
       </c>
       <c r="Q56">
-        <v>4442.490319810365</v>
+        <v>4426.558196103149</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1594455383731571</v>
+        <v>0.1616352404612719</v>
       </c>
       <c r="T56">
-        <v>1.758060335020453</v>
+        <v>1.791934329914874</v>
       </c>
       <c r="U56">
         <v>0.07363097776675757</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.619358549516191</v>
+        <v>2.571733848615897</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1031086365363598</v>
+        <v>0.1030517794255306</v>
       </c>
       <c r="C57">
-        <v>12862.37831456615</v>
+        <v>12598.06112229823</v>
       </c>
       <c r="D57">
-        <v>24354.69831456615</v>
+        <v>24378.88512229823</v>
       </c>
       <c r="E57">
-        <v>1267.02</v>
+        <v>1555.523999999999</v>
       </c>
       <c r="F57">
-        <v>15867.72</v>
+        <v>16156.224</v>
       </c>
       <c r="G57">
         <v>4375.4</v>
@@ -5967,28 +5967,28 @@
         <v>3004.7</v>
       </c>
       <c r="M57">
-        <v>1168.355738529135</v>
+        <v>1189.598570138755</v>
       </c>
       <c r="N57">
-        <v>1836.344261470865</v>
+        <v>1815.101429861244</v>
       </c>
       <c r="O57">
-        <v>459.0860653677163</v>
+        <v>453.7753574653111</v>
       </c>
       <c r="P57">
-        <v>1377.258196103149</v>
+        <v>1361.326072395933</v>
       </c>
       <c r="Q57">
-        <v>4426.558196103149</v>
+        <v>4410.626072395933</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1616352404612719</v>
+        <v>0.1639244744624828</v>
       </c>
       <c r="T57">
-        <v>1.791934329914874</v>
+        <v>1.82734805184995</v>
       </c>
       <c r="U57">
         <v>0.07363097776675757</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.571733848615897</v>
+        <v>2.525810029890613</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1030517794255306</v>
+        <v>0.1044911723147013</v>
       </c>
       <c r="C58">
-        <v>12598.06112229823</v>
+        <v>11711.66833413787</v>
       </c>
       <c r="D58">
-        <v>24378.88512229823</v>
+        <v>23780.99633413788</v>
       </c>
       <c r="E58">
-        <v>1555.523999999999</v>
+        <v>1844.028</v>
       </c>
       <c r="F58">
-        <v>16156.224</v>
+        <v>16444.728</v>
       </c>
       <c r="G58">
         <v>4375.4</v>
@@ -6049,45 +6049,45 @@
         <v>3004.7</v>
       </c>
       <c r="M58">
-        <v>1189.598570138755</v>
+        <v>1268.397949748376</v>
       </c>
       <c r="N58">
-        <v>1815.101429861244</v>
+        <v>1736.302050251624</v>
       </c>
       <c r="O58">
-        <v>453.7753574653111</v>
+        <v>434.0755125629059</v>
       </c>
       <c r="P58">
-        <v>1361.326072395933</v>
+        <v>1302.226537688718</v>
       </c>
       <c r="Q58">
-        <v>4410.626072395933</v>
+        <v>4351.526537688718</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1639244744624828</v>
+        <v>0.16632018446375</v>
       </c>
       <c r="T58">
-        <v>1.82734805184995</v>
+        <v>1.864408923642473</v>
       </c>
       <c r="U58">
-        <v>0.07363097776675757</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.05522323332506818</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.525810029890613</v>
+        <v>2.368893769180303</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1044911723147013</v>
+        <v>0.1044605652038721</v>
       </c>
       <c r="C59">
-        <v>11711.66833413787</v>
+        <v>11435.57245853795</v>
       </c>
       <c r="D59">
-        <v>23780.99633413788</v>
+        <v>23793.40445853795</v>
       </c>
       <c r="E59">
-        <v>1844.028</v>
+        <v>2132.532000000001</v>
       </c>
       <c r="F59">
-        <v>16444.728</v>
+        <v>16733.232</v>
       </c>
       <c r="G59">
         <v>4375.4</v>
@@ -6131,28 +6131,28 @@
         <v>3004.7</v>
       </c>
       <c r="M59">
-        <v>1268.397949748376</v>
+        <v>1290.650545357997</v>
       </c>
       <c r="N59">
-        <v>1736.302050251624</v>
+        <v>1714.049454642003</v>
       </c>
       <c r="O59">
-        <v>434.0755125629059</v>
+        <v>428.5123636605008</v>
       </c>
       <c r="P59">
-        <v>1302.226537688718</v>
+        <v>1285.537090981502</v>
       </c>
       <c r="Q59">
-        <v>4351.526537688718</v>
+        <v>4334.837090981502</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.16632018446375</v>
+        <v>0.168829975893649</v>
       </c>
       <c r="T59">
-        <v>1.864408923642473</v>
+        <v>1.903234598853686</v>
       </c>
       <c r="U59">
         <v>0.07713097776675758</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.368893769180303</v>
+        <v>2.328050773159954</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1044605652038721</v>
+        <v>0.1044299580930429</v>
       </c>
       <c r="C60">
-        <v>11435.57245853795</v>
+        <v>11159.48953798187</v>
       </c>
       <c r="D60">
-        <v>23793.40445853795</v>
+        <v>23805.82553798187</v>
       </c>
       <c r="E60">
-        <v>2132.531999999997</v>
+        <v>2421.035999999998</v>
       </c>
       <c r="F60">
-        <v>16733.232</v>
+        <v>17021.736</v>
       </c>
       <c r="G60">
         <v>4375.4</v>
@@ -6213,28 +6213,28 @@
         <v>3004.7</v>
       </c>
       <c r="M60">
-        <v>1290.650545357996</v>
+        <v>1312.903140967617</v>
       </c>
       <c r="N60">
-        <v>1714.049454642003</v>
+        <v>1691.796859032383</v>
       </c>
       <c r="O60">
-        <v>428.5123636605009</v>
+        <v>422.9492147580956</v>
       </c>
       <c r="P60">
-        <v>1285.537090981503</v>
+        <v>1268.847644274287</v>
       </c>
       <c r="Q60">
-        <v>4334.837090981503</v>
+        <v>4318.147644274287</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.168829975893649</v>
+        <v>0.171462196173787</v>
       </c>
       <c r="T60">
-        <v>1.903234598853686</v>
+        <v>1.943954209441056</v>
       </c>
       <c r="U60">
         <v>0.07713097776675758</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.328050773159954</v>
+        <v>2.288592285479276</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1044299580930429</v>
+        <v>0.1043993509822136</v>
       </c>
       <c r="C61">
-        <v>11159.48953798187</v>
+        <v>10883.41959276933</v>
       </c>
       <c r="D61">
-        <v>23805.82553798187</v>
+        <v>23818.25959276934</v>
       </c>
       <c r="E61">
-        <v>2421.035999999998</v>
+        <v>2709.539999999999</v>
       </c>
       <c r="F61">
-        <v>17021.736</v>
+        <v>17310.24</v>
       </c>
       <c r="G61">
         <v>4375.4</v>
@@ -6295,28 +6295,28 @@
         <v>3004.7</v>
       </c>
       <c r="M61">
-        <v>1312.903140967617</v>
+        <v>1335.155736577238</v>
       </c>
       <c r="N61">
-        <v>1691.796859032383</v>
+        <v>1669.544263422762</v>
       </c>
       <c r="O61">
-        <v>422.9492147580956</v>
+        <v>417.3860658556905</v>
       </c>
       <c r="P61">
-        <v>1268.847644274287</v>
+        <v>1252.158197567072</v>
       </c>
       <c r="Q61">
-        <v>4318.147644274287</v>
+        <v>4301.458197567072</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.171462196173787</v>
+        <v>0.1742260274679318</v>
       </c>
       <c r="T61">
-        <v>1.943954209441056</v>
+        <v>1.986709800557795</v>
       </c>
       <c r="U61">
         <v>0.07713097776675758</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.288592285479276</v>
+        <v>2.250449080721289</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1043993509822136</v>
+        <v>0.1056497438713844</v>
       </c>
       <c r="C62">
-        <v>10883.41959276933</v>
+        <v>10097.29972174366</v>
       </c>
       <c r="D62">
-        <v>23818.25959276934</v>
+        <v>23320.64372174366</v>
       </c>
       <c r="E62">
-        <v>2709.539999999999</v>
+        <v>2998.043999999996</v>
       </c>
       <c r="F62">
-        <v>17310.24</v>
+        <v>17598.744</v>
       </c>
       <c r="G62">
         <v>4375.4</v>
@@ -6377,45 +6377,45 @@
         <v>3004.7</v>
       </c>
       <c r="M62">
-        <v>1335.155736577238</v>
+        <v>1406.684815386858</v>
       </c>
       <c r="N62">
-        <v>1669.544263422762</v>
+        <v>1598.015184613141</v>
       </c>
       <c r="O62">
-        <v>417.3860658556905</v>
+        <v>399.5037961532854</v>
       </c>
       <c r="P62">
-        <v>1252.158197567072</v>
+        <v>1198.511388459856</v>
       </c>
       <c r="Q62">
-        <v>4301.458197567072</v>
+        <v>4247.811388459856</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1742260274679318</v>
+        <v>0.177131593700238</v>
       </c>
       <c r="T62">
-        <v>1.986709800557795</v>
+        <v>2.031657986090777</v>
       </c>
       <c r="U62">
-        <v>0.07713097776675758</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.05784823332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.250449080721289</v>
+        <v>2.136015095303111</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1056497438713844</v>
+        <v>0.1056401367605552</v>
       </c>
       <c r="C63">
-        <v>10097.29972174366</v>
+        <v>9812.539764136818</v>
       </c>
       <c r="D63">
-        <v>23320.64372174366</v>
+        <v>23324.38776413682</v>
       </c>
       <c r="E63">
-        <v>2998.043999999996</v>
+        <v>3286.547999999997</v>
       </c>
       <c r="F63">
-        <v>17598.744</v>
+        <v>17887.248</v>
       </c>
       <c r="G63">
         <v>4375.4</v>
@@ -6459,28 +6459,28 @@
         <v>3004.7</v>
       </c>
       <c r="M63">
-        <v>1406.684815386858</v>
+        <v>1429.745222196479</v>
       </c>
       <c r="N63">
-        <v>1598.015184613141</v>
+        <v>1574.954777803521</v>
       </c>
       <c r="O63">
-        <v>399.5037961532854</v>
+        <v>393.7386944508802</v>
       </c>
       <c r="P63">
-        <v>1198.511388459856</v>
+        <v>1181.21608335264</v>
       </c>
       <c r="Q63">
-        <v>4247.811388459856</v>
+        <v>4230.516083352641</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.177131593700238</v>
+        <v>0.1801900844710866</v>
       </c>
       <c r="T63">
-        <v>2.031657986090777</v>
+        <v>2.078971865599179</v>
       </c>
       <c r="U63">
         <v>0.07993097776675759</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.136015095303111</v>
+        <v>2.101563238927254</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1056401367605552</v>
+        <v>0.1056305296497259</v>
       </c>
       <c r="C64">
-        <v>9812.539764136818</v>
+        <v>9527.781008907106</v>
       </c>
       <c r="D64">
-        <v>23324.38776413682</v>
+        <v>23328.13300890711</v>
       </c>
       <c r="E64">
-        <v>3286.547999999997</v>
+        <v>3575.051999999998</v>
       </c>
       <c r="F64">
-        <v>17887.248</v>
+        <v>18175.752</v>
       </c>
       <c r="G64">
         <v>4375.4</v>
@@ -6541,28 +6541,28 @@
         <v>3004.7</v>
       </c>
       <c r="M64">
-        <v>1429.745222196479</v>
+        <v>1452.8056290061</v>
       </c>
       <c r="N64">
-        <v>1574.954777803521</v>
+        <v>1551.8943709939</v>
       </c>
       <c r="O64">
-        <v>393.7386944508802</v>
+        <v>387.973592748475</v>
       </c>
       <c r="P64">
-        <v>1181.21608335264</v>
+        <v>1163.920778245425</v>
       </c>
       <c r="Q64">
-        <v>4230.516083352641</v>
+        <v>4213.220778245425</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1801900844710866</v>
+        <v>0.1834138990673864</v>
       </c>
       <c r="T64">
-        <v>2.078971865599179</v>
+        <v>2.128843252108035</v>
       </c>
       <c r="U64">
         <v>0.07993097776675759</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.101563238927254</v>
+        <v>2.068205092277616</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1056305296497259</v>
+        <v>0.1056209225388967</v>
       </c>
       <c r="C65">
-        <v>9527.781008907106</v>
+        <v>9243.023456633819</v>
       </c>
       <c r="D65">
-        <v>23328.13300890711</v>
+        <v>23331.87945663382</v>
       </c>
       <c r="E65">
-        <v>3575.051999999998</v>
+        <v>3863.555999999999</v>
       </c>
       <c r="F65">
-        <v>18175.752</v>
+        <v>18464.256</v>
       </c>
       <c r="G65">
         <v>4375.4</v>
@@ -6623,28 +6623,28 @@
         <v>3004.7</v>
       </c>
       <c r="M65">
-        <v>1452.8056290061</v>
+        <v>1475.866035815721</v>
       </c>
       <c r="N65">
-        <v>1551.8943709939</v>
+        <v>1528.833964184279</v>
       </c>
       <c r="O65">
-        <v>387.973592748475</v>
+        <v>382.2084910460698</v>
       </c>
       <c r="P65">
-        <v>1163.920778245425</v>
+        <v>1146.625473138209</v>
       </c>
       <c r="Q65">
-        <v>4213.220778245425</v>
+        <v>4195.92547313821</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1834138990673864</v>
+        <v>0.1868168144745918</v>
       </c>
       <c r="T65">
-        <v>2.128843252108035</v>
+        <v>2.181485271200716</v>
       </c>
       <c r="U65">
         <v>0.07993097776675759</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.068205092277616</v>
+        <v>2.035889387710777</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1056209225388967</v>
+        <v>0.1056113154280675</v>
       </c>
       <c r="C66">
-        <v>9243.023456633819</v>
+        <v>8958.267107896638</v>
       </c>
       <c r="D66">
-        <v>23331.87945663382</v>
+        <v>23335.62710789664</v>
       </c>
       <c r="E66">
-        <v>3863.555999999999</v>
+        <v>4152.059999999999</v>
       </c>
       <c r="F66">
-        <v>18464.256</v>
+        <v>18752.76</v>
       </c>
       <c r="G66">
         <v>4375.4</v>
@@ -6705,28 +6705,28 @@
         <v>3004.7</v>
       </c>
       <c r="M66">
-        <v>1475.866035815721</v>
+        <v>1498.926442625341</v>
       </c>
       <c r="N66">
-        <v>1528.833964184279</v>
+        <v>1505.773557374659</v>
       </c>
       <c r="O66">
-        <v>382.2084910460698</v>
+        <v>376.4433893436646</v>
       </c>
       <c r="P66">
-        <v>1146.625473138209</v>
+        <v>1129.330168030994</v>
       </c>
       <c r="Q66">
-        <v>4195.92547313821</v>
+        <v>4178.630168030994</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1868168144745918</v>
+        <v>0.1904141821907804</v>
       </c>
       <c r="T66">
-        <v>2.181485271200716</v>
+        <v>2.237135405670122</v>
       </c>
       <c r="U66">
         <v>0.07993097776675759</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.035889387710777</v>
+        <v>2.004568012515227</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1056113154280675</v>
+        <v>0.1094627083172382</v>
       </c>
       <c r="C67">
-        <v>8958.267107896638</v>
+        <v>7258.031331424943</v>
       </c>
       <c r="D67">
-        <v>23335.62710789664</v>
+        <v>21923.89533142494</v>
       </c>
       <c r="E67">
-        <v>4152.059999999999</v>
+        <v>4440.564</v>
       </c>
       <c r="F67">
-        <v>18752.76</v>
+        <v>19041.264</v>
       </c>
       <c r="G67">
         <v>4375.4</v>
@@ -6787,45 +6787,45 @@
         <v>3004.7</v>
       </c>
       <c r="M67">
-        <v>1498.926442625341</v>
+        <v>1670.508708634962</v>
       </c>
       <c r="N67">
-        <v>1505.773557374659</v>
+        <v>1334.191291365038</v>
       </c>
       <c r="O67">
-        <v>376.4433893436646</v>
+        <v>333.5478228412595</v>
       </c>
       <c r="P67">
-        <v>1129.330168030994</v>
+        <v>1000.643468523778</v>
       </c>
       <c r="Q67">
-        <v>4178.630168030994</v>
+        <v>4049.943468523778</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1904141821907804</v>
+        <v>0.1942231597726271</v>
       </c>
       <c r="T67">
-        <v>2.237135405670122</v>
+        <v>2.296059077461258</v>
       </c>
       <c r="U67">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.05994823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.004568012515227</v>
+        <v>1.798673652204578</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1094627083172382</v>
+        <v>0.109511601206409</v>
       </c>
       <c r="C68">
-        <v>7258.031331424943</v>
+        <v>6952.70272547668</v>
       </c>
       <c r="D68">
-        <v>21923.89533142494</v>
+        <v>21907.07072547668</v>
       </c>
       <c r="E68">
-        <v>4440.564</v>
+        <v>4729.068000000001</v>
       </c>
       <c r="F68">
-        <v>19041.264</v>
+        <v>19329.768</v>
       </c>
       <c r="G68">
         <v>4375.4</v>
@@ -6869,28 +6869,28 @@
         <v>3004.7</v>
       </c>
       <c r="M68">
-        <v>1670.508708634962</v>
+        <v>1695.819446644583</v>
       </c>
       <c r="N68">
-        <v>1334.191291365038</v>
+        <v>1308.880553355417</v>
       </c>
       <c r="O68">
-        <v>333.5478228412595</v>
+        <v>327.2201383388543</v>
       </c>
       <c r="P68">
-        <v>1000.643468523778</v>
+        <v>981.6604150165629</v>
       </c>
       <c r="Q68">
-        <v>4049.943468523778</v>
+        <v>4030.960415016563</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1942231597726271</v>
+        <v>0.1982629844806464</v>
       </c>
       <c r="T68">
-        <v>2.296059077461258</v>
+        <v>2.358553880876099</v>
       </c>
       <c r="U68">
         <v>0.08773097776675759</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.798673652204578</v>
+        <v>1.771827776798539</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.109511601206409</v>
+        <v>0.1115494940955798</v>
       </c>
       <c r="C69">
-        <v>6952.70272547668</v>
+        <v>5985.193293296306</v>
       </c>
       <c r="D69">
-        <v>21907.07072547668</v>
+        <v>21228.06529329631</v>
       </c>
       <c r="E69">
-        <v>4729.068000000001</v>
+        <v>5017.571999999998</v>
       </c>
       <c r="F69">
-        <v>19329.768</v>
+        <v>19618.272</v>
       </c>
       <c r="G69">
         <v>4375.4</v>
@@ -6951,45 +6951,45 @@
         <v>3004.7</v>
       </c>
       <c r="M69">
-        <v>1695.819446644583</v>
+        <v>1797.641445454203</v>
       </c>
       <c r="N69">
-        <v>1308.880553355417</v>
+        <v>1207.058554545797</v>
       </c>
       <c r="O69">
-        <v>327.2201383388543</v>
+        <v>301.7646386364493</v>
       </c>
       <c r="P69">
-        <v>981.6604150165629</v>
+        <v>905.2939159093478</v>
       </c>
       <c r="Q69">
-        <v>4030.960415016563</v>
+        <v>3954.593915909348</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1982629844806464</v>
+        <v>0.2025552982329168</v>
       </c>
       <c r="T69">
-        <v>2.358553880876099</v>
+        <v>2.424954609504367</v>
       </c>
       <c r="U69">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.06579823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.771827776798539</v>
+        <v>1.671467915694842</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1115494940955798</v>
+        <v>0.1116276369847505</v>
       </c>
       <c r="C70">
-        <v>5985.193293296306</v>
+        <v>5671.489811292911</v>
       </c>
       <c r="D70">
-        <v>21228.06529329631</v>
+        <v>21202.86581129291</v>
       </c>
       <c r="E70">
-        <v>5017.571999999998</v>
+        <v>5306.075999999999</v>
       </c>
       <c r="F70">
-        <v>19618.272</v>
+        <v>19906.776</v>
       </c>
       <c r="G70">
         <v>4375.4</v>
@@ -7033,28 +7033,28 @@
         <v>3004.7</v>
       </c>
       <c r="M70">
-        <v>1797.641445454203</v>
+        <v>1824.077349063823</v>
       </c>
       <c r="N70">
-        <v>1207.058554545797</v>
+        <v>1180.622650936176</v>
       </c>
       <c r="O70">
-        <v>301.7646386364493</v>
+        <v>295.1556627340441</v>
       </c>
       <c r="P70">
-        <v>905.2939159093478</v>
+        <v>885.4669882021323</v>
       </c>
       <c r="Q70">
-        <v>3954.593915909348</v>
+        <v>3934.766988202132</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2025552982329168</v>
+        <v>0.2071245354530757</v>
       </c>
       <c r="T70">
-        <v>2.424954609504367</v>
+        <v>2.495639256108654</v>
       </c>
       <c r="U70">
         <v>0.09163097776675758</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.671467915694842</v>
+        <v>1.647243743003613</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1116276369847505</v>
+        <v>0.1117057798739213</v>
       </c>
       <c r="C71">
-        <v>5671.489811292911</v>
+        <v>5357.846086122157</v>
       </c>
       <c r="D71">
-        <v>21202.86581129291</v>
+        <v>21177.72608612216</v>
       </c>
       <c r="E71">
-        <v>5306.075999999999</v>
+        <v>5594.58</v>
       </c>
       <c r="F71">
-        <v>19906.776</v>
+        <v>20195.28</v>
       </c>
       <c r="G71">
         <v>4375.4</v>
@@ -7115,28 +7115,28 @@
         <v>3004.7</v>
       </c>
       <c r="M71">
-        <v>1824.077349063823</v>
+        <v>1850.513252673444</v>
       </c>
       <c r="N71">
-        <v>1180.622650936176</v>
+        <v>1154.186747326556</v>
       </c>
       <c r="O71">
-        <v>295.1556627340441</v>
+        <v>288.5466868316389</v>
       </c>
       <c r="P71">
-        <v>885.4669882021323</v>
+        <v>865.6400604949167</v>
       </c>
       <c r="Q71">
-        <v>3934.766988202132</v>
+        <v>3914.940060494917</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2071245354530757</v>
+        <v>0.2119983884879118</v>
       </c>
       <c r="T71">
-        <v>2.495639256108654</v>
+        <v>2.571036212486558</v>
       </c>
       <c r="U71">
         <v>0.09163097776675758</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.647243743003613</v>
+        <v>1.623711689532132</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1117057798739213</v>
+        <v>0.111783922763092</v>
       </c>
       <c r="C72">
-        <v>5357.846086122157</v>
+        <v>5044.261905479081</v>
       </c>
       <c r="D72">
-        <v>21177.72608612216</v>
+        <v>21152.64590547909</v>
       </c>
       <c r="E72">
-        <v>5594.58</v>
+        <v>5883.084000000001</v>
       </c>
       <c r="F72">
-        <v>20195.28</v>
+        <v>20483.784</v>
       </c>
       <c r="G72">
         <v>4375.4</v>
@@ -7197,28 +7197,28 @@
         <v>3004.7</v>
       </c>
       <c r="M72">
-        <v>1850.513252673444</v>
+        <v>1876.949156283065</v>
       </c>
       <c r="N72">
-        <v>1154.186747326556</v>
+        <v>1127.750843716935</v>
       </c>
       <c r="O72">
-        <v>288.5466868316389</v>
+        <v>281.9377109292337</v>
       </c>
       <c r="P72">
-        <v>865.6400604949167</v>
+        <v>845.8131327877012</v>
       </c>
       <c r="Q72">
-        <v>3914.940060494917</v>
+        <v>3895.113132787701</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2119983884879118</v>
+        <v>0.2172083693182539</v>
       </c>
       <c r="T72">
-        <v>2.571036212486558</v>
+        <v>2.651632958959492</v>
       </c>
       <c r="U72">
         <v>0.09163097776675758</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.623711689532132</v>
+        <v>1.600842510806328</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.111783922763092</v>
+        <v>0.1118620656522628</v>
       </c>
       <c r="C73">
-        <v>5044.261905479085</v>
+        <v>4730.737058063256</v>
       </c>
       <c r="D73">
-        <v>21152.64590547909</v>
+        <v>21127.62505806325</v>
       </c>
       <c r="E73">
-        <v>5883.083999999997</v>
+        <v>6171.587999999998</v>
       </c>
       <c r="F73">
-        <v>20483.784</v>
+        <v>20772.288</v>
       </c>
       <c r="G73">
         <v>4375.4</v>
@@ -7279,28 +7279,28 @@
         <v>3004.7</v>
       </c>
       <c r="M73">
-        <v>1876.949156283064</v>
+        <v>1903.385059892685</v>
       </c>
       <c r="N73">
-        <v>1127.750843716935</v>
+        <v>1101.314940107315</v>
       </c>
       <c r="O73">
-        <v>281.9377109292338</v>
+        <v>275.3287350268287</v>
       </c>
       <c r="P73">
-        <v>845.8131327877015</v>
+        <v>825.986205080486</v>
       </c>
       <c r="Q73">
-        <v>3895.113132787702</v>
+        <v>3875.286205080486</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2172083693182539</v>
+        <v>0.2227904916364775</v>
       </c>
       <c r="T73">
-        <v>2.651632958959491</v>
+        <v>2.737986615894776</v>
       </c>
       <c r="U73">
         <v>0.09163097776675758</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.600842510806328</v>
+        <v>1.578608587045129</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1118620656522628</v>
+        <v>0.1119402085414336</v>
       </c>
       <c r="C74">
-        <v>4730.737058063256</v>
+        <v>4417.271333572782</v>
       </c>
       <c r="D74">
-        <v>21127.62505806325</v>
+        <v>21102.66333357278</v>
       </c>
       <c r="E74">
-        <v>6171.587999999998</v>
+        <v>6460.091999999999</v>
       </c>
       <c r="F74">
-        <v>20772.288</v>
+        <v>21060.792</v>
       </c>
       <c r="G74">
         <v>4375.4</v>
@@ -7361,28 +7361,28 @@
         <v>3004.7</v>
       </c>
       <c r="M74">
-        <v>1903.385059892685</v>
+        <v>1929.820963502306</v>
       </c>
       <c r="N74">
-        <v>1101.314940107315</v>
+        <v>1074.879036497694</v>
       </c>
       <c r="O74">
-        <v>275.3287350268287</v>
+        <v>268.7197591244235</v>
       </c>
       <c r="P74">
-        <v>825.986205080486</v>
+        <v>806.1592773732705</v>
       </c>
       <c r="Q74">
-        <v>3875.286205080486</v>
+        <v>3855.459277373271</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2227904916364775</v>
+        <v>0.2287861044967918</v>
       </c>
       <c r="T74">
-        <v>2.737986615894776</v>
+        <v>2.830736840010453</v>
       </c>
       <c r="U74">
         <v>0.09163097776675758</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.578608587045129</v>
+        <v>1.556983811880127</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1119402085414336</v>
+        <v>0.1120183514306043</v>
       </c>
       <c r="C75">
-        <v>4417.271333572782</v>
+        <v>4103.864522698495</v>
       </c>
       <c r="D75">
-        <v>21102.66333357278</v>
+        <v>21077.7605226985</v>
       </c>
       <c r="E75">
-        <v>6460.091999999999</v>
+        <v>6748.596</v>
       </c>
       <c r="F75">
-        <v>21060.792</v>
+        <v>21349.296</v>
       </c>
       <c r="G75">
         <v>4375.4</v>
@@ -7443,28 +7443,28 @@
         <v>3004.7</v>
       </c>
       <c r="M75">
-        <v>1929.820963502306</v>
+        <v>1956.256867111927</v>
       </c>
       <c r="N75">
-        <v>1074.879036497694</v>
+        <v>1048.443132888073</v>
       </c>
       <c r="O75">
-        <v>268.7197591244235</v>
+        <v>262.1107832220183</v>
       </c>
       <c r="P75">
-        <v>806.1592773732705</v>
+        <v>786.3323496660549</v>
       </c>
       <c r="Q75">
-        <v>3855.459277373271</v>
+        <v>3835.632349666055</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2287861044967918</v>
+        <v>0.235242918346361</v>
       </c>
       <c r="T75">
-        <v>2.830736840010453</v>
+        <v>2.930621696750412</v>
       </c>
       <c r="U75">
         <v>0.09163097776675758</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.556983811880127</v>
+        <v>1.535943490097963</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1120183514306043</v>
+        <v>0.1120964943197751</v>
       </c>
       <c r="C76">
-        <v>4103.864522698495</v>
+        <v>3790.516417118059</v>
       </c>
       <c r="D76">
-        <v>21077.7605226985</v>
+        <v>21052.91641711806</v>
       </c>
       <c r="E76">
-        <v>6748.596</v>
+        <v>7037.1</v>
       </c>
       <c r="F76">
-        <v>21349.296</v>
+        <v>21637.8</v>
       </c>
       <c r="G76">
         <v>4375.4</v>
@@ -7525,28 +7525,28 @@
         <v>3004.7</v>
       </c>
       <c r="M76">
-        <v>1956.256867111927</v>
+        <v>1982.692770721547</v>
       </c>
       <c r="N76">
-        <v>1048.443132888073</v>
+        <v>1022.007229278453</v>
       </c>
       <c r="O76">
-        <v>262.1107832220183</v>
+        <v>255.5018073196131</v>
       </c>
       <c r="P76">
-        <v>786.3323496660549</v>
+        <v>766.5054219588394</v>
       </c>
       <c r="Q76">
-        <v>3835.632349666055</v>
+        <v>3815.805421958839</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.235242918346361</v>
+        <v>0.2422162773038957</v>
       </c>
       <c r="T76">
-        <v>2.930621696750412</v>
+        <v>3.038497342029569</v>
       </c>
       <c r="U76">
         <v>0.09163097776675758</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.535943490097963</v>
+        <v>1.515464243563323</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1120964943197751</v>
+        <v>0.1202686372089458</v>
       </c>
       <c r="C77">
-        <v>3790.516417118059</v>
+        <v>1191.678192634765</v>
       </c>
       <c r="D77">
-        <v>21052.91641711806</v>
+        <v>18742.58219263477</v>
       </c>
       <c r="E77">
-        <v>7037.1</v>
+        <v>7325.603999999998</v>
       </c>
       <c r="F77">
-        <v>21637.8</v>
+        <v>21926.304</v>
       </c>
       <c r="G77">
         <v>4375.4</v>
@@ -7607,45 +7607,45 @@
         <v>3004.7</v>
       </c>
       <c r="M77">
-        <v>1982.692770721547</v>
+        <v>2320.482191131168</v>
       </c>
       <c r="N77">
-        <v>1022.007229278453</v>
+        <v>684.217808868832</v>
       </c>
       <c r="O77">
-        <v>255.5018073196131</v>
+        <v>171.054452217208</v>
       </c>
       <c r="P77">
-        <v>766.5054219588394</v>
+        <v>513.163356651624</v>
       </c>
       <c r="Q77">
-        <v>3815.805421958839</v>
+        <v>3562.463356651624</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2422162773038957</v>
+        <v>0.2497707495078917</v>
       </c>
       <c r="T77">
-        <v>3.038497342029569</v>
+        <v>3.155362624415321</v>
       </c>
       <c r="U77">
-        <v>0.09163097776675758</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V77">
         <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.06872323332506819</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.515464243563323</v>
+        <v>1.294860185302821</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1202686372089458</v>
+        <v>0.1204532800981166</v>
       </c>
       <c r="C78">
-        <v>1191.678192634765</v>
+        <v>856.8174281092179</v>
       </c>
       <c r="D78">
-        <v>18742.58219263477</v>
+        <v>18696.22542810922</v>
       </c>
       <c r="E78">
-        <v>7325.603999999998</v>
+        <v>7614.107999999998</v>
       </c>
       <c r="F78">
-        <v>21926.304</v>
+        <v>22214.808</v>
       </c>
       <c r="G78">
         <v>4375.4</v>
@@ -7689,28 +7689,28 @@
         <v>3004.7</v>
       </c>
       <c r="M78">
-        <v>2320.482191131168</v>
+        <v>2351.014851540789</v>
       </c>
       <c r="N78">
-        <v>684.217808868832</v>
+        <v>653.6851484592112</v>
       </c>
       <c r="O78">
-        <v>171.054452217208</v>
+        <v>163.4212871148028</v>
       </c>
       <c r="P78">
-        <v>513.163356651624</v>
+        <v>490.2638613444084</v>
       </c>
       <c r="Q78">
-        <v>3562.463356651624</v>
+        <v>3539.563861344408</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2497707495078917</v>
+        <v>0.2579821323383222</v>
       </c>
       <c r="T78">
-        <v>3.155362624415321</v>
+        <v>3.282390105269401</v>
       </c>
       <c r="U78">
         <v>0.1058309777667576</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.294860185302821</v>
+        <v>1.278043819259927</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1204532800981166</v>
+        <v>0.1206379229872873</v>
       </c>
       <c r="C79">
-        <v>856.8174281092179</v>
+        <v>522.1854098286967</v>
       </c>
       <c r="D79">
-        <v>18696.22542810922</v>
+        <v>18650.0974098287</v>
       </c>
       <c r="E79">
-        <v>7614.107999999998</v>
+        <v>7902.611999999999</v>
       </c>
       <c r="F79">
-        <v>22214.808</v>
+        <v>22503.312</v>
       </c>
       <c r="G79">
         <v>4375.4</v>
@@ -7771,28 +7771,28 @@
         <v>3004.7</v>
       </c>
       <c r="M79">
-        <v>2351.014851540789</v>
+        <v>2381.547511950409</v>
       </c>
       <c r="N79">
-        <v>653.6851484592112</v>
+        <v>623.1524880495904</v>
       </c>
       <c r="O79">
-        <v>163.4212871148028</v>
+        <v>155.7881220123976</v>
       </c>
       <c r="P79">
-        <v>490.2638613444084</v>
+        <v>467.3643660371928</v>
       </c>
       <c r="Q79">
-        <v>3539.563861344408</v>
+        <v>3516.664366037193</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2579821323383222</v>
+        <v>0.2669400045169735</v>
       </c>
       <c r="T79">
-        <v>3.282390105269401</v>
+        <v>3.420965538928395</v>
       </c>
       <c r="U79">
         <v>0.1058309777667576</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.278043819259927</v>
+        <v>1.261658642089928</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1206379229872873</v>
+        <v>0.1385120090705982</v>
       </c>
       <c r="C80">
-        <v>522.1854098286967</v>
+        <v>-3361.89860086409</v>
       </c>
       <c r="D80">
-        <v>18650.0974098287</v>
+        <v>15054.51739913592</v>
       </c>
       <c r="E80">
-        <v>7902.611999999999</v>
+        <v>8191.116</v>
       </c>
       <c r="F80">
-        <v>22503.312</v>
+        <v>22791.816</v>
       </c>
       <c r="G80">
         <v>4375.4</v>
@@ -7853,45 +7853,45 @@
         <v>3004.7</v>
       </c>
       <c r="M80">
-        <v>2381.547511950409</v>
+        <v>3063.92610996003</v>
       </c>
       <c r="N80">
-        <v>623.1524880495904</v>
+        <v>-59.22610996003004</v>
       </c>
       <c r="O80">
-        <v>155.7881220123976</v>
+        <v>-14.80652749000751</v>
       </c>
       <c r="P80">
-        <v>467.3643660371928</v>
+        <v>-44.41958247002253</v>
       </c>
       <c r="Q80">
-        <v>3516.664366037193</v>
+        <v>3004.880417529977</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2669400045169735</v>
+        <v>0.2778497016019513</v>
       </c>
       <c r="T80">
-        <v>3.420965538928395</v>
+        <v>3.589735083133555</v>
       </c>
       <c r="U80">
-        <v>0.1058309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V80">
-        <v>0.25</v>
+        <v>0.2451674658726673</v>
       </c>
       <c r="W80">
-        <v>0.07937323332506818</v>
+        <v>0.1014728756128967</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.261658642089928</v>
+        <v>0.9806698634906693</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1385120090705982</v>
+        <v>0.1393983188482658</v>
       </c>
       <c r="C81">
-        <v>-3361.89860086409</v>
+        <v>-3792.958216532268</v>
       </c>
       <c r="D81">
-        <v>15054.51739913592</v>
+        <v>14911.96178346774</v>
       </c>
       <c r="E81">
-        <v>8191.116</v>
+        <v>8479.620000000001</v>
       </c>
       <c r="F81">
-        <v>22791.816</v>
+        <v>23080.32</v>
       </c>
       <c r="G81">
         <v>4375.4</v>
@@ -7935,37 +7935,37 @@
         <v>3004.7</v>
       </c>
       <c r="M81">
-        <v>3063.92610996003</v>
+        <v>3102.709984769651</v>
       </c>
       <c r="N81">
-        <v>-59.22610996003004</v>
+        <v>-98.00998476965106</v>
       </c>
       <c r="O81">
-        <v>-14.80652749000751</v>
+        <v>-24.50249619241276</v>
       </c>
       <c r="P81">
-        <v>-44.41958247002253</v>
+        <v>-73.50748857723829</v>
       </c>
       <c r="Q81">
-        <v>3004.880417529977</v>
+        <v>2975.792511422762</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2778497016019513</v>
+        <v>0.2894521866820489</v>
       </c>
       <c r="T81">
-        <v>3.589735083133555</v>
+        <v>3.769221837290234</v>
       </c>
       <c r="U81">
         <v>0.1344309777667576</v>
       </c>
       <c r="V81">
-        <v>0.2451674658726673</v>
+        <v>0.2421028725492589</v>
       </c>
       <c r="W81">
-        <v>0.1014728756128967</v>
+        <v>0.10188485188982</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9806698634906693</v>
+        <v>0.9684114901970358</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1393983188482658</v>
+        <v>0.1402846286259334</v>
       </c>
       <c r="C82">
-        <v>-3792.958216532268</v>
+        <v>-4221.343356195928</v>
       </c>
       <c r="D82">
-        <v>14911.96178346774</v>
+        <v>14772.08064380408</v>
       </c>
       <c r="E82">
-        <v>8479.620000000001</v>
+        <v>8768.124000000002</v>
       </c>
       <c r="F82">
-        <v>23080.32</v>
+        <v>23368.824</v>
       </c>
       <c r="G82">
         <v>4375.4</v>
@@ -8017,37 +8017,37 @@
         <v>3004.7</v>
       </c>
       <c r="M82">
-        <v>3102.709984769651</v>
+        <v>3141.493859579271</v>
       </c>
       <c r="N82">
-        <v>-98.00998476965106</v>
+        <v>-136.7938595792716</v>
       </c>
       <c r="O82">
-        <v>-24.50249619241276</v>
+        <v>-34.1984648948179</v>
       </c>
       <c r="P82">
-        <v>-73.50748857723829</v>
+        <v>-102.5953946844537</v>
       </c>
       <c r="Q82">
-        <v>2975.792511422762</v>
+        <v>2946.704605315546</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2894521866820489</v>
+        <v>0.3022759859811042</v>
       </c>
       <c r="T82">
-        <v>3.769221837290234</v>
+        <v>3.96760193398972</v>
       </c>
       <c r="U82">
         <v>0.1344309777667576</v>
       </c>
       <c r="V82">
-        <v>0.2421028725492589</v>
+        <v>0.239113948196799</v>
       </c>
       <c r="W82">
-        <v>0.10188485188982</v>
+        <v>0.1022866559129921</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9684114901970358</v>
+        <v>0.9564557927871958</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1402846286259334</v>
+        <v>0.1411709384036009</v>
       </c>
       <c r="C83">
-        <v>-4221.343356195928</v>
+        <v>-4647.128583897495</v>
       </c>
       <c r="D83">
-        <v>14772.08064380408</v>
+        <v>14634.79941610251</v>
       </c>
       <c r="E83">
-        <v>8768.124000000002</v>
+        <v>9056.627999999999</v>
       </c>
       <c r="F83">
-        <v>23368.824</v>
+        <v>23657.328</v>
       </c>
       <c r="G83">
         <v>4375.4</v>
@@ -8099,37 +8099,37 @@
         <v>3004.7</v>
       </c>
       <c r="M83">
-        <v>3141.493859579271</v>
+        <v>3180.277734388892</v>
       </c>
       <c r="N83">
-        <v>-136.7938595792716</v>
+        <v>-175.5777343888922</v>
       </c>
       <c r="O83">
-        <v>-34.1984648948179</v>
+        <v>-43.89443359722304</v>
       </c>
       <c r="P83">
-        <v>-102.5953946844537</v>
+        <v>-131.6833007916691</v>
       </c>
       <c r="Q83">
-        <v>2946.704605315546</v>
+        <v>2917.616699208331</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3022759859811042</v>
+        <v>0.3165246518689433</v>
       </c>
       <c r="T83">
-        <v>3.96760193398972</v>
+        <v>4.188024263655816</v>
       </c>
       <c r="U83">
         <v>0.1344309777667576</v>
       </c>
       <c r="V83">
-        <v>0.239113948196799</v>
+        <v>0.2361979244383014</v>
       </c>
       <c r="W83">
-        <v>0.1022866559129921</v>
+        <v>0.102678659838038</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9564557927871958</v>
+        <v>0.9447916977532057</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1411709384036009</v>
+        <v>0.1420572481812685</v>
       </c>
       <c r="C84">
-        <v>-4647.128583897495</v>
+        <v>-5070.385717420162</v>
       </c>
       <c r="D84">
-        <v>14634.79941610251</v>
+        <v>14500.04628257984</v>
       </c>
       <c r="E84">
-        <v>9056.627999999999</v>
+        <v>9345.132</v>
       </c>
       <c r="F84">
-        <v>23657.328</v>
+        <v>23945.832</v>
       </c>
       <c r="G84">
         <v>4375.4</v>
@@ -8181,37 +8181,37 @@
         <v>3004.7</v>
       </c>
       <c r="M84">
-        <v>3180.277734388892</v>
+        <v>3219.061609198513</v>
       </c>
       <c r="N84">
-        <v>-175.5777343888922</v>
+        <v>-214.3616091985127</v>
       </c>
       <c r="O84">
-        <v>-43.89443359722304</v>
+        <v>-53.59040229962818</v>
       </c>
       <c r="P84">
-        <v>-131.6833007916691</v>
+        <v>-160.7712068988845</v>
       </c>
       <c r="Q84">
-        <v>2917.616699208331</v>
+        <v>2888.528793101116</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3165246518689433</v>
+        <v>0.3324496313906458</v>
       </c>
       <c r="T84">
-        <v>4.188024263655816</v>
+        <v>4.434378632106157</v>
       </c>
       <c r="U84">
         <v>0.1344309777667576</v>
       </c>
       <c r="V84">
-        <v>0.2361979244383014</v>
+        <v>0.2333521663125388</v>
       </c>
       <c r="W84">
-        <v>0.102678659838038</v>
+        <v>0.103061217885372</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9447916977532057</v>
+        <v>0.9334086652501551</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1420572481812685</v>
+        <v>0.1429435579589361</v>
       </c>
       <c r="C85">
-        <v>-5070.385717420162</v>
+        <v>-5491.183953568237</v>
       </c>
       <c r="D85">
-        <v>14500.04628257984</v>
+        <v>14367.75204643177</v>
       </c>
       <c r="E85">
-        <v>9345.132</v>
+        <v>9633.636</v>
       </c>
       <c r="F85">
-        <v>23945.832</v>
+        <v>24234.336</v>
       </c>
       <c r="G85">
         <v>4375.4</v>
@@ -8263,37 +8263,37 @@
         <v>3004.7</v>
       </c>
       <c r="M85">
-        <v>3219.061609198513</v>
+        <v>3257.845484008133</v>
       </c>
       <c r="N85">
-        <v>-214.3616091985127</v>
+        <v>-253.1454840081333</v>
       </c>
       <c r="O85">
-        <v>-53.59040229962818</v>
+        <v>-63.28637100203332</v>
       </c>
       <c r="P85">
-        <v>-160.7712068988845</v>
+        <v>-189.8591130061</v>
       </c>
       <c r="Q85">
-        <v>2888.528793101116</v>
+        <v>2859.4408869939</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3324496313906458</v>
+        <v>0.3503652333525613</v>
       </c>
       <c r="T85">
-        <v>4.434378632106157</v>
+        <v>4.711527296612794</v>
       </c>
       <c r="U85">
         <v>0.1344309777667576</v>
       </c>
       <c r="V85">
-        <v>0.2333521663125388</v>
+        <v>0.2305741643326276</v>
       </c>
       <c r="W85">
-        <v>0.103061217885372</v>
+        <v>0.1034346674077694</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9334086652501551</v>
+        <v>0.9222966573305104</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1429435579589361</v>
+        <v>0.1438298677366037</v>
       </c>
       <c r="C86">
-        <v>-5491.183953568234</v>
+        <v>-5909.589986651368</v>
       </c>
       <c r="D86">
-        <v>14367.75204643177</v>
+        <v>14237.85001334863</v>
       </c>
       <c r="E86">
-        <v>9633.635999999997</v>
+        <v>9922.139999999998</v>
       </c>
       <c r="F86">
-        <v>24234.336</v>
+        <v>24522.84</v>
       </c>
       <c r="G86">
         <v>4375.4</v>
@@ -8345,37 +8345,37 @@
         <v>3004.7</v>
       </c>
       <c r="M86">
-        <v>3257.845484008133</v>
+        <v>3296.629358817754</v>
       </c>
       <c r="N86">
-        <v>-253.1454840081328</v>
+        <v>-291.9293588177538</v>
       </c>
       <c r="O86">
-        <v>-63.28637100203321</v>
+        <v>-72.98233970443846</v>
       </c>
       <c r="P86">
-        <v>-189.8591130060996</v>
+        <v>-218.9470191133154</v>
       </c>
       <c r="Q86">
-        <v>2859.440886993901</v>
+        <v>2830.352980886685</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3503652333525611</v>
+        <v>0.3706695822427318</v>
       </c>
       <c r="T86">
-        <v>4.711527296612791</v>
+        <v>5.025629116386976</v>
       </c>
       <c r="U86">
         <v>0.1344309777667576</v>
       </c>
       <c r="V86">
-        <v>0.2305741643326276</v>
+        <v>0.2278615271051849</v>
       </c>
       <c r="W86">
-        <v>0.1034346674077694</v>
+        <v>0.103799329882581</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9222966573305105</v>
+        <v>0.9114461084207397</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1438298677366037</v>
+        <v>0.1447161775142712</v>
       </c>
       <c r="C87">
-        <v>-5909.589986651368</v>
+        <v>-6325.668120599013</v>
       </c>
       <c r="D87">
-        <v>14237.85001334863</v>
+        <v>14110.27587940099</v>
       </c>
       <c r="E87">
-        <v>9922.139999999998</v>
+        <v>10210.644</v>
       </c>
       <c r="F87">
-        <v>24522.84</v>
+        <v>24811.344</v>
       </c>
       <c r="G87">
         <v>4375.4</v>
@@ -8427,37 +8427,37 @@
         <v>3004.7</v>
       </c>
       <c r="M87">
-        <v>3296.629358817754</v>
+        <v>3335.413233627374</v>
       </c>
       <c r="N87">
-        <v>-291.9293588177538</v>
+        <v>-330.7132336273744</v>
       </c>
       <c r="O87">
-        <v>-72.98233970443846</v>
+        <v>-82.6783084068436</v>
       </c>
       <c r="P87">
-        <v>-218.9470191133154</v>
+        <v>-248.0349252205308</v>
       </c>
       <c r="Q87">
-        <v>2830.352980886685</v>
+        <v>2801.26507477947</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3706695822427318</v>
+        <v>0.3938745524029269</v>
       </c>
       <c r="T87">
-        <v>5.025629116386976</v>
+        <v>5.384602624700332</v>
       </c>
       <c r="U87">
         <v>0.1344309777667576</v>
       </c>
       <c r="V87">
-        <v>0.2278615271051849</v>
+        <v>0.225211974464427</v>
       </c>
       <c r="W87">
-        <v>0.103799329882581</v>
+        <v>0.1041555118347226</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9114461084207397</v>
+        <v>0.9008478978577078</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1447161775142712</v>
+        <v>0.1456024872919388</v>
       </c>
       <c r="C88">
-        <v>-6325.668120599013</v>
+        <v>-6739.480375100913</v>
       </c>
       <c r="D88">
-        <v>14110.27587940099</v>
+        <v>13984.96762489909</v>
       </c>
       <c r="E88">
-        <v>10210.644</v>
+        <v>10499.148</v>
       </c>
       <c r="F88">
-        <v>24811.344</v>
+        <v>25099.848</v>
       </c>
       <c r="G88">
         <v>4375.4</v>
@@ -8509,37 +8509,37 @@
         <v>3004.7</v>
       </c>
       <c r="M88">
-        <v>3335.413233627374</v>
+        <v>3374.197108436995</v>
       </c>
       <c r="N88">
-        <v>-330.7132336273744</v>
+        <v>-369.4971084369949</v>
       </c>
       <c r="O88">
-        <v>-82.6783084068436</v>
+        <v>-92.37427710924874</v>
       </c>
       <c r="P88">
-        <v>-248.0349252205308</v>
+        <v>-277.1228313277462</v>
       </c>
       <c r="Q88">
-        <v>2801.26507477947</v>
+        <v>2772.177168672254</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3938745524029269</v>
+        <v>0.4206495179723828</v>
       </c>
       <c r="T88">
-        <v>5.384602624700332</v>
+        <v>5.798802826600357</v>
       </c>
       <c r="U88">
         <v>0.1344309777667576</v>
       </c>
       <c r="V88">
-        <v>0.225211974464427</v>
+        <v>0.2226233310797784</v>
       </c>
       <c r="W88">
-        <v>0.1041555118347226</v>
+        <v>0.1045035056960104</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9008478978577078</v>
+        <v>0.8904933243191135</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1456024872919388</v>
+        <v>0.1464887970696064</v>
       </c>
       <c r="C89">
-        <v>-6739.480375100913</v>
+        <v>-7151.08658614177</v>
       </c>
       <c r="D89">
-        <v>13984.96762489909</v>
+        <v>13861.86541385823</v>
       </c>
       <c r="E89">
-        <v>10499.148</v>
+        <v>10787.652</v>
       </c>
       <c r="F89">
-        <v>25099.848</v>
+        <v>25388.352</v>
       </c>
       <c r="G89">
         <v>4375.4</v>
@@ -8591,37 +8591,37 @@
         <v>3004.7</v>
       </c>
       <c r="M89">
-        <v>3374.197108436995</v>
+        <v>3412.980983246616</v>
       </c>
       <c r="N89">
-        <v>-369.4971084369949</v>
+        <v>-408.280983246616</v>
       </c>
       <c r="O89">
-        <v>-92.37427710924874</v>
+        <v>-102.070245811654</v>
       </c>
       <c r="P89">
-        <v>-277.1228313277462</v>
+        <v>-306.210737434962</v>
       </c>
       <c r="Q89">
-        <v>2772.177168672254</v>
+        <v>2743.089262565038</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4206495179723828</v>
+        <v>0.4518869778034149</v>
       </c>
       <c r="T89">
-        <v>5.798802826600357</v>
+        <v>6.282036395483722</v>
       </c>
       <c r="U89">
         <v>0.1344309777667576</v>
       </c>
       <c r="V89">
-        <v>0.2226233310797784</v>
+        <v>0.2200935204993263</v>
       </c>
       <c r="W89">
-        <v>0.1045035056960104</v>
+        <v>0.1048435906059052</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8904933243191135</v>
+        <v>0.8803740819973053</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1464887970696064</v>
+        <v>0.147375106847274</v>
       </c>
       <c r="C90">
-        <v>-7151.08658614177</v>
+        <v>-7560.544501272638</v>
       </c>
       <c r="D90">
-        <v>13861.86541385823</v>
+        <v>13740.91149872736</v>
       </c>
       <c r="E90">
-        <v>10787.652</v>
+        <v>11076.156</v>
       </c>
       <c r="F90">
-        <v>25388.352</v>
+        <v>25676.856</v>
       </c>
       <c r="G90">
         <v>4375.4</v>
@@ -8673,37 +8673,37 @@
         <v>3004.7</v>
       </c>
       <c r="M90">
-        <v>3412.980983246616</v>
+        <v>3451.764858056236</v>
       </c>
       <c r="N90">
-        <v>-408.280983246616</v>
+        <v>-447.0648580562365</v>
       </c>
       <c r="O90">
-        <v>-102.070245811654</v>
+        <v>-111.7662145140591</v>
       </c>
       <c r="P90">
-        <v>-306.210737434962</v>
+        <v>-335.2986435421774</v>
       </c>
       <c r="Q90">
-        <v>2743.089262565038</v>
+        <v>2714.001356457823</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4518869778034149</v>
+        <v>0.4888039757855435</v>
       </c>
       <c r="T90">
-        <v>6.282036395483722</v>
+        <v>6.85313061325497</v>
       </c>
       <c r="U90">
         <v>0.1344309777667576</v>
       </c>
       <c r="V90">
-        <v>0.2200935204993263</v>
+        <v>0.2176205595948395</v>
       </c>
       <c r="W90">
-        <v>0.1048435906059052</v>
+        <v>0.1051760331582744</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8803740819973053</v>
+        <v>0.8704822383793581</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.147375106847274</v>
+        <v>0.1482614166249415</v>
       </c>
       <c r="C91">
-        <v>-7560.544501272638</v>
+        <v>-7967.909869937554</v>
       </c>
       <c r="D91">
-        <v>13740.91149872736</v>
+        <v>13622.05013006245</v>
       </c>
       <c r="E91">
-        <v>11076.156</v>
+        <v>11364.66</v>
       </c>
       <c r="F91">
-        <v>25676.856</v>
+        <v>25965.36</v>
       </c>
       <c r="G91">
         <v>4375.4</v>
@@ -8755,37 +8755,37 @@
         <v>3004.7</v>
       </c>
       <c r="M91">
-        <v>3451.764858056236</v>
+        <v>3490.548732865857</v>
       </c>
       <c r="N91">
-        <v>-447.0648580562365</v>
+        <v>-485.8487328658571</v>
       </c>
       <c r="O91">
-        <v>-111.7662145140591</v>
+        <v>-121.4621832164643</v>
       </c>
       <c r="P91">
-        <v>-335.2986435421774</v>
+        <v>-364.3865496493928</v>
       </c>
       <c r="Q91">
-        <v>2714.001356457823</v>
+        <v>2684.913450350607</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4888039757855435</v>
+        <v>0.5331043733640978</v>
       </c>
       <c r="T91">
-        <v>6.85313061325497</v>
+        <v>7.538443674580466</v>
       </c>
       <c r="U91">
         <v>0.1344309777667576</v>
       </c>
       <c r="V91">
-        <v>0.2176205595948395</v>
+        <v>0.2152025533771191</v>
       </c>
       <c r="W91">
-        <v>0.1051760331582744</v>
+        <v>0.1055010880983686</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8704822383793581</v>
+        <v>0.8608102135084763</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1482614166249415</v>
+        <v>0.1491477264026091</v>
       </c>
       <c r="C92">
-        <v>-7967.909869937554</v>
+        <v>-8373.236529152317</v>
       </c>
       <c r="D92">
-        <v>13622.05013006245</v>
+        <v>13505.22747084769</v>
       </c>
       <c r="E92">
-        <v>11364.66</v>
+        <v>11653.164</v>
       </c>
       <c r="F92">
-        <v>25965.36</v>
+        <v>26253.864</v>
       </c>
       <c r="G92">
         <v>4375.4</v>
@@ -8837,37 +8837,37 @@
         <v>3004.7</v>
       </c>
       <c r="M92">
-        <v>3490.548732865857</v>
+        <v>3529.332607675477</v>
       </c>
       <c r="N92">
-        <v>-485.8487328658571</v>
+        <v>-524.6326076754776</v>
       </c>
       <c r="O92">
-        <v>-121.4621832164643</v>
+        <v>-131.1581519188694</v>
       </c>
       <c r="P92">
-        <v>-364.3865496493928</v>
+        <v>-393.4744557566082</v>
       </c>
       <c r="Q92">
-        <v>2684.913450350607</v>
+        <v>2655.825544243392</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5331043733640978</v>
+        <v>0.5872493037378865</v>
       </c>
       <c r="T92">
-        <v>7.538443674580466</v>
+        <v>8.376048527311632</v>
       </c>
       <c r="U92">
         <v>0.1344309777667576</v>
       </c>
       <c r="V92">
-        <v>0.2152025533771191</v>
+        <v>0.2128376901531947</v>
       </c>
       <c r="W92">
-        <v>0.1055010880983686</v>
+        <v>0.1058189989738454</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8608102135084763</v>
+        <v>0.8513507606127788</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1491477264026091</v>
+        <v>0.1500340361802767</v>
       </c>
       <c r="C93">
-        <v>-8373.236529152317</v>
+        <v>-8776.576484812085</v>
       </c>
       <c r="D93">
-        <v>13505.22747084769</v>
+        <v>13390.39151518792</v>
       </c>
       <c r="E93">
-        <v>11653.164</v>
+        <v>11941.668</v>
       </c>
       <c r="F93">
-        <v>26253.864</v>
+        <v>26542.368</v>
       </c>
       <c r="G93">
         <v>4375.4</v>
@@ -8919,37 +8919,37 @@
         <v>3004.7</v>
       </c>
       <c r="M93">
-        <v>3529.332607675477</v>
+        <v>3568.116482485098</v>
       </c>
       <c r="N93">
-        <v>-524.6326076754776</v>
+        <v>-563.4164824850982</v>
       </c>
       <c r="O93">
-        <v>-131.1581519188694</v>
+        <v>-140.8541206212745</v>
       </c>
       <c r="P93">
-        <v>-393.4744557566082</v>
+        <v>-422.5623618638236</v>
       </c>
       <c r="Q93">
-        <v>2655.825544243392</v>
+        <v>2626.737638136176</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5872493037378865</v>
+        <v>0.6549304667051224</v>
       </c>
       <c r="T93">
-        <v>8.376048527311632</v>
+        <v>9.423054593225586</v>
       </c>
       <c r="U93">
         <v>0.1344309777667576</v>
       </c>
       <c r="V93">
-        <v>0.2128376901531947</v>
+        <v>0.2105242369993556</v>
       </c>
       <c r="W93">
-        <v>0.1058189989738454</v>
+        <v>0.1061299987433336</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8513507606127788</v>
+        <v>0.8420969479974225</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1500340361802767</v>
+        <v>0.1509203459579443</v>
       </c>
       <c r="C94">
-        <v>-8776.576484812085</v>
+        <v>-9177.979988885789</v>
       </c>
       <c r="D94">
-        <v>13390.39151518792</v>
+        <v>13277.49201111421</v>
       </c>
       <c r="E94">
-        <v>11941.668</v>
+        <v>12230.172</v>
       </c>
       <c r="F94">
-        <v>26542.368</v>
+        <v>26830.872</v>
       </c>
       <c r="G94">
         <v>4375.4</v>
@@ -9001,37 +9001,37 @@
         <v>3004.7</v>
       </c>
       <c r="M94">
-        <v>3568.116482485098</v>
+        <v>3606.900357294719</v>
       </c>
       <c r="N94">
-        <v>-563.4164824850982</v>
+        <v>-602.2003572947192</v>
       </c>
       <c r="O94">
-        <v>-140.8541206212745</v>
+        <v>-150.5500893236798</v>
       </c>
       <c r="P94">
-        <v>-422.5623618638236</v>
+        <v>-451.6502679710394</v>
       </c>
       <c r="Q94">
-        <v>2626.737638136176</v>
+        <v>2597.649732028961</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6549304667051224</v>
+        <v>0.7419491048058543</v>
       </c>
       <c r="T94">
-        <v>9.423054593225586</v>
+        <v>10.76920524940067</v>
       </c>
       <c r="U94">
         <v>0.1344309777667576</v>
       </c>
       <c r="V94">
-        <v>0.2105242369993556</v>
+        <v>0.2082605355262443</v>
       </c>
       <c r="W94">
-        <v>0.1061299987433336</v>
+        <v>0.106434310345736</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8420969479974225</v>
+        <v>0.8330421421049771</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1509203459579443</v>
+        <v>0.1518066557356119</v>
       </c>
       <c r="C95">
-        <v>-9177.979988885789</v>
+        <v>-9577.495612738014</v>
       </c>
       <c r="D95">
-        <v>13277.49201111421</v>
+        <v>13166.48038726199</v>
       </c>
       <c r="E95">
-        <v>12230.172</v>
+        <v>12518.676</v>
       </c>
       <c r="F95">
-        <v>26830.872</v>
+        <v>27119.376</v>
       </c>
       <c r="G95">
         <v>4375.4</v>
@@ -9083,37 +9083,37 @@
         <v>3004.7</v>
       </c>
       <c r="M95">
-        <v>3606.900357294719</v>
+        <v>3645.68423210434</v>
       </c>
       <c r="N95">
-        <v>-602.2003572947192</v>
+        <v>-640.9842321043398</v>
       </c>
       <c r="O95">
-        <v>-150.5500893236798</v>
+        <v>-160.2460580260849</v>
       </c>
       <c r="P95">
-        <v>-451.6502679710394</v>
+        <v>-480.7381740782548</v>
       </c>
       <c r="Q95">
-        <v>2597.649732028961</v>
+        <v>2568.561825921745</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7419491048058543</v>
+        <v>0.8579739556068303</v>
       </c>
       <c r="T95">
-        <v>10.76920524940067</v>
+        <v>12.56407279096745</v>
       </c>
       <c r="U95">
         <v>0.1344309777667576</v>
       </c>
       <c r="V95">
-        <v>0.2082605355262443</v>
+        <v>0.206044997914263</v>
       </c>
       <c r="W95">
-        <v>0.106434310345736</v>
+        <v>0.1067321472331937</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8330421421049771</v>
+        <v>0.8241799916570518</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1518066557356119</v>
+        <v>0.1526929655132795</v>
       </c>
       <c r="C96">
-        <v>-9577.495612738014</v>
+        <v>-9975.170316803189</v>
       </c>
       <c r="D96">
-        <v>13166.48038726199</v>
+        <v>13057.30968319682</v>
       </c>
       <c r="E96">
-        <v>12518.676</v>
+        <v>12807.18</v>
       </c>
       <c r="F96">
-        <v>27119.376</v>
+        <v>27407.88</v>
       </c>
       <c r="G96">
         <v>4375.4</v>
@@ -9165,37 +9165,37 @@
         <v>3004.7</v>
       </c>
       <c r="M96">
-        <v>3645.68423210434</v>
+        <v>3684.468106913961</v>
       </c>
       <c r="N96">
-        <v>-640.9842321043398</v>
+        <v>-679.7681069139608</v>
       </c>
       <c r="O96">
-        <v>-160.2460580260849</v>
+        <v>-169.9420267284902</v>
       </c>
       <c r="P96">
-        <v>-480.7381740782548</v>
+        <v>-509.8260801854706</v>
       </c>
       <c r="Q96">
-        <v>2568.561825921745</v>
+        <v>2539.47391981453</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8579739556068303</v>
+        <v>1.020408746728197</v>
       </c>
       <c r="T96">
-        <v>12.56407279096745</v>
+        <v>15.07688734916096</v>
       </c>
       <c r="U96">
         <v>0.1344309777667576</v>
       </c>
       <c r="V96">
-        <v>0.206044997914263</v>
+        <v>0.2038761031993759</v>
       </c>
       <c r="W96">
-        <v>0.1067321472331937</v>
+        <v>0.1070237138703891</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8241799916570518</v>
+        <v>0.8155044127975037</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1526929655132795</v>
+        <v>0.153579275290947</v>
       </c>
       <c r="C97">
-        <v>-9975.170316803189</v>
+        <v>-10371.04951682202</v>
       </c>
       <c r="D97">
-        <v>13057.30968319682</v>
+        <v>12949.93448317798</v>
       </c>
       <c r="E97">
-        <v>12807.18</v>
+        <v>13095.684</v>
       </c>
       <c r="F97">
-        <v>27407.88</v>
+        <v>27696.384</v>
       </c>
       <c r="G97">
         <v>4375.4</v>
@@ -9247,37 +9247,37 @@
         <v>3004.7</v>
       </c>
       <c r="M97">
-        <v>3684.468106913961</v>
+        <v>3723.251981723581</v>
       </c>
       <c r="N97">
-        <v>-679.7681069139608</v>
+        <v>-718.5519817235809</v>
       </c>
       <c r="O97">
-        <v>-169.9420267284902</v>
+        <v>-179.6379954308952</v>
       </c>
       <c r="P97">
-        <v>-509.8260801854706</v>
+        <v>-538.9139862926856</v>
       </c>
       <c r="Q97">
-        <v>2539.47391981453</v>
+        <v>2510.386013707314</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.020408746728197</v>
+        <v>1.264060933410247</v>
       </c>
       <c r="T97">
-        <v>15.07688734916096</v>
+        <v>18.8461091864512</v>
       </c>
       <c r="U97">
         <v>0.1344309777667576</v>
       </c>
       <c r="V97">
-        <v>0.2038761031993759</v>
+        <v>0.2017523937910491</v>
       </c>
       <c r="W97">
-        <v>0.1070237138703891</v>
+        <v>0.1073092062026429</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8155044127975037</v>
+        <v>0.8070095751641966</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.153579275290947</v>
+        <v>0.1838492758499622</v>
       </c>
       <c r="C98">
-        <v>-10371.04951682202</v>
+        <v>-13499.07963263478</v>
       </c>
       <c r="D98">
-        <v>12949.93448317798</v>
+        <v>10110.40836736522</v>
       </c>
       <c r="E98">
-        <v>13095.684</v>
+        <v>13384.188</v>
       </c>
       <c r="F98">
-        <v>27696.384</v>
+        <v>27984.888</v>
       </c>
       <c r="G98">
         <v>4375.4</v>
@@ -9329,45 +9329,45 @@
         <v>3004.7</v>
       </c>
       <c r="M98">
-        <v>3723.251981723581</v>
+        <v>4551.209698133201</v>
       </c>
       <c r="N98">
-        <v>-718.5519817235809</v>
+        <v>-1546.509698133201</v>
       </c>
       <c r="O98">
-        <v>-179.6379954308952</v>
+        <v>-386.6274245333002</v>
       </c>
       <c r="P98">
-        <v>-538.9139862926856</v>
+        <v>-1159.882273599901</v>
       </c>
       <c r="Q98">
-        <v>2510.386013707314</v>
+        <v>1889.4177264001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.264060933410243</v>
+        <v>1.737804270591912</v>
       </c>
       <c r="T98">
-        <v>18.84610918645114</v>
+        <v>26.17476794421576</v>
       </c>
       <c r="U98">
-        <v>0.1344309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V98">
-        <v>0.2017523937910491</v>
+        <v>0.1650495252521795</v>
       </c>
       <c r="W98">
-        <v>0.1073092062026429</v>
+        <v>0.1357888120950565</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.8070095751641966</v>
+        <v>0.660198101008718</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1838492758499622</v>
+        <v>0.1850175856276298</v>
       </c>
       <c r="C99">
-        <v>-13499.07963263478</v>
+        <v>-13872.42987457004</v>
       </c>
       <c r="D99">
-        <v>10110.40836736522</v>
+        <v>10025.56212542996</v>
       </c>
       <c r="E99">
-        <v>13384.188</v>
+        <v>13672.692</v>
       </c>
       <c r="F99">
-        <v>27984.888</v>
+        <v>28273.392</v>
       </c>
       <c r="G99">
         <v>4375.4</v>
@@ -9411,37 +9411,37 @@
         <v>3004.7</v>
       </c>
       <c r="M99">
-        <v>4551.209698133201</v>
+        <v>4598.129385742822</v>
       </c>
       <c r="N99">
-        <v>-1546.509698133201</v>
+        <v>-1593.429385742822</v>
       </c>
       <c r="O99">
-        <v>-386.6274245333002</v>
+        <v>-398.3573464357055</v>
       </c>
       <c r="P99">
-        <v>-1159.882273599901</v>
+        <v>-1195.072039307116</v>
       </c>
       <c r="Q99">
-        <v>1889.4177264001</v>
+        <v>1854.227960692884</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.737804270591912</v>
+        <v>2.583806405887868</v>
       </c>
       <c r="T99">
-        <v>26.17476794421576</v>
+        <v>39.26215191632364</v>
       </c>
       <c r="U99">
         <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.1650495252521795</v>
+        <v>0.1633653464230756</v>
       </c>
       <c r="W99">
-        <v>0.1357888120950565</v>
+        <v>0.1360627117447677</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.660198101008718</v>
+        <v>0.6534613856923024</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1850175856276298</v>
+        <v>0.242057762254414</v>
       </c>
       <c r="C100">
-        <v>-13872.42987457004</v>
+        <v>-17074.75408656251</v>
       </c>
       <c r="D100">
-        <v>10025.56212542996</v>
+        <v>7111.741913437497</v>
       </c>
       <c r="E100">
-        <v>13672.692</v>
+        <v>13961.196</v>
       </c>
       <c r="F100">
-        <v>28273.392</v>
+        <v>28561.896</v>
       </c>
       <c r="G100">
         <v>4375.4</v>
@@ -9493,129 +9493,47 @@
         <v>3004.7</v>
       </c>
       <c r="M100">
-        <v>4598.129385742822</v>
+        <v>6187.391457352443</v>
       </c>
       <c r="N100">
-        <v>-1593.429385742822</v>
+        <v>-3182.691457352443</v>
       </c>
       <c r="O100">
-        <v>-398.3573464357055</v>
+        <v>-795.6728643381107</v>
       </c>
       <c r="P100">
-        <v>-1195.072039307116</v>
+        <v>-2387.018593014332</v>
       </c>
       <c r="Q100">
-        <v>1854.227960692884</v>
+        <v>662.2814069856681</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.583806405887868</v>
+        <v>5.3629994966874</v>
       </c>
       <c r="T100">
-        <v>39.26215191632364</v>
+        <v>82.25538514167319</v>
       </c>
       <c r="U100">
-        <v>0.1626309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1633653464230756</v>
+        <v>0.1214041499034917</v>
       </c>
       <c r="W100">
-        <v>0.1360627117447677</v>
+        <v>0.1903310780682222</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.6534613856923024</v>
+        <v>0.4856165996139669</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.242057762254414</v>
-      </c>
-      <c r="C101">
-        <v>-17074.75408656251</v>
-      </c>
-      <c r="D101">
-        <v>7111.741913437497</v>
-      </c>
-      <c r="E101">
-        <v>13961.196</v>
-      </c>
-      <c r="F101">
-        <v>28561.896</v>
-      </c>
-      <c r="G101">
-        <v>4375.4</v>
-      </c>
-      <c r="H101">
-        <v>14249.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6054</v>
-      </c>
-      <c r="K101">
-        <v>3049.3</v>
-      </c>
-      <c r="L101">
-        <v>3004.7</v>
-      </c>
-      <c r="M101">
-        <v>6187.391457352443</v>
-      </c>
-      <c r="N101">
-        <v>-3182.691457352443</v>
-      </c>
-      <c r="O101">
-        <v>-795.6728643381107</v>
-      </c>
-      <c r="P101">
-        <v>-2387.018593014332</v>
-      </c>
-      <c r="Q101">
-        <v>662.2814069856681</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.3629994966874</v>
-      </c>
-      <c r="T101">
-        <v>82.25538514167319</v>
-      </c>
-      <c r="U101">
-        <v>0.2166309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.1214041499034917</v>
-      </c>
-      <c r="W101">
-        <v>0.1903310780682222</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4856165996139669</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
